--- a/research/traditional_assets/database/data/bermuda/bermuda_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_real_estate_operations_services.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -596,40 +596,40 @@
         <v>0.0218</v>
       </c>
       <c r="G2">
-        <v>0.3617685426761088</v>
+        <v>0.3604834440161612</v>
       </c>
       <c r="H2">
-        <v>0.3617685426761088</v>
+        <v>0.3604834440161612</v>
       </c>
       <c r="I2">
-        <v>0.2871785314945956</v>
+        <v>0.2854846050248455</v>
       </c>
       <c r="J2">
-        <v>0.2871785314945956</v>
+        <v>0.2854846050248455</v>
       </c>
       <c r="K2">
-        <v>-1082.3</v>
+        <v>-1100.834</v>
       </c>
       <c r="L2">
-        <v>-0.5042396571002609</v>
+        <v>-0.5112311336088794</v>
       </c>
       <c r="M2">
         <v>507</v>
       </c>
       <c r="N2">
-        <v>0.05163195682061205</v>
+        <v>0.05082849443392898</v>
       </c>
       <c r="O2">
-        <v>-0.4684468262034556</v>
+        <v>-0.4605599027646312</v>
       </c>
       <c r="P2">
         <v>478.8</v>
       </c>
       <c r="Q2">
-        <v>0.04876012016905138</v>
+        <v>0.04800134740624298</v>
       </c>
       <c r="R2">
-        <v>-0.442391203917583</v>
+        <v>-0.4349429614274268</v>
       </c>
       <c r="S2">
         <v>28.19999999999999</v>
@@ -638,73 +638,73 @@
         <v>0.05562130177514791</v>
       </c>
       <c r="U2">
-        <v>1068.9</v>
+        <v>1076.16</v>
       </c>
       <c r="V2">
-        <v>0.1088548296756454</v>
+        <v>0.1078887427416509</v>
       </c>
       <c r="W2">
-        <v>-0.03368146539115064</v>
+        <v>-0.04146892655367232</v>
       </c>
       <c r="X2">
-        <v>0.09573293149701441</v>
+        <v>0.08668206921158214</v>
       </c>
       <c r="Y2">
-        <v>-0.1294143968881651</v>
+        <v>-0.1281509957652545</v>
       </c>
       <c r="Z2">
-        <v>0.05696677911041163</v>
+        <v>0.05701837308705252</v>
       </c>
       <c r="AA2">
-        <v>0.01635963596890501</v>
+        <v>-0.01161671707451196</v>
       </c>
       <c r="AB2">
-        <v>0.08265983161077731</v>
+        <v>0.07973846829728631</v>
       </c>
       <c r="AC2">
-        <v>-0.0663001956418723</v>
+        <v>-0.09135518537179826</v>
       </c>
       <c r="AD2">
-        <v>6425.4</v>
+        <v>6477.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6425.4</v>
+        <v>6477.2</v>
       </c>
       <c r="AG2">
-        <v>5356.5</v>
+        <v>5401.04</v>
       </c>
       <c r="AH2">
-        <v>0.3955333673953056</v>
+        <v>0.3937048077063346</v>
       </c>
       <c r="AI2">
-        <v>0.1738742176147295</v>
+        <v>0.1748633289688593</v>
       </c>
       <c r="AJ2">
-        <v>0.352958618871903</v>
+        <v>0.3512697908916372</v>
       </c>
       <c r="AK2">
-        <v>0.1492668327509238</v>
+        <v>0.150173472571092</v>
       </c>
       <c r="AL2">
-        <v>242.7</v>
+        <v>246.85</v>
       </c>
       <c r="AM2">
-        <v>119.6</v>
+        <v>123.426</v>
       </c>
       <c r="AN2">
-        <v>10.24131335671023</v>
+        <v>10.34101794495179</v>
       </c>
       <c r="AO2">
-        <v>2.53976102183766</v>
+        <v>2.49031395584363</v>
       </c>
       <c r="AP2">
-        <v>8.537615556263948</v>
+        <v>8.62290056836324</v>
       </c>
       <c r="AQ2">
-        <v>5.153846153846154</v>
+        <v>4.980587558537098</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>-0.03368146539115064</v>
       </c>
       <c r="X3">
-        <v>0.09573293149701441</v>
+        <v>0.09571248118736939</v>
       </c>
       <c r="Y3">
-        <v>-0.1294143968881651</v>
+        <v>-0.12939394657852</v>
       </c>
       <c r="Z3">
         <v>0.05696677911041163</v>
@@ -793,10 +793,10 @@
         <v>0.01635963596890501</v>
       </c>
       <c r="AB3">
-        <v>0.08265983161077731</v>
+        <v>0.08264747008097045</v>
       </c>
       <c r="AC3">
-        <v>-0.0663001956418723</v>
+        <v>-0.06628783411206544</v>
       </c>
       <c r="AD3">
         <v>6425.4</v>
@@ -839,6 +839,259 @@
       </c>
       <c r="AQ3">
         <v>5.153846153846154</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Auto Italia Holdings Limited (SEHK:720)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Real Estate (Operations &amp; Services)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.339</v>
+      </c>
+      <c r="G4">
+        <v>-0.09582463465553236</v>
+      </c>
+      <c r="H4">
+        <v>-0.09582463465553236</v>
+      </c>
+      <c r="I4">
+        <v>-0.1764091858037578</v>
+      </c>
+      <c r="J4">
+        <v>-0.1764091858037578</v>
+      </c>
+      <c r="K4">
+        <v>-17.8</v>
+      </c>
+      <c r="L4">
+        <v>-3.7160751565762</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2.67</v>
+      </c>
+      <c r="V4">
+        <v>0.01830020562028787</v>
+      </c>
+      <c r="W4">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="X4">
+        <v>0.08668206921158214</v>
+      </c>
+      <c r="Y4">
+        <v>-0.7533487358782489</v>
+      </c>
+      <c r="Z4">
+        <v>0.06585097607918614</v>
+      </c>
+      <c r="AA4">
+        <v>-0.01161671707451196</v>
+      </c>
+      <c r="AB4">
+        <v>0.07973846829728631</v>
+      </c>
+      <c r="AC4">
+        <v>-0.09135518537179826</v>
+      </c>
+      <c r="AD4">
+        <v>51.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>51.8</v>
+      </c>
+      <c r="AG4">
+        <v>49.13</v>
+      </c>
+      <c r="AH4">
+        <v>0.2620131512392514</v>
+      </c>
+      <c r="AI4">
+        <v>0.7562043795620438</v>
+      </c>
+      <c r="AJ4">
+        <v>0.251909962569861</v>
+      </c>
+      <c r="AK4">
+        <v>0.7463162691781862</v>
+      </c>
+      <c r="AL4">
+        <v>4.15</v>
+      </c>
+      <c r="AM4">
+        <v>4.149</v>
+      </c>
+      <c r="AN4">
+        <v>-219.4915254237288</v>
+      </c>
+      <c r="AO4">
+        <v>-0.2036144578313253</v>
+      </c>
+      <c r="AP4">
+        <v>-208.1779661016949</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.2036635333815377</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RomReal Limited (OB:ROM)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Real Estate (Operations &amp; Services)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.5429999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.08909952606635071</v>
+      </c>
+      <c r="H5">
+        <v>0.08909952606635071</v>
+      </c>
+      <c r="I5">
+        <v>-0.3890995260663507</v>
+      </c>
+      <c r="J5">
+        <v>-0.3890995260663507</v>
+      </c>
+      <c r="K5">
+        <v>-0.734</v>
+      </c>
+      <c r="L5">
+        <v>-0.3478672985781991</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>4.59</v>
+      </c>
+      <c r="V5">
+        <v>0.4924892703862661</v>
+      </c>
+      <c r="W5">
+        <v>-0.04146892655367232</v>
+      </c>
+      <c r="X5">
+        <v>0.07597042942827432</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1174393559819466</v>
+      </c>
+      <c r="Z5">
+        <v>0.1488011283497884</v>
+      </c>
+      <c r="AA5">
+        <v>-0.0578984485190409</v>
+      </c>
+      <c r="AB5">
+        <v>0.07597042942827432</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1338688779473152</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-4.59</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.9704016913319238</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3253012048192771</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-0.323</v>
+      </c>
+      <c r="AN5">
+        <v>-0</v>
+      </c>
+      <c r="AP5">
+        <v>5.708955223880596</v>
+      </c>
+      <c r="AQ5">
+        <v>2.541795665634675</v>
       </c>
     </row>
   </sheetData>
@@ -1151,13 +1404,13 @@
         <v>9819.5</v>
       </c>
       <c r="L2">
-        <v>19548.1579896179</v>
+        <v>19548.2039153343</v>
       </c>
       <c r="M2">
         <v>15176</v>
       </c>
       <c r="N2">
-        <v>18479.2579896179</v>
+        <v>18479.3039153343</v>
       </c>
       <c r="O2">
         <v>6425.4</v>
@@ -1166,16 +1419,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.08265983161077731</v>
+        <v>0.08264747008097049</v>
       </c>
       <c r="R2">
-        <v>0.07598279095808121</v>
+        <v>0.0759704294282743</v>
       </c>
       <c r="S2">
         <v>0.06268110587651871</v>
       </c>
       <c r="T2">
-        <v>0.0600811058765187</v>
+        <v>0.0586811058765187</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1441,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0957329314970144</v>
+        <v>0.0957124811873694</v>
       </c>
       <c r="X2">
-        <v>0.07598279095808121</v>
+        <v>0.0759704294282743</v>
       </c>
       <c r="Y2">
         <v>0.914164621486046</v>
@@ -1230,7 +1483,7 @@
         <v>9819.5</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788713</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1671,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07598279095808118</v>
+        <v>0.07597042942827434</v>
       </c>
       <c r="C2">
-        <v>19548.15798961793</v>
+        <v>19548.20391533428</v>
       </c>
       <c r="D2">
-        <v>18479.25798961793</v>
+        <v>18479.30391533428</v>
       </c>
       <c r="E2">
         <v>-6425.4</v>
@@ -1469,19 +1722,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07598279095808118</v>
+        <v>0.07597042942827434</v>
       </c>
       <c r="T2">
         <v>0.5525820103960151</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1753,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07612560201684637</v>
+        <v>0.07609924048703952</v>
       </c>
       <c r="C3">
-        <v>19300.07811639984</v>
+        <v>19308.48221187117</v>
       </c>
       <c r="D3">
-        <v>18393.62711639984</v>
+        <v>18402.03121187117</v>
       </c>
       <c r="E3">
         <v>-6262.951</v>
@@ -1533,37 +1786,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M3">
-        <v>9.760115568534589</v>
+        <v>9.532686968534589</v>
       </c>
       <c r="N3">
-        <v>676.3509955425765</v>
+        <v>676.5784241425765</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>676.3509955425765</v>
+        <v>676.5784241425765</v>
       </c>
       <c r="Q3">
-        <v>687.3509955425765</v>
+        <v>687.5784241425765</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07628766763442543</v>
+        <v>0.07627518124068114</v>
       </c>
       <c r="T3">
         <v>0.5581636468646617</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1824,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>70.29743718640472</v>
+        <v>71.97457688223905</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1835,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07626841307561155</v>
+        <v>0.0762280515458047</v>
       </c>
       <c r="C4">
-        <v>19052.78819097</v>
+        <v>19069.40406145376</v>
       </c>
       <c r="D4">
-        <v>18308.78619097</v>
+        <v>18325.40206145376</v>
       </c>
       <c r="E4">
         <v>-6100.501999999999</v>
@@ -1615,37 +1868,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M4">
-        <v>19.52023113706918</v>
+        <v>19.06537393706918</v>
       </c>
       <c r="N4">
-        <v>666.5908799740419</v>
+        <v>667.045737174042</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>666.5908799740419</v>
+        <v>667.045737174042</v>
       </c>
       <c r="Q4">
-        <v>677.5908799740419</v>
+        <v>678.045737174042</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07659876628375631</v>
+        <v>0.07658615247783095</v>
       </c>
       <c r="T4">
         <v>0.563859194281648</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1906,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.14871859320236</v>
+        <v>35.98728844111952</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1917,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07641122413437675</v>
+        <v>0.07635686260456989</v>
       </c>
       <c r="C5">
-        <v>18806.27733257227</v>
+        <v>18830.96145783233</v>
       </c>
       <c r="D5">
-        <v>18224.72433257227</v>
+        <v>18249.40845783233</v>
       </c>
       <c r="E5">
         <v>-5938.053</v>
@@ -1697,37 +1950,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M5">
-        <v>29.28034670560377</v>
+        <v>28.59806090560377</v>
       </c>
       <c r="N5">
-        <v>656.8307644055074</v>
+        <v>657.5130502055073</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>656.8307644055074</v>
+        <v>657.5130502055073</v>
       </c>
       <c r="Q5">
-        <v>667.8307644055074</v>
+        <v>668.5130502055073</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07691627933822802</v>
+        <v>0.07690353549306632</v>
       </c>
       <c r="T5">
         <v>0.5696721756659948</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1988,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.43247906213491</v>
+        <v>23.99152562741302</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1999,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07655403519314194</v>
+        <v>0.07648567366333507</v>
       </c>
       <c r="C6">
-        <v>18560.53485936626</v>
+        <v>18593.14652701318</v>
       </c>
       <c r="D6">
-        <v>18141.43085936626</v>
+        <v>18174.04252701318</v>
       </c>
       <c r="E6">
         <v>-5775.603999999999</v>
@@ -1779,37 +2032,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M6">
-        <v>39.04046227413836</v>
+        <v>38.13074787413836</v>
       </c>
       <c r="N6">
-        <v>647.0706488369727</v>
+        <v>647.9803632369727</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>647.0706488369727</v>
+        <v>647.9803632369727</v>
       </c>
       <c r="Q6">
-        <v>658.0706488369727</v>
+        <v>658.9803632369727</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07724040724800124</v>
+        <v>0.07722753065445243</v>
       </c>
       <c r="T6">
         <v>0.5756062608291824</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +2070,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.57435929660118</v>
+        <v>17.99364422055976</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +2081,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07669684625190712</v>
+        <v>0.07661448472210027</v>
       </c>
       <c r="C7">
-        <v>18315.55028390237</v>
+        <v>18355.95152453887</v>
       </c>
       <c r="D7">
-        <v>18058.89528390237</v>
+        <v>18099.29652453887</v>
       </c>
       <c r="E7">
         <v>-5613.155</v>
@@ -1861,37 +2114,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M7">
-        <v>48.80057784267294</v>
+        <v>47.66343484267294</v>
       </c>
       <c r="N7">
-        <v>637.3105332684381</v>
+        <v>638.4476762684382</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>637.3105332684381</v>
+        <v>638.4476762684382</v>
       </c>
       <c r="Q7">
-        <v>648.3105332684381</v>
+        <v>649.4476762684382</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07757135890324335</v>
+        <v>0.07755834676660456</v>
       </c>
       <c r="T7">
         <v>0.5816652741010685</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2152,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>14.05948743728094</v>
+        <v>14.39491537644781</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2163,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07683965731067231</v>
+        <v>0.07674329578086544</v>
       </c>
       <c r="C8">
-        <v>18071.31330871983</v>
+        <v>18119.36883283543</v>
       </c>
       <c r="D8">
-        <v>17977.10730871983</v>
+        <v>18025.16283283543</v>
       </c>
       <c r="E8">
         <v>-5450.706</v>
@@ -1943,37 +2196,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M8">
-        <v>58.56069341120753</v>
+        <v>57.19612181120753</v>
       </c>
       <c r="N8">
-        <v>627.5504176999035</v>
+        <v>628.9149892999036</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>627.5504176999035</v>
+        <v>628.9149892999036</v>
       </c>
       <c r="Q8">
-        <v>638.5504176999035</v>
+        <v>639.9149892999036</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0779093520830651</v>
+        <v>0.07789620151944078</v>
       </c>
       <c r="T8">
         <v>0.5878532025489522</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2234,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.71623953106745</v>
+        <v>11.99576281370651</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2245,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07698246836943749</v>
+        <v>0.07687210683963064</v>
       </c>
       <c r="C9">
-        <v>17827.81382206394</v>
+        <v>17883.39095862435</v>
       </c>
       <c r="D9">
-        <v>17896.05682206394</v>
+        <v>17951.63395862435</v>
       </c>
       <c r="E9">
         <v>-5288.257</v>
@@ -2025,37 +2278,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M9">
-        <v>68.32080897974213</v>
+        <v>66.72880877974212</v>
       </c>
       <c r="N9">
-        <v>617.790302131369</v>
+        <v>619.3823023313689</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>617.790302131369</v>
+        <v>619.3823023313689</v>
       </c>
       <c r="Q9">
-        <v>628.790302131369</v>
+        <v>630.3823023313689</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07825461393342062</v>
+        <v>0.07824132196588637</v>
       </c>
       <c r="T9">
         <v>0.5941742047268979</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2316,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.04249102662925</v>
+        <v>10.28208241174844</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2327,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07712527942820267</v>
+        <v>0.07700091789839583</v>
       </c>
       <c r="C10">
-        <v>17585.04189371843</v>
+        <v>17648.01053039779</v>
       </c>
       <c r="D10">
-        <v>17815.73389371843</v>
+        <v>17878.70253039779</v>
       </c>
       <c r="E10">
         <v>-5125.807999999999</v>
@@ -2107,37 +2360,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M10">
-        <v>78.08092454827671</v>
+        <v>76.26149574827672</v>
       </c>
       <c r="N10">
-        <v>608.0301865628344</v>
+        <v>609.8496153628344</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>608.0301865628344</v>
+        <v>609.8496153628344</v>
       </c>
       <c r="Q10">
-        <v>619.0301865628344</v>
+        <v>620.8496153628344</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07860738147617519</v>
+        <v>0.07859394503073297</v>
       </c>
       <c r="T10">
         <v>0.6006326199956685</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2398,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.78717964830059</v>
+        <v>8.996822110279881</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2409,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07736709048696788</v>
+        <v>0.07726472895716102</v>
       </c>
       <c r="C11">
-        <v>17288.21983899472</v>
+        <v>17338.02893812492</v>
       </c>
       <c r="D11">
-        <v>17681.36083899472</v>
+        <v>17731.16993812492</v>
       </c>
       <c r="E11">
         <v>-4963.358999999999</v>
@@ -2189,37 +2442,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M11">
-        <v>89.4492852168113</v>
+        <v>87.98724421681131</v>
       </c>
       <c r="N11">
-        <v>596.6618258942998</v>
+        <v>598.1238668942998</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>596.6618258942998</v>
+        <v>598.1238668942998</v>
       </c>
       <c r="Q11">
-        <v>607.6618258942998</v>
+        <v>609.1238668942998</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07896790215173757</v>
+        <v>0.07895431805304873</v>
       </c>
       <c r="T11">
         <v>0.6072329784571595</v>
       </c>
       <c r="U11">
-        <v>0.06118110587651872</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.06118110587651872</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2480,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.670392328435978</v>
+        <v>7.797847485942958</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2491,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07752090154573305</v>
+        <v>0.0774085400159262</v>
       </c>
       <c r="C12">
-        <v>17041.34857511461</v>
+        <v>17096.17647670852</v>
       </c>
       <c r="D12">
-        <v>17596.93857511461</v>
+        <v>17651.76647670852</v>
       </c>
       <c r="E12">
         <v>-4800.91</v>
@@ -2271,37 +2524,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M12">
-        <v>99.38809468534589</v>
+        <v>97.7636046853459</v>
       </c>
       <c r="N12">
-        <v>586.7230164257652</v>
+        <v>588.3475064257652</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>586.7230164257652</v>
+        <v>588.3475064257652</v>
       </c>
       <c r="Q12">
-        <v>597.7230164257652</v>
+        <v>599.3475064257652</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07933643439786797</v>
+        <v>0.07932269936474926</v>
       </c>
       <c r="T12">
         <v>0.6139800115511279</v>
       </c>
       <c r="U12">
-        <v>0.06118110587651872</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.06118110587651872</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2562,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.903353095592379</v>
+        <v>7.018062737348663</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2573,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07791671260449824</v>
+        <v>0.0777393510746914</v>
       </c>
       <c r="C13">
-        <v>16665.31239672518</v>
+        <v>16753.74630993861</v>
       </c>
       <c r="D13">
-        <v>17383.35139672518</v>
+        <v>17471.78530993861</v>
       </c>
       <c r="E13">
         <v>-4638.460999999999</v>
@@ -2353,37 +2606,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M13">
-        <v>113.2581699538805</v>
+        <v>110.5777614538805</v>
       </c>
       <c r="N13">
-        <v>572.8529411572306</v>
+        <v>575.5333496572306</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>572.8529411572306</v>
+        <v>575.5333496572306</v>
       </c>
       <c r="Q13">
-        <v>583.8529411572306</v>
+        <v>586.5333496572306</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07971324826750695</v>
+        <v>0.07969935890817341</v>
       </c>
       <c r="T13">
         <v>0.6208786633663091</v>
       </c>
       <c r="U13">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2644,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.057939232026267</v>
+        <v>6.204783874172319</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2655,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07827252366326343</v>
+        <v>0.07790016213345657</v>
       </c>
       <c r="C14">
-        <v>16315.23865332074</v>
+        <v>16505.12558148245</v>
       </c>
       <c r="D14">
-        <v>17195.72665332074</v>
+        <v>17385.61358148245</v>
       </c>
       <c r="E14">
         <v>-4476.012</v>
@@ -2435,45 +2688,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M14">
-        <v>126.4784492224151</v>
+        <v>120.6302852224151</v>
       </c>
       <c r="N14">
-        <v>559.632661888696</v>
+        <v>565.480825888696</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>559.632661888696</v>
+        <v>565.480825888696</v>
       </c>
       <c r="Q14">
-        <v>570.632661888696</v>
+        <v>576.480825888696</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08009862608872861</v>
+        <v>0.08008457889576628</v>
       </c>
       <c r="T14">
         <v>0.6279341027227443</v>
       </c>
       <c r="U14">
-        <v>0.06488110587651871</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.06488110587651871</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>5.424727416641313</v>
+        <v>5.687718551324626</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2737,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07846333472202863</v>
+        <v>0.07816497319222176</v>
       </c>
       <c r="C15">
-        <v>16053.83078632388</v>
+        <v>16202.61314446036</v>
       </c>
       <c r="D15">
-        <v>17096.76778632388</v>
+        <v>17245.55014446036</v>
       </c>
       <c r="E15">
         <v>-4313.563</v>
@@ -2517,37 +2770,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M15">
-        <v>137.0183199909496</v>
+        <v>132.3722785909497</v>
       </c>
       <c r="N15">
-        <v>549.0927911201615</v>
+        <v>553.7388325201614</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>549.0927911201615</v>
+        <v>553.7388325201614</v>
       </c>
       <c r="Q15">
-        <v>560.0927911201615</v>
+        <v>564.7388325201614</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08049286317020826</v>
+        <v>0.08047865451525785</v>
       </c>
       <c r="T15">
         <v>0.6351517360873736</v>
       </c>
       <c r="U15">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2808,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.007440692284289</v>
+        <v>5.183193327292477</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2819,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0786541457807938</v>
+        <v>0.07833378425098694</v>
       </c>
       <c r="C16">
-        <v>15793.55538945442</v>
+        <v>15952.04873003331</v>
       </c>
       <c r="D16">
-        <v>16998.94138945442</v>
+        <v>17157.43473003331</v>
       </c>
       <c r="E16">
         <v>-4151.114</v>
@@ -2599,37 +2852,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M16">
-        <v>147.5581907594842</v>
+        <v>142.5547615594843</v>
       </c>
       <c r="N16">
-        <v>538.5529203516269</v>
+        <v>543.5563495516268</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>538.5529203516269</v>
+        <v>543.5563495516268</v>
       </c>
       <c r="Q16">
-        <v>549.5529203516269</v>
+        <v>554.5563495516268</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08089626855590835</v>
+        <v>0.08088189468403992</v>
       </c>
       <c r="T16">
         <v>0.6425372213907152</v>
       </c>
       <c r="U16">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2890,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.649766357121125</v>
+        <v>4.812965232485871</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2901,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07884495683955899</v>
+        <v>0.07850259530975214</v>
       </c>
       <c r="C17">
-        <v>15534.39313358993</v>
+        <v>15702.38018223449</v>
       </c>
       <c r="D17">
-        <v>16902.22813358993</v>
+        <v>17070.21518223449</v>
       </c>
       <c r="E17">
         <v>-3988.665</v>
@@ -2681,37 +2934,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M17">
-        <v>158.0980615280188</v>
+        <v>152.7372445280188</v>
       </c>
       <c r="N17">
-        <v>528.0130495830923</v>
+        <v>533.3738665830922</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>528.0130495830923</v>
+        <v>533.3738665830922</v>
       </c>
       <c r="Q17">
-        <v>539.0130495830923</v>
+        <v>544.3738665830922</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08130916583303668</v>
+        <v>0.08129462285679333</v>
       </c>
       <c r="T17">
         <v>0.6500964828188412</v>
       </c>
       <c r="U17">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2972,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.33978193331305</v>
+        <v>4.49210088365348</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2983,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07925976789832417</v>
+        <v>0.07883140636851732</v>
       </c>
       <c r="C18">
-        <v>15165.44590867507</v>
+        <v>15372.56530557344</v>
       </c>
       <c r="D18">
-        <v>16695.72990867507</v>
+        <v>16902.84930557344</v>
       </c>
       <c r="E18">
         <v>-3826.215999999999</v>
@@ -2763,37 +3016,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M18">
-        <v>172.2767898965535</v>
+        <v>165.5189114965534</v>
       </c>
       <c r="N18">
-        <v>513.8343212145576</v>
+        <v>520.5921996145577</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>513.8343212145576</v>
+        <v>520.5921996145577</v>
       </c>
       <c r="Q18">
-        <v>524.8343212145576</v>
+        <v>531.5921996145577</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08173189399771569</v>
+        <v>0.08171717789080277</v>
       </c>
       <c r="T18">
         <v>0.6578357266619227</v>
       </c>
       <c r="U18">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +3054,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.982609099711564</v>
+        <v>4.145212803223382</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +3065,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07946457895708936</v>
+        <v>0.07901021742728251</v>
       </c>
       <c r="C19">
-        <v>14902.88886579874</v>
+        <v>15120.47124420821</v>
       </c>
       <c r="D19">
-        <v>16595.62186579873</v>
+        <v>16813.20424420821</v>
       </c>
       <c r="E19">
         <v>-3663.766999999999</v>
@@ -2845,37 +3098,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M19">
-        <v>183.044089265088</v>
+        <v>175.8638434650881</v>
       </c>
       <c r="N19">
-        <v>503.0670218460231</v>
+        <v>510.247267646023</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>503.0670218460231</v>
+        <v>510.247267646023</v>
       </c>
       <c r="Q19">
-        <v>514.0670218460231</v>
+        <v>521.247267646023</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08216480838323034</v>
+        <v>0.0821499149738245</v>
       </c>
       <c r="T19">
         <v>0.6657614583084519</v>
       </c>
       <c r="U19">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3136,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.74833797619912</v>
+        <v>3.901376755974947</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3147,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07966939001585456</v>
+        <v>0.07918902848604771</v>
       </c>
       <c r="C20">
-        <v>14641.5251685926</v>
+        <v>14869.3230400966</v>
       </c>
       <c r="D20">
-        <v>16496.7071685926</v>
+        <v>16724.5050400966</v>
       </c>
       <c r="E20">
         <v>-3501.318</v>
@@ -2927,37 +3180,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M20">
-        <v>193.8113886336226</v>
+        <v>186.2087754336226</v>
       </c>
       <c r="N20">
-        <v>492.2997224774884</v>
+        <v>499.9023356774885</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>492.2997224774884</v>
+        <v>499.9023356774885</v>
       </c>
       <c r="Q20">
-        <v>503.2997224774884</v>
+        <v>510.9023356774885</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08260828165619656</v>
+        <v>0.08259320661984675</v>
       </c>
       <c r="T20">
         <v>0.6738805004829452</v>
       </c>
       <c r="U20">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3218,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.540096977521391</v>
+        <v>3.684633602865229</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3229,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07987420107461973</v>
+        <v>0.0793678395448129</v>
       </c>
       <c r="C21">
-        <v>14381.33360543003</v>
+        <v>14619.10580199531</v>
       </c>
       <c r="D21">
-        <v>16398.96460543003</v>
+        <v>16636.73680199531</v>
       </c>
       <c r="E21">
         <v>-3338.869</v>
@@ -3009,37 +3262,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M21">
-        <v>204.5786880021572</v>
+        <v>196.5537074021572</v>
       </c>
       <c r="N21">
-        <v>481.5324231089539</v>
+        <v>489.5574037089539</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>481.5324231089539</v>
+        <v>489.5574037089539</v>
       </c>
       <c r="Q21">
-        <v>492.5324231089539</v>
+        <v>500.5574037089539</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08306270488651997</v>
+        <v>0.08304744373861028</v>
       </c>
       <c r="T21">
         <v>0.6822000128345864</v>
       </c>
       <c r="U21">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3300,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.353776083967634</v>
+        <v>3.4907055185039</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3311,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08007901213338492</v>
+        <v>0.07954665060357809</v>
       </c>
       <c r="C22">
-        <v>14122.29346443668</v>
+        <v>14369.80494961914</v>
       </c>
       <c r="D22">
-        <v>16302.37346443667</v>
+        <v>16549.88494961914</v>
       </c>
       <c r="E22">
         <v>-3176.42</v>
@@ -3091,37 +3344,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M22">
-        <v>215.3459873706918</v>
+        <v>206.8986393706918</v>
       </c>
       <c r="N22">
-        <v>470.7651237404193</v>
+        <v>479.2124717404193</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>470.7651237404193</v>
+        <v>479.2124717404193</v>
       </c>
       <c r="Q22">
-        <v>481.7651237404193</v>
+        <v>490.2124717404193</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08352848869760147</v>
+        <v>0.08351303678534291</v>
       </c>
       <c r="T22">
         <v>0.6907275129950188</v>
       </c>
       <c r="U22">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3382,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.186087279769252</v>
+        <v>3.316170242578705</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3393,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08028382319215012</v>
+        <v>0.07972546166234326</v>
       </c>
       <c r="C23">
-        <v>13864.38451885883</v>
+        <v>14121.40620556638</v>
       </c>
       <c r="D23">
-        <v>16206.91351885883</v>
+        <v>16463.93520556638</v>
       </c>
       <c r="E23">
         <v>-3013.971</v>
@@ -3173,37 +3426,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M23">
-        <v>226.1132867392264</v>
+        <v>217.2435713392263</v>
       </c>
       <c r="N23">
-        <v>459.9978243718847</v>
+        <v>468.8675397718847</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>459.9978243718847</v>
+        <v>468.8675397718847</v>
       </c>
       <c r="Q23">
-        <v>470.9978243718847</v>
+        <v>479.8675397718847</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08400606450390023</v>
+        <v>0.08399041699781562</v>
       </c>
       <c r="T23">
         <v>0.6994708992354621</v>
       </c>
       <c r="U23">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3464,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.034368837875478</v>
+        <v>3.158257373884481</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3475,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08106063425091529</v>
+        <v>0.07990427272110845</v>
       </c>
       <c r="C24">
-        <v>13349.81374319393</v>
+        <v>13873.89558749452</v>
       </c>
       <c r="D24">
-        <v>15854.79174319393</v>
+        <v>16378.87358749452</v>
       </c>
       <c r="E24">
         <v>-2851.521999999999</v>
@@ -3255,45 +3508,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M24">
-        <v>246.172668907761</v>
+        <v>227.588503307761</v>
       </c>
       <c r="N24">
-        <v>439.9384422033501</v>
+        <v>458.5226078033501</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>439.9384422033501</v>
+        <v>458.5226078033501</v>
       </c>
       <c r="Q24">
-        <v>450.9384422033501</v>
+        <v>469.5226078033501</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08449588584369382</v>
+        <v>0.08448003772855683</v>
       </c>
       <c r="T24">
         <v>0.7084384748666859</v>
       </c>
       <c r="U24">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.787113265478678</v>
+        <v>3.014700220526096</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3557,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08129144530968048</v>
+        <v>0.08065808377987364</v>
       </c>
       <c r="C25">
-        <v>13085.66971491321</v>
+        <v>13362.31066445911</v>
       </c>
       <c r="D25">
-        <v>15753.09671491321</v>
+        <v>16029.73766445911</v>
       </c>
       <c r="E25">
         <v>-2689.072999999999</v>
@@ -3337,37 +3590,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M25">
-        <v>257.3623356762956</v>
+        <v>247.2742527762956</v>
       </c>
       <c r="N25">
-        <v>428.7487754348155</v>
+        <v>438.8368583348155</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>428.7487754348155</v>
+        <v>438.8368583348155</v>
       </c>
       <c r="Q25">
-        <v>439.7487754348155</v>
+        <v>449.8368583348155</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08499842981568984</v>
+        <v>0.08498237588087576</v>
       </c>
       <c r="T25">
         <v>0.7176389745402793</v>
       </c>
       <c r="U25">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3628,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.66593442784917</v>
+        <v>2.774696934305664</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3639,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08152225636844566</v>
+        <v>0.08086189483863883</v>
       </c>
       <c r="C26">
-        <v>12822.82194675855</v>
+        <v>13108.00591381858</v>
       </c>
       <c r="D26">
-        <v>15652.69794675855</v>
+        <v>15937.88191381858</v>
       </c>
       <c r="E26">
         <v>-2526.624</v>
@@ -3419,37 +3672,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M26">
-        <v>268.5520024448301</v>
+        <v>258.0253072448302</v>
       </c>
       <c r="N26">
-        <v>417.559108666281</v>
+        <v>428.0858038662809</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>417.559108666281</v>
+        <v>428.0858038662809</v>
       </c>
       <c r="Q26">
-        <v>428.559108666281</v>
+        <v>439.0858038662809</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08551419862905418</v>
+        <v>0.08549793345825571</v>
       </c>
       <c r="T26">
         <v>0.7270815926263356</v>
       </c>
       <c r="U26">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3710,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.554853826688788</v>
+        <v>2.659084562042928</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3721,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08242806742721086</v>
+        <v>0.08106570589740401</v>
       </c>
       <c r="C27">
-        <v>12278.42531071199</v>
+        <v>12854.74789332543</v>
       </c>
       <c r="D27">
-        <v>15270.75031071199</v>
+        <v>15847.07289332543</v>
       </c>
       <c r="E27">
         <v>-2364.175</v>
@@ -3501,45 +3754,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M27">
-        <v>290.7069767133647</v>
+        <v>268.7763617133647</v>
       </c>
       <c r="N27">
-        <v>395.4041343977464</v>
+        <v>417.3347493977464</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>395.4041343977464</v>
+        <v>417.3347493977464</v>
       </c>
       <c r="Q27">
-        <v>406.4041343977464</v>
+        <v>428.3347493977464</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08604372127744157</v>
+        <v>0.08602723923769912</v>
       </c>
       <c r="T27">
         <v>0.7367760138613534</v>
       </c>
       <c r="U27">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.360146697778129</v>
+        <v>2.552721179561211</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3803,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08268587848597604</v>
+        <v>0.08217951695616919</v>
       </c>
       <c r="C28">
-        <v>12010.65090793162</v>
+        <v>12213.76281222267</v>
       </c>
       <c r="D28">
-        <v>15165.42490793162</v>
+        <v>15368.53681222266</v>
       </c>
       <c r="E28">
         <v>-2201.726</v>
@@ -3583,37 +3836,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M28">
-        <v>302.3352557818993</v>
+        <v>294.3102751818993</v>
       </c>
       <c r="N28">
-        <v>383.7758553292118</v>
+        <v>391.8008359292118</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>383.7758553292118</v>
+        <v>391.8008359292118</v>
       </c>
       <c r="Q28">
-        <v>394.7758553292118</v>
+        <v>402.8008359292118</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08658755534875834</v>
+        <v>0.0865708505787491</v>
       </c>
       <c r="T28">
         <v>0.7467324464811014</v>
       </c>
       <c r="U28">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3874,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.269371824786662</v>
+        <v>2.3312509584895</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3885,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08421268954474123</v>
+        <v>0.08317432801493439</v>
       </c>
       <c r="C29">
-        <v>11253.05478467149</v>
+        <v>11647.69712357523</v>
       </c>
       <c r="D29">
-        <v>14570.27778467149</v>
+        <v>14964.92012357523</v>
       </c>
       <c r="E29">
         <v>-2039.276999999999</v>
@@ -3665,37 +3918,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M29">
-        <v>334.5783129504339</v>
+        <v>317.911045550434</v>
       </c>
       <c r="N29">
-        <v>351.5327981606771</v>
+        <v>368.2000655606771</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>351.5327981606771</v>
+        <v>368.2000655606771</v>
       </c>
       <c r="Q29">
-        <v>362.5327981606771</v>
+        <v>379.2000655606771</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08714628898367285</v>
+        <v>0.08712935538119772</v>
       </c>
       <c r="T29">
         <v>0.7569616580767331</v>
       </c>
       <c r="U29">
-        <v>0.07628110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.07628110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3956,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.050674190627397</v>
+        <v>2.158185821833187</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3967,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08712150060350642</v>
+        <v>0.08344113907369959</v>
       </c>
       <c r="C30">
-        <v>10077.03478852461</v>
+        <v>11380.57723558891</v>
       </c>
       <c r="D30">
-        <v>13556.70678852461</v>
+        <v>14860.24923558891</v>
       </c>
       <c r="E30">
         <v>-1876.828</v>
@@ -3747,45 +4000,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M30">
-        <v>389.2718219189684</v>
+        <v>329.6855287189686</v>
       </c>
       <c r="N30">
-        <v>296.8392891921426</v>
+        <v>356.4255823921425</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>296.8392891921426</v>
+        <v>356.4255823921425</v>
       </c>
       <c r="Q30">
-        <v>307.8392891921426</v>
+        <v>367.4255823921425</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08772054299733498</v>
+        <v>0.08770337420593657</v>
       </c>
       <c r="T30">
         <v>0.7674750144389098</v>
       </c>
       <c r="U30">
-        <v>0.08558110587651871</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.08558110587651871</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.762550157699144</v>
+        <v>2.081107756767716</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +4049,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0888823116622716</v>
+        <v>0.08370795013246475</v>
       </c>
       <c r="C31">
-        <v>9366.782930538633</v>
+        <v>11114.91140097185</v>
       </c>
       <c r="D31">
-        <v>13008.90393053863</v>
+        <v>14757.03240097185</v>
       </c>
       <c r="E31">
         <v>-1714.379</v>
@@ -3829,45 +4082,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M31">
-        <v>425.3161856875031</v>
+        <v>341.4600118875031</v>
       </c>
       <c r="N31">
-        <v>260.794925423608</v>
+        <v>344.651099223608</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>260.794925423608</v>
+        <v>344.651099223608</v>
       </c>
       <c r="Q31">
-        <v>271.794925423608</v>
+        <v>355.651099223608</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08831097318039602</v>
+        <v>0.08829356257503426</v>
       </c>
       <c r="T31">
         <v>0.7782845216845282</v>
       </c>
       <c r="U31">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.613178934166462</v>
+        <v>2.00934542032745</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4131,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08932712272103679</v>
+        <v>0.08631476119122994</v>
       </c>
       <c r="C32">
-        <v>9072.883234229239</v>
+        <v>10014.65458853131</v>
       </c>
       <c r="D32">
-        <v>12877.45323422924</v>
+        <v>13819.22458853131</v>
       </c>
       <c r="E32">
         <v>-1551.93</v>
@@ -3911,45 +4164,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M32">
-        <v>439.9822610560376</v>
+        <v>391.2475610560376</v>
       </c>
       <c r="N32">
-        <v>246.1288500550735</v>
+        <v>294.8635500550735</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>246.1288500550735</v>
+        <v>294.8635500550735</v>
       </c>
       <c r="Q32">
-        <v>257.1288500550735</v>
+        <v>305.8635500550735</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08891827279725883</v>
+        <v>0.08890061346896333</v>
       </c>
       <c r="T32">
         <v>0.7894028719943073</v>
       </c>
       <c r="U32">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.55940630302758</v>
+        <v>1.753649554413045</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4213,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08977193377980197</v>
+        <v>0.08786857224999514</v>
       </c>
       <c r="C33">
-        <v>8781.61349518522</v>
+        <v>9347.846050826529</v>
       </c>
       <c r="D33">
-        <v>12748.63249518522</v>
+        <v>13314.86505082653</v>
       </c>
       <c r="E33">
         <v>-1389.481</v>
@@ -3993,37 +4246,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M33">
-        <v>454.6483364245723</v>
+        <v>423.9292305245723</v>
       </c>
       <c r="N33">
-        <v>231.4627746865388</v>
+        <v>262.1818805865388</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>231.4627746865388</v>
+        <v>262.1818805865388</v>
       </c>
       <c r="Q33">
-        <v>242.4627746865388</v>
+        <v>273.1818805865388</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08954317530156693</v>
+        <v>0.0895252600409773</v>
       </c>
       <c r="T33">
         <v>0.8008434933275581</v>
       </c>
       <c r="U33">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4284,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.509102873897658</v>
+        <v>1.618456718028416</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4295,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1058967448385671</v>
+        <v>0.08825238330876031</v>
       </c>
       <c r="C34">
-        <v>5226.369988949991</v>
+        <v>9066.433232482692</v>
       </c>
       <c r="D34">
-        <v>9355.837988949992</v>
+        <v>13195.90123248269</v>
       </c>
       <c r="E34">
         <v>-1227.031999999999</v>
@@ -4075,45 +4328,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M34">
-        <v>724.0344437931069</v>
+        <v>437.6043669931069</v>
       </c>
       <c r="N34">
-        <v>-37.92333268199582</v>
+        <v>248.5067441180042</v>
       </c>
       <c r="O34">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>-37.92333268199582</v>
+        <v>248.5067441180042</v>
       </c>
       <c r="Q34">
-        <v>-26.92333268199582</v>
+        <v>259.5067441180042</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09018645729129585</v>
+        <v>0.09016827857099166</v>
       </c>
       <c r="T34">
         <v>0.8126206035235516</v>
       </c>
       <c r="U34">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.9476221980775925</v>
+        <v>1.567879945590028</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4377,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1068315558973323</v>
+        <v>0.08863619436752551</v>
       </c>
       <c r="C35">
-        <v>4921.767830477901</v>
+        <v>8787.127392009828</v>
       </c>
       <c r="D35">
-        <v>9213.684830477901</v>
+        <v>13079.04439200983</v>
       </c>
       <c r="E35">
         <v>-1064.583</v>
@@ -4157,45 +4410,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M35">
-        <v>746.6605201616414</v>
+        <v>451.2795034616415</v>
       </c>
       <c r="N35">
-        <v>-60.54940905053036</v>
+        <v>234.8316076494696</v>
       </c>
       <c r="O35">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>-60.54940905053036</v>
+        <v>234.8316076494696</v>
       </c>
       <c r="Q35">
-        <v>-49.54940905053036</v>
+        <v>245.8316076494696</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09084894172847938</v>
+        <v>0.09083049168399154</v>
       </c>
       <c r="T35">
         <v>0.8247492692477837</v>
       </c>
       <c r="U35">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.9189063738934231</v>
+        <v>1.5203684320873</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4459,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1077663669560975</v>
+        <v>0.0938480054262907</v>
       </c>
       <c r="C36">
-        <v>4621.420786618984</v>
+        <v>7220.742757074578</v>
       </c>
       <c r="D36">
-        <v>9075.786786618984</v>
+        <v>11675.10875707458</v>
       </c>
       <c r="E36">
         <v>-902.1339999999991</v>
@@ -4239,45 +4492,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M36">
-        <v>769.2865965301761</v>
+        <v>543.385017130176</v>
       </c>
       <c r="N36">
-        <v>-83.17548541906501</v>
+        <v>142.726093980935</v>
       </c>
       <c r="O36">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>-83.17548541906501</v>
+        <v>142.726093980935</v>
       </c>
       <c r="Q36">
-        <v>-72.17548541906501</v>
+        <v>153.726093980935</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09153150145163816</v>
+        <v>0.09151277186102172</v>
       </c>
       <c r="T36">
         <v>0.8372454702969925</v>
       </c>
       <c r="U36">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651872</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651872</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8918797158377342</v>
+        <v>1.262661077286831</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4541,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1087011780148627</v>
+        <v>0.1043838164850559</v>
       </c>
       <c r="C37">
-        <v>4325.140620155187</v>
+        <v>4976.572876468657</v>
       </c>
       <c r="D37">
-        <v>8941.955620155188</v>
+        <v>9593.387876468658</v>
       </c>
       <c r="E37">
         <v>-739.6849999999995</v>
@@ -4321,37 +4574,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M37">
-        <v>791.9126728987105</v>
+        <v>721.9783783987107</v>
       </c>
       <c r="N37">
-        <v>-105.8015617875994</v>
+        <v>-35.86726728759959</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-105.8015617875994</v>
+        <v>-35.86726728759959</v>
       </c>
       <c r="Q37">
-        <v>-94.80156178759944</v>
+        <v>-24.86726728759959</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09223506301243259</v>
+        <v>0.0922160452742682</v>
       </c>
       <c r="T37">
         <v>0.8501261698400232</v>
       </c>
       <c r="U37">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4612,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8663974382423705</v>
+        <v>0.9503208567448374</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4623,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1096359890736279</v>
+        <v>0.1051956275438211</v>
       </c>
       <c r="C38">
-        <v>4032.750035476066</v>
+        <v>4684.108567810247</v>
       </c>
       <c r="D38">
-        <v>8812.014035476066</v>
+        <v>9463.372567810247</v>
       </c>
       <c r="E38">
         <v>-577.2359999999999</v>
@@ -4403,37 +4656,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M38">
-        <v>814.5387492672451</v>
+        <v>742.6063320672453</v>
       </c>
       <c r="N38">
-        <v>-128.427638156134</v>
+        <v>-56.49522095613418</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-128.427638156134</v>
+        <v>-56.49522095613418</v>
       </c>
       <c r="Q38">
-        <v>-117.427638156134</v>
+        <v>-45.49522095613418</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09296061087200184</v>
+        <v>0.09294129598167863</v>
       </c>
       <c r="T38">
         <v>0.8634093912437736</v>
       </c>
       <c r="U38">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4694,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.842330842735638</v>
+        <v>0.9239230551685919</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4705,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1105708001323931</v>
+        <v>0.1060074386025863</v>
       </c>
       <c r="C39">
-        <v>3744.081894966597</v>
+        <v>4395.12122707422</v>
       </c>
       <c r="D39">
-        <v>8685.794894966597</v>
+        <v>9336.83422707422</v>
       </c>
       <c r="E39">
         <v>-414.7870000000003</v>
@@ -4485,37 +4738,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M39">
-        <v>837.1648256357796</v>
+        <v>763.2342857357797</v>
       </c>
       <c r="N39">
-        <v>-151.0537145246685</v>
+        <v>-77.12317462466865</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-151.0537145246685</v>
+        <v>-77.12317462466865</v>
       </c>
       <c r="Q39">
-        <v>-140.0537145246685</v>
+        <v>-66.12317462466865</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09370919199695427</v>
+        <v>0.09368957052107038</v>
       </c>
       <c r="T39">
         <v>0.877114302215897</v>
       </c>
       <c r="U39">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4776,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8195651442833235</v>
+        <v>0.8989521617856571</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4787,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1437676111911583</v>
+        <v>0.1068192496613515</v>
       </c>
       <c r="C40">
-        <v>653.1516215828851</v>
+        <v>4109.473219065872</v>
       </c>
       <c r="D40">
-        <v>5757.313621582885</v>
+        <v>9213.635219065873</v>
       </c>
       <c r="E40">
         <v>-252.3379999999997</v>
@@ -4567,45 +4820,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M40">
-        <v>1383.883865804314</v>
+        <v>783.8622394043144</v>
       </c>
       <c r="N40">
-        <v>-697.7727546932033</v>
+        <v>-97.75112829320335</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-697.7727546932033</v>
+        <v>-97.75112829320335</v>
       </c>
       <c r="Q40">
-        <v>-686.7727546932033</v>
+        <v>-86.75112829320335</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09448192090013094</v>
+        <v>0.09446198294882957</v>
       </c>
       <c r="T40">
         <v>0.8912613070903468</v>
       </c>
       <c r="U40">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.4957866249219857</v>
+        <v>0.8752955259491922</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4869,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1455514222499235</v>
+        <v>0.1076310607201166</v>
       </c>
       <c r="C41">
-        <v>388.2536550727455</v>
+        <v>3827.034078340985</v>
       </c>
       <c r="D41">
-        <v>5654.864655072745</v>
+        <v>9093.645078340985</v>
       </c>
       <c r="E41">
         <v>-89.88899999999921</v>
@@ -4649,45 +4902,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M41">
-        <v>1420.301862272849</v>
+        <v>804.4901930728491</v>
       </c>
       <c r="N41">
-        <v>-734.190751161738</v>
+        <v>-118.3790819617381</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-734.190751161738</v>
+        <v>-118.3790819617381</v>
       </c>
       <c r="Q41">
-        <v>-723.190751161738</v>
+        <v>-107.3790819617381</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09527998517718227</v>
+        <v>0.09525972037422022</v>
       </c>
       <c r="T41">
         <v>0.9058721481901887</v>
       </c>
       <c r="U41">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.4830741473598834</v>
+        <v>0.8528520509248539</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4951,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1473352333086887</v>
+        <v>0.1084428717788818</v>
       </c>
       <c r="C42">
-        <v>126.9380148364789</v>
+        <v>3547.680048345567</v>
       </c>
       <c r="D42">
-        <v>5555.998014836478</v>
+        <v>8976.740048345568</v>
       </c>
       <c r="E42">
         <v>72.5600000000004</v>
@@ -4731,45 +4984,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M42">
-        <v>1456.719858741384</v>
+        <v>825.1181467413836</v>
       </c>
       <c r="N42">
-        <v>-770.6087476302725</v>
+        <v>-139.0070356302725</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-770.6087476302725</v>
+        <v>-139.0070356302725</v>
       </c>
       <c r="Q42">
-        <v>-759.6087476302725</v>
+        <v>-128.0070356302725</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09610465159680197</v>
+        <v>0.09608404904712389</v>
       </c>
       <c r="T42">
         <v>0.9209700173266918</v>
       </c>
       <c r="U42">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.4709972936758863</v>
+        <v>0.8315307496517327</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +5033,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1491190443674539</v>
+        <v>0.109254682837647</v>
       </c>
       <c r="C43">
-        <v>-130.979964977384</v>
+        <v>3271.293655652483</v>
       </c>
       <c r="D43">
-        <v>5460.529035022617</v>
+        <v>8862.802655652484</v>
       </c>
       <c r="E43">
         <v>235.0090000000009</v>
@@ -4813,45 +5066,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M43">
-        <v>1493.137855209918</v>
+        <v>845.7461004099183</v>
       </c>
       <c r="N43">
-        <v>-807.0267440988073</v>
+        <v>-159.6349892988072</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-807.0267440988073</v>
+        <v>-159.6349892988072</v>
       </c>
       <c r="Q43">
-        <v>-796.0267440988073</v>
+        <v>-148.6349892988072</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09695727281030708</v>
+        <v>0.09693632106487174</v>
       </c>
       <c r="T43">
         <v>0.9365796786373136</v>
       </c>
       <c r="U43">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.4595095548057427</v>
+        <v>0.8112495118553489</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +5115,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1509028554262191</v>
+        <v>0.1445904938964122</v>
       </c>
       <c r="C44">
-        <v>-385.6724721430537</v>
+        <v>-45.11357270572717</v>
       </c>
       <c r="D44">
-        <v>5368.285527856945</v>
+        <v>5708.844427294272</v>
       </c>
       <c r="E44">
         <v>397.4579999999996</v>
@@ -4895,37 +5148,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M44">
-        <v>1529.555851678453</v>
+        <v>1427.212981678453</v>
       </c>
       <c r="N44">
-        <v>-843.4447405673416</v>
+        <v>-741.1018705673416</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-843.4447405673416</v>
+        <v>-741.1018705673416</v>
       </c>
       <c r="Q44">
-        <v>-832.4447405673416</v>
+        <v>-730.1018705673416</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09783929475531238</v>
+        <v>0.09781798177288678</v>
       </c>
       <c r="T44">
         <v>0.9527276041310604</v>
       </c>
       <c r="U44">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5186,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4485688511198918</v>
+        <v>0.4807349147737013</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5197,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1526866664849842</v>
+        <v>0.1462243049551774</v>
       </c>
       <c r="C45">
-        <v>-637.3002527961316</v>
+        <v>-299.9753669449228</v>
       </c>
       <c r="D45">
-        <v>5279.106747203868</v>
+        <v>5616.431633055077</v>
       </c>
       <c r="E45">
         <v>559.9070000000002</v>
@@ -4977,37 +5230,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M45">
-        <v>1565.973848146987</v>
+        <v>1461.194243146987</v>
       </c>
       <c r="N45">
-        <v>-879.8627370358763</v>
+        <v>-775.0831320358764</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-879.8627370358763</v>
+        <v>-775.0831320358764</v>
       </c>
       <c r="Q45">
-        <v>-868.8627370358763</v>
+        <v>-764.0831320358764</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.0987522648387389</v>
+        <v>0.09873057794434092</v>
       </c>
       <c r="T45">
         <v>0.9694421235017807</v>
       </c>
       <c r="U45">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5268,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4381370173729175</v>
+        <v>0.469555033034778</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5279,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1544704775437494</v>
+        <v>0.1478581160139426</v>
       </c>
       <c r="C46">
-        <v>-886.0135462554526</v>
+        <v>-551.8929288520658</v>
       </c>
       <c r="D46">
-        <v>5192.842453744547</v>
+        <v>5526.963071147934</v>
       </c>
       <c r="E46">
         <v>722.3560000000007</v>
@@ -5059,37 +5312,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M46">
-        <v>1602.391844615522</v>
+        <v>1495.175504615522</v>
       </c>
       <c r="N46">
-        <v>-916.280733504411</v>
+        <v>-809.0643935044109</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-916.280733504411</v>
+        <v>-809.0643935044109</v>
       </c>
       <c r="Q46">
-        <v>-905.280733504411</v>
+        <v>-798.0643935044109</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09969784099657353</v>
+        <v>0.09967576683620416</v>
       </c>
       <c r="T46">
         <v>0.986753589992884</v>
       </c>
       <c r="U46">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5350,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4281793578871693</v>
+        <v>0.458883327738533</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5361,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1562542886025146</v>
+        <v>0.1494919270727078</v>
       </c>
       <c r="C47">
-        <v>-1131.9529296647</v>
+        <v>-801.0047551885782</v>
       </c>
       <c r="D47">
-        <v>5109.352070335301</v>
+        <v>5440.300244811421</v>
       </c>
       <c r="E47">
         <v>884.8050000000003</v>
@@ -5141,37 +5394,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M47">
-        <v>1638.809841084057</v>
+        <v>1529.156766084056</v>
       </c>
       <c r="N47">
-        <v>-952.6987299729456</v>
+        <v>-843.0456549729454</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-952.6987299729456</v>
+        <v>-843.0456549729454</v>
       </c>
       <c r="Q47">
-        <v>-941.6987299729456</v>
+        <v>-832.0456549729454</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1006778017419658</v>
+        <v>0.1006553262332261</v>
       </c>
       <c r="T47">
         <v>1.004694564356391</v>
       </c>
       <c r="U47">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5432,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4186642610452322</v>
+        <v>0.4486859204554545</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5443,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1580380996612798</v>
+        <v>0.151125738131473</v>
       </c>
       <c r="C48">
-        <v>-1375.250082442573</v>
+        <v>-1047.440790296469</v>
       </c>
       <c r="D48">
-        <v>5028.503917557427</v>
+        <v>5356.313209703532</v>
       </c>
       <c r="E48">
         <v>1047.254000000001</v>
@@ -5223,37 +5476,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M48">
-        <v>1675.227837552591</v>
+        <v>1563.138027552591</v>
       </c>
       <c r="N48">
-        <v>-989.1167264414803</v>
+        <v>-877.0269164414801</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-989.1167264414803</v>
+        <v>-877.0269164414801</v>
       </c>
       <c r="Q48">
-        <v>-978.1167264414803</v>
+        <v>-866.0269164414801</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.10169405732978</v>
+        <v>0.1016711656079154</v>
       </c>
       <c r="T48">
         <v>1.02330001925188</v>
       </c>
       <c r="U48">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5514,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4095628640659881</v>
+        <v>0.4389318787064229</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5525,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.159821910720045</v>
+        <v>0.1527595491902382</v>
       </c>
       <c r="C49">
-        <v>-1616.028479285566</v>
+        <v>-1291.323076220512</v>
       </c>
       <c r="D49">
-        <v>4950.174520714434</v>
+        <v>5274.879923779487</v>
       </c>
       <c r="E49">
         <v>1209.703</v>
@@ -5305,37 +5558,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M49">
-        <v>1711.645834021126</v>
+        <v>1597.119289021126</v>
       </c>
       <c r="N49">
-        <v>-1025.534722910015</v>
+        <v>-911.0081779100146</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-1025.534722910015</v>
+        <v>-911.0081779100146</v>
       </c>
       <c r="Q49">
-        <v>-1014.534722910015</v>
+        <v>-900.0081779100146</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1027486621850588</v>
+        <v>0.1027253385439138</v>
       </c>
       <c r="T49">
         <v>1.042607566784934</v>
       </c>
       <c r="U49">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5596,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4008487605752223</v>
+        <v>0.4295929025637331</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5607,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1616057217788102</v>
+        <v>0.1543933602490033</v>
       </c>
       <c r="C50">
-        <v>-1854.404019394429</v>
+        <v>-1532.766344414795</v>
       </c>
       <c r="D50">
-        <v>4874.24798060557</v>
+        <v>5195.885655585204</v>
       </c>
       <c r="E50">
         <v>1372.152</v>
@@ -5387,37 +5640,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M50">
-        <v>1748.06383048966</v>
+        <v>1631.10055048966</v>
       </c>
       <c r="N50">
-        <v>-1061.952719378549</v>
+        <v>-944.9894393785492</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-1061.952719378549</v>
+        <v>-944.9894393785492</v>
       </c>
       <c r="Q50">
-        <v>-1050.952719378549</v>
+        <v>-933.9894393785492</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1038438287655407</v>
+        <v>0.1038200565928352</v>
       </c>
       <c r="T50">
         <v>1.062657712300029</v>
       </c>
       <c r="U50">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5678,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3924977447299053</v>
+        <v>0.4206430504269887</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5689,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1633895328375754</v>
+        <v>0.1560271713077685</v>
       </c>
       <c r="C51">
-        <v>-2090.48559866839</v>
+        <v>-1771.878555066894</v>
       </c>
       <c r="D51">
-        <v>4800.61540133161</v>
+        <v>5119.222444933105</v>
       </c>
       <c r="E51">
         <v>1534.601</v>
@@ -5469,37 +5722,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M51">
-        <v>1784.481826958195</v>
+        <v>1665.081811958195</v>
       </c>
       <c r="N51">
-        <v>-1098.370715847084</v>
+        <v>-978.9707008470837</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-1098.370715847084</v>
+        <v>-978.9707008470837</v>
       </c>
       <c r="Q51">
-        <v>-1087.370715847084</v>
+        <v>-967.9707008470837</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1049819430550611</v>
+        <v>0.1049577047613222</v>
       </c>
       <c r="T51">
         <v>1.083494138031402</v>
       </c>
       <c r="U51">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5760,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3844875866741929</v>
+        <v>0.4120584983774582</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5771,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1651733438963406</v>
+        <v>0.1576609823665337</v>
       </c>
       <c r="C52">
-        <v>-2324.375630808209</v>
+        <v>-2008.761389371201</v>
       </c>
       <c r="D52">
-        <v>4729.17436919179</v>
+        <v>5044.788610628798</v>
       </c>
       <c r="E52">
         <v>1697.05</v>
@@ -5551,37 +5804,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M52">
-        <v>1820.89982342673</v>
+        <v>1699.063073426729</v>
       </c>
       <c r="N52">
-        <v>-1134.788712315619</v>
+        <v>-1012.951962315618</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-1134.788712315619</v>
+        <v>-1012.951962315618</v>
       </c>
       <c r="Q52">
-        <v>-1123.788712315619</v>
+        <v>-1001.951962315618</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1061655819161624</v>
+        <v>0.1061408588565487</v>
       </c>
       <c r="T52">
         <v>1.10516402079203</v>
       </c>
       <c r="U52">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5842,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3767978349407091</v>
+        <v>0.403817328409909</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5853,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1669571549551057</v>
+        <v>0.1592947934252989</v>
       </c>
       <c r="C53">
-        <v>-2556.170522572338</v>
+        <v>-2243.510699471608</v>
       </c>
       <c r="D53">
-        <v>4659.828477427662</v>
+        <v>4972.488300528391</v>
       </c>
       <c r="E53">
         <v>1859.499</v>
@@ -5633,37 +5886,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M53">
-        <v>1857.317819895264</v>
+        <v>1733.044334895264</v>
       </c>
       <c r="N53">
-        <v>-1171.206708784153</v>
+        <v>-1046.933223784153</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-1171.206708784153</v>
+        <v>-1046.933223784153</v>
       </c>
       <c r="Q53">
-        <v>-1160.206708784153</v>
+        <v>-1035.933223784153</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1073975325675126</v>
+        <v>0.1073723049556619</v>
       </c>
       <c r="T53">
         <v>1.127718388563296</v>
       </c>
       <c r="U53">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5924,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3694096420987344</v>
+        <v>0.3958993415783423</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5935,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.168740966013871</v>
+        <v>0.1609286044840641</v>
       </c>
       <c r="C54">
-        <v>-2785.961107824025</v>
+        <v>-2476.216920260265</v>
       </c>
       <c r="D54">
-        <v>4592.486892175975</v>
+        <v>4902.231079739735</v>
       </c>
       <c r="E54">
         <v>2021.948</v>
@@ -5715,37 +5968,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M54">
-        <v>1893.735816363799</v>
+        <v>1767.025596363799</v>
       </c>
       <c r="N54">
-        <v>-1207.624705252688</v>
+        <v>-1080.914485252688</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-1207.624705252688</v>
+        <v>-1080.914485252688</v>
       </c>
       <c r="Q54">
-        <v>-1196.624705252688</v>
+        <v>-1069.914485252688</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1086808144960025</v>
+        <v>0.1086550613089049</v>
       </c>
       <c r="T54">
         <v>1.151212521658365</v>
       </c>
       <c r="U54">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +6006,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3623056105199125</v>
+        <v>0.3882858927018357</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +6017,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1705247770726361</v>
+        <v>0.1625624155428293</v>
       </c>
       <c r="C55">
-        <v>-3013.833044478737</v>
+        <v>-2706.9654467524</v>
       </c>
       <c r="D55">
-        <v>4527.063955521264</v>
+        <v>4833.9315532476</v>
       </c>
       <c r="E55">
         <v>2184.397000000001</v>
@@ -5797,37 +6050,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M55">
-        <v>1930.153812832333</v>
+        <v>1801.006857832333</v>
       </c>
       <c r="N55">
-        <v>-1244.042701721222</v>
+        <v>-1114.895746721222</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-1244.042701721222</v>
+        <v>-1114.895746721222</v>
       </c>
       <c r="Q55">
-        <v>-1233.042701721222</v>
+        <v>-1103.895746721222</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1100187041661302</v>
+        <v>0.1099924030388816</v>
       </c>
       <c r="T55">
         <v>1.175706405097904</v>
       </c>
       <c r="U55">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V55">
         <v>0</v>
       </c>
       <c r="W55">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +6088,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3554696556044424</v>
+        <v>0.3809597437829331</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +6099,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1723085881314013</v>
+        <v>0.1641962266015944</v>
       </c>
       <c r="C56">
-        <v>-3239.867177999506</v>
+        <v>-2935.836980348362</v>
       </c>
       <c r="D56">
-        <v>4463.478822000496</v>
+        <v>4767.509019651639</v>
       </c>
       <c r="E56">
         <v>2346.846000000001</v>
@@ -5879,37 +6132,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M56">
-        <v>1966.571809300868</v>
+        <v>1834.988119300868</v>
       </c>
       <c r="N56">
-        <v>-1280.460698189757</v>
+        <v>-1148.877008189757</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-1280.460698189757</v>
+        <v>-1148.877008189757</v>
       </c>
       <c r="Q56">
-        <v>-1269.460698189757</v>
+        <v>-1137.877008189757</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1114147629523504</v>
+        <v>0.1113878900614659</v>
       </c>
       <c r="T56">
         <v>1.201265239991337</v>
       </c>
       <c r="U56">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +6170,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3488868842043602</v>
+        <v>0.3739049337128787</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6181,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1740923991901665</v>
+        <v>0.1658300376603596</v>
       </c>
       <c r="C57">
-        <v>-3464.139874683591</v>
+        <v>-3162.907846934912</v>
       </c>
       <c r="D57">
-        <v>4401.655125316408</v>
+        <v>4702.887153065088</v>
       </c>
       <c r="E57">
         <v>2509.295</v>
@@ -5961,37 +6214,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M57">
-        <v>2002.989805769402</v>
+        <v>1868.969380769403</v>
       </c>
       <c r="N57">
-        <v>-1316.878694658291</v>
+        <v>-1182.858269658291</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-1316.878694658291</v>
+        <v>-1182.858269658291</v>
       </c>
       <c r="Q57">
-        <v>-1305.878694658291</v>
+        <v>-1171.858269658291</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.112872868795736</v>
+        <v>0.1128453987294985</v>
       </c>
       <c r="T57">
         <v>1.227960023102256</v>
       </c>
       <c r="U57">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +6252,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3425434863097355</v>
+        <v>0.3671066621908264</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6263,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1758762102489317</v>
+        <v>0.1674638487191248</v>
       </c>
       <c r="C58">
-        <v>-3686.723327629432</v>
+        <v>-3388.250289461997</v>
       </c>
       <c r="D58">
-        <v>4341.520672370568</v>
+        <v>4639.993710538002</v>
       </c>
       <c r="E58">
         <v>2671.744000000001</v>
@@ -6043,37 +6296,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M58">
-        <v>2039.407802237937</v>
+        <v>1902.950642237937</v>
       </c>
       <c r="N58">
-        <v>-1353.296691126826</v>
+        <v>-1216.839531126826</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-1353.296691126826</v>
+        <v>-1216.839531126826</v>
       </c>
       <c r="Q58">
-        <v>-1342.296691126826</v>
+        <v>-1205.839531126826</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1143972521774572</v>
+        <v>0.1143691577915326</v>
       </c>
       <c r="T58">
         <v>1.255868205445489</v>
       </c>
       <c r="U58">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V58">
         <v>0</v>
       </c>
       <c r="W58">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6334,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3364266383399188</v>
+        <v>0.3605511860802759</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6345,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1776600213076969</v>
+        <v>0.16909765977789</v>
       </c>
       <c r="C59">
-        <v>-3907.685837961251</v>
+        <v>-3611.932737352921</v>
       </c>
       <c r="D59">
-        <v>4283.00716203875</v>
+        <v>4578.76026264708</v>
       </c>
       <c r="E59">
         <v>2834.193000000001</v>
@@ -6125,37 +6378,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M59">
-        <v>2075.825798706472</v>
+        <v>1936.931903706472</v>
       </c>
       <c r="N59">
-        <v>-1389.714687595361</v>
+        <v>-1250.820792595361</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-1389.714687595361</v>
+        <v>-1250.820792595361</v>
       </c>
       <c r="Q59">
-        <v>-1378.714687595361</v>
+        <v>-1239.820792595361</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1159925371118167</v>
+        <v>0.1159637893680799</v>
       </c>
       <c r="T59">
         <v>1.285074442781431</v>
       </c>
       <c r="U59">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V59">
         <v>0</v>
       </c>
       <c r="W59">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6416,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.330524416614657</v>
+        <v>0.3542257266753588</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6427,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1794438323664621</v>
+        <v>0.1707314708366552</v>
       </c>
       <c r="C60">
-        <v>-4127.092073614653</v>
+        <v>-3834.020054860111</v>
       </c>
       <c r="D60">
-        <v>4226.049926385346</v>
+        <v>4519.121945139887</v>
       </c>
       <c r="E60">
         <v>2996.642</v>
@@ -6207,37 +6460,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M60">
-        <v>2112.243795175006</v>
+        <v>1970.913165175006</v>
       </c>
       <c r="N60">
-        <v>-1426.132684063895</v>
+        <v>-1284.802054063895</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-1426.132684063895</v>
+        <v>-1284.802054063895</v>
       </c>
       <c r="Q60">
-        <v>-1415.132684063895</v>
+        <v>-1273.802054063895</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1176637879954314</v>
+        <v>0.1176343557816055</v>
       </c>
       <c r="T60">
         <v>1.315671453323845</v>
       </c>
       <c r="U60">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6498,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3248257197764733</v>
+        <v>0.3481183865602665</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6509,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1812276434252272</v>
+        <v>0.1723652818954204</v>
       </c>
       <c r="C61">
-        <v>-4345.003307744544</v>
+        <v>-4054.573770261482</v>
       </c>
       <c r="D61">
-        <v>4170.587692255456</v>
+        <v>4461.017229738518</v>
       </c>
       <c r="E61">
         <v>3159.091</v>
@@ -6289,37 +6542,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M61">
-        <v>2148.661791643541</v>
+        <v>2004.894426643541</v>
       </c>
       <c r="N61">
-        <v>-1462.55068053243</v>
+        <v>-1318.78331553243</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-1462.55068053243</v>
+        <v>-1318.78331553243</v>
       </c>
       <c r="Q61">
-        <v>-1451.55068053243</v>
+        <v>-1307.78331553243</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1194165633123931</v>
+        <v>0.1193864132396935</v>
       </c>
       <c r="T61">
         <v>1.34776100096589</v>
       </c>
       <c r="U61">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V61">
         <v>0</v>
       </c>
       <c r="W61">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6580,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3193201991022958</v>
+        <v>0.3422180749236517</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6591,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1830114544839924</v>
+        <v>0.1739990929541856</v>
       </c>
       <c r="C62">
-        <v>-4561.477638603175</v>
+        <v>-4273.652287599803</v>
       </c>
       <c r="D62">
-        <v>4116.562361396823</v>
+        <v>4404.387712400196</v>
       </c>
       <c r="E62">
         <v>3321.539999999999</v>
@@ -6371,37 +6624,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M62">
-        <v>2185.079788112075</v>
+        <v>2038.875688112075</v>
       </c>
       <c r="N62">
-        <v>-1498.968677000964</v>
+        <v>-1352.764577000964</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-1498.968677000964</v>
+        <v>-1352.764577000964</v>
       </c>
       <c r="Q62">
-        <v>-1487.968677000964</v>
+        <v>-1341.764577000964</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1212569773952029</v>
+        <v>0.1212260735706858</v>
       </c>
       <c r="T62">
         <v>1.381455025990038</v>
       </c>
       <c r="U62">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6662,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3139981957839242</v>
+        <v>0.3365144403415909</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6673,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1847952655427576</v>
+        <v>0.1756329040129507</v>
       </c>
       <c r="C63">
-        <v>-4776.570192547137</v>
+        <v>-4491.311082496994</v>
       </c>
       <c r="D63">
-        <v>4063.918807452862</v>
+        <v>4349.177917503005</v>
       </c>
       <c r="E63">
         <v>3483.989</v>
@@ -6453,37 +6706,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M63">
-        <v>2221.49778458061</v>
+        <v>2072.85694958061</v>
       </c>
       <c r="N63">
-        <v>-1535.386673469499</v>
+        <v>-1386.745838469499</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-1535.386673469499</v>
+        <v>-1386.745838469499</v>
       </c>
       <c r="Q63">
-        <v>-1524.386673469499</v>
+        <v>-1375.745838469499</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1231917716873876</v>
+        <v>0.1231600754571137</v>
       </c>
       <c r="T63">
         <v>1.416876949733372</v>
       </c>
       <c r="U63">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V63">
         <v>0</v>
       </c>
       <c r="W63">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6744,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3088506843776303</v>
+        <v>0.3309978101720567</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6755,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1865790766015228</v>
+        <v>0.1772667150717159</v>
       </c>
       <c r="C64">
-        <v>-4990.333311664358</v>
+        <v>-4707.602883423269</v>
       </c>
       <c r="D64">
-        <v>4012.604688335642</v>
+        <v>4295.33511657673</v>
       </c>
       <c r="E64">
         <v>3646.438</v>
@@ -6535,37 +6788,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M64">
-        <v>2257.915781049145</v>
+        <v>2106.838211049144</v>
       </c>
       <c r="N64">
-        <v>-1571.804669938034</v>
+        <v>-1420.727099938033</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-1571.804669938034</v>
+        <v>-1420.727099938033</v>
       </c>
       <c r="Q64">
-        <v>-1560.804669938034</v>
+        <v>-1409.727099938033</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1252283972581084</v>
+        <v>0.1251958669165114</v>
       </c>
       <c r="T64">
         <v>1.454163185252671</v>
       </c>
       <c r="U64">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6826,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3038692217263782</v>
+        <v>0.3256591358144428</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6837,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.188362887660288</v>
+        <v>0.1789005261304811</v>
       </c>
       <c r="C65">
-        <v>-5202.816727363687</v>
+        <v>-4922.577839666325</v>
       </c>
       <c r="D65">
-        <v>3962.570272636313</v>
+        <v>4242.809160333675</v>
       </c>
       <c r="E65">
         <v>3808.887000000001</v>
@@ -6617,37 +6870,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M65">
-        <v>2294.333777517679</v>
+        <v>2140.819472517679</v>
       </c>
       <c r="N65">
-        <v>-1608.222666406568</v>
+        <v>-1454.708361406568</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-1608.222666406568</v>
+        <v>-1454.708361406568</v>
       </c>
       <c r="Q65">
-        <v>-1597.222666406568</v>
+        <v>-1443.708361406568</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1273751106975167</v>
+        <v>0.1273417011574982</v>
       </c>
       <c r="T65">
         <v>1.493464892962203</v>
       </c>
       <c r="U65">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V65">
         <v>0</v>
       </c>
       <c r="W65">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6908,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2990459007465944</v>
+        <v>0.3204899431824675</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6919,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1901466987190532</v>
+        <v>0.1805343371892463</v>
       </c>
       <c r="C66">
-        <v>-5414.06772113714</v>
+        <v>-5136.283677125206</v>
       </c>
       <c r="D66">
-        <v>3913.768278862861</v>
+        <v>4191.552322874794</v>
       </c>
       <c r="E66">
         <v>3971.336000000001</v>
@@ -6699,37 +6952,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M66">
-        <v>2330.751773986214</v>
+        <v>2174.800733986214</v>
       </c>
       <c r="N66">
-        <v>-1644.640662875103</v>
+        <v>-1488.689622875103</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-1644.640662875103</v>
+        <v>-1488.689622875103</v>
       </c>
       <c r="Q66">
-        <v>-1633.640662875103</v>
+        <v>-1477.689622875103</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1296410859946699</v>
+        <v>0.1296067484118731</v>
       </c>
       <c r="T66">
         <v>1.53495002887782</v>
       </c>
       <c r="U66">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6990,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2943733085474289</v>
+        <v>0.3154822878202415</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +7001,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1919305097778184</v>
+        <v>0.1821681482480115</v>
       </c>
       <c r="C67">
-        <v>-5624.131273587225</v>
+        <v>-5348.765842946234</v>
       </c>
       <c r="D67">
-        <v>3866.153726412775</v>
+        <v>4141.519157053766</v>
       </c>
       <c r="E67">
         <v>4133.785</v>
@@ -6781,37 +7034,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M67">
-        <v>2367.169770454748</v>
+        <v>2208.781995454748</v>
       </c>
       <c r="N67">
-        <v>-1681.058659343637</v>
+        <v>-1522.670884343637</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-1681.058659343637</v>
+        <v>-1522.670884343637</v>
       </c>
       <c r="Q67">
-        <v>-1670.058659343637</v>
+        <v>-1511.670884343637</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1320365455945177</v>
+        <v>0.1320012269379267</v>
       </c>
       <c r="T67">
         <v>1.578805743988615</v>
       </c>
       <c r="U67">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V67">
         <v>0</v>
       </c>
       <c r="W67">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +7072,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.28984448841593</v>
+        <v>0.3106287141614685</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +7083,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1937143208365835</v>
+        <v>0.1838019593067767</v>
       </c>
       <c r="C68">
-        <v>-5833.050202706741</v>
+        <v>-5560.067639922285</v>
       </c>
       <c r="D68">
-        <v>3819.683797293259</v>
+        <v>4092.666360077715</v>
       </c>
       <c r="E68">
         <v>4296.234</v>
@@ -6863,37 +7116,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M68">
-        <v>2403.587766923283</v>
+        <v>2242.763256923283</v>
       </c>
       <c r="N68">
-        <v>-1717.476655812172</v>
+        <v>-1556.652145812172</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-1717.476655812172</v>
+        <v>-1556.652145812172</v>
       </c>
       <c r="Q68">
-        <v>-1706.476655812172</v>
+        <v>-1545.652145812172</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1345729145825917</v>
+        <v>0.1345365571419833</v>
       </c>
       <c r="T68">
         <v>1.625241207047103</v>
       </c>
       <c r="U68">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +7154,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2854529052581128</v>
+        <v>0.3059222184923553</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7165,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1954981318953487</v>
+        <v>0.1854357703655419</v>
       </c>
       <c r="C69">
-        <v>-6040.865292304498</v>
+        <v>-5770.230351490854</v>
       </c>
       <c r="D69">
-        <v>3774.317707695502</v>
+        <v>4044.952648509146</v>
       </c>
       <c r="E69">
         <v>4458.683000000001</v>
@@ -6945,37 +7198,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M69">
-        <v>2440.005763391818</v>
+        <v>2276.744518391818</v>
       </c>
       <c r="N69">
-        <v>-1753.894652280707</v>
+        <v>-1590.633407280706</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-1753.894652280707</v>
+        <v>-1590.633407280706</v>
       </c>
       <c r="Q69">
-        <v>-1742.894652280707</v>
+        <v>-1579.633407280706</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1372630029032763</v>
+        <v>0.1372255437220434</v>
       </c>
       <c r="T69">
         <v>1.674490940593985</v>
       </c>
       <c r="U69">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +7236,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2811924141348575</v>
+        <v>0.3013562152312754</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7247,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1972819429541139</v>
+        <v>0.1870695814243071</v>
       </c>
       <c r="C70">
-        <v>-6247.615411386678</v>
+        <v>-5979.293358089228</v>
       </c>
       <c r="D70">
-        <v>3730.016588613324</v>
+        <v>3998.338641910774</v>
       </c>
       <c r="E70">
         <v>4621.132000000001</v>
@@ -7027,37 +7280,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M70">
-        <v>2476.423759860353</v>
+        <v>2310.725779860352</v>
       </c>
       <c r="N70">
-        <v>-1790.312648749242</v>
+        <v>-1624.614668749241</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-1790.312648749242</v>
+        <v>-1624.614668749241</v>
       </c>
       <c r="Q70">
-        <v>-1779.312648749242</v>
+        <v>-1613.614668749241</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1401212217440037</v>
+        <v>0.1400825919633573</v>
       </c>
       <c r="T70">
         <v>1.726818782487547</v>
       </c>
       <c r="U70">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7318,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2770572315740507</v>
+        <v>0.2969245061837567</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7329,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1990657540128791</v>
+        <v>0.1887033924830723</v>
       </c>
       <c r="C71">
-        <v>-6453.337625228263</v>
+        <v>-6187.294245556071</v>
       </c>
       <c r="D71">
-        <v>3686.743374771738</v>
+        <v>3952.78675444393</v>
       </c>
       <c r="E71">
         <v>4783.581000000002</v>
@@ -7109,37 +7362,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M71">
-        <v>2512.841756328887</v>
+        <v>2344.707041328887</v>
       </c>
       <c r="N71">
-        <v>-1826.730645217776</v>
+        <v>-1658.595930217776</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-1826.730645217776</v>
+        <v>-1658.595930217776</v>
       </c>
       <c r="Q71">
-        <v>-1815.730645217776</v>
+        <v>-1647.595930217776</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1431638418002619</v>
+        <v>0.1431239658976592</v>
       </c>
       <c r="T71">
         <v>1.782522614180694</v>
       </c>
       <c r="U71">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V71">
         <v>0</v>
       </c>
       <c r="W71">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7400,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2730419093773253</v>
+        <v>0.2926212524709486</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7411,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2008495650716443</v>
+        <v>0.1903372035418374</v>
       </c>
       <c r="C72">
-        <v>-6658.067298801692</v>
+        <v>-6394.268906206577</v>
       </c>
       <c r="D72">
-        <v>3644.462701198308</v>
+        <v>3908.261093793423</v>
       </c>
       <c r="E72">
         <v>4946.030000000001</v>
@@ -7191,37 +7444,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M72">
-        <v>2549.259752797422</v>
+        <v>2378.688302797421</v>
       </c>
       <c r="N72">
-        <v>-1863.148641686311</v>
+        <v>-1692.57719168631</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-1863.148641686311</v>
+        <v>-1692.57719168631</v>
       </c>
       <c r="Q72">
-        <v>-1852.148641686311</v>
+        <v>-1681.57719168631</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.146409303193604</v>
+        <v>0.1463680980942478</v>
       </c>
       <c r="T72">
         <v>1.841940034653384</v>
       </c>
       <c r="U72">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V72">
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7482,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.269141310671935</v>
+        <v>0.2884409488642208</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7493,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2026333761304095</v>
+        <v>0.1919710146006026</v>
       </c>
       <c r="C73">
-        <v>-6861.838193169275</v>
+        <v>-6600.251633152386</v>
       </c>
       <c r="D73">
-        <v>3603.140806830724</v>
+        <v>3864.727366847613</v>
       </c>
       <c r="E73">
         <v>5108.478999999999</v>
@@ -7273,37 +7526,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M73">
-        <v>2585.677749265956</v>
+        <v>2412.669564265956</v>
       </c>
       <c r="N73">
-        <v>-1899.566638154845</v>
+        <v>-1726.558453154845</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-1899.566638154845</v>
+        <v>-1726.558453154845</v>
       </c>
       <c r="Q73">
-        <v>-1888.566638154845</v>
+        <v>-1715.558453154845</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1498785895106247</v>
+        <v>0.1498359635457736</v>
       </c>
       <c r="T73">
         <v>1.905455208262121</v>
       </c>
       <c r="U73">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7564,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2653505879864149</v>
+        <v>0.2843784002886683</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7575,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2044171871891747</v>
+        <v>0.1936048256593678</v>
       </c>
       <c r="C74">
-        <v>-7064.682555391614</v>
+        <v>-6805.27520838726</v>
       </c>
       <c r="D74">
-        <v>3562.745444608385</v>
+        <v>3822.152791612739</v>
       </c>
       <c r="E74">
         <v>5270.928</v>
@@ -7355,37 +7608,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M74">
-        <v>2622.095745734491</v>
+        <v>2446.65082573449</v>
       </c>
       <c r="N74">
-        <v>-1935.98463462338</v>
+        <v>-1760.539714623379</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-1935.98463462338</v>
+        <v>-1760.539714623379</v>
       </c>
       <c r="Q74">
-        <v>-1924.98463462338</v>
+        <v>-1749.539714623379</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1535956819931471</v>
+        <v>0.1535515336724083</v>
       </c>
       <c r="T74">
         <v>1.973507179985768</v>
       </c>
       <c r="U74">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V74">
         <v>0</v>
       </c>
       <c r="W74">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7646,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2616651631532702</v>
+        <v>0.280428700284659</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7657,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2062009982479399</v>
+        <v>0.195238636718133</v>
       </c>
       <c r="C75">
-        <v>-7266.631202455181</v>
+        <v>-7009.370985113959</v>
       </c>
       <c r="D75">
-        <v>3523.245797544819</v>
+        <v>3780.506014886041</v>
       </c>
       <c r="E75">
         <v>5433.377</v>
@@ -7437,37 +7690,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M75">
-        <v>2658.513742203025</v>
+        <v>2480.632087203025</v>
       </c>
       <c r="N75">
-        <v>-1972.402631091914</v>
+        <v>-1794.520976091914</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-1972.402631091914</v>
+        <v>-1794.520976091914</v>
       </c>
       <c r="Q75">
-        <v>-1961.402631091914</v>
+        <v>-1783.520976091914</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1575881146595599</v>
+        <v>0.1575423312158309</v>
       </c>
       <c r="T75">
         <v>2.046600038503759</v>
       </c>
       <c r="U75">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7728,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2580807088634993</v>
+        <v>0.2765872112396638</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7739,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.207984809306705</v>
+        <v>0.1968724477768982</v>
       </c>
       <c r="C76">
-        <v>-7467.713599678196</v>
+        <v>-7212.568964746863</v>
       </c>
       <c r="D76">
-        <v>3484.612400321803</v>
+        <v>3739.757035253136</v>
       </c>
       <c r="E76">
         <v>5595.825999999999</v>
@@ -7519,37 +7772,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M76">
-        <v>2694.93173867156</v>
+        <v>2514.613348671559</v>
       </c>
       <c r="N76">
-        <v>-2008.820627560449</v>
+        <v>-1828.502237560448</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-2008.820627560449</v>
+        <v>-1828.502237560448</v>
       </c>
       <c r="Q76">
-        <v>-1997.820627560449</v>
+        <v>-1817.502237560448</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1618876575310814</v>
+        <v>0.1618401131856705</v>
       </c>
       <c r="T76">
         <v>2.125315424600058</v>
       </c>
       <c r="U76">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V76">
         <v>0</v>
       </c>
       <c r="W76">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7810,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2545931317166953</v>
+        <v>0.2728495462229116</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7821,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2097686203654702</v>
+        <v>0.1985062588356634</v>
       </c>
       <c r="C77">
-        <v>-7667.957934013966</v>
+        <v>-7414.897868987782</v>
       </c>
       <c r="D77">
-        <v>3446.817065986033</v>
+        <v>3699.877131012217</v>
       </c>
       <c r="E77">
         <v>5758.275</v>
@@ -7601,37 +7854,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M77">
-        <v>2731.349735140094</v>
+        <v>2548.594610140094</v>
       </c>
       <c r="N77">
-        <v>-2045.238624028983</v>
+        <v>-1862.483499028983</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-2045.238624028983</v>
+        <v>-1862.483499028983</v>
       </c>
       <c r="Q77">
-        <v>-2034.238624028983</v>
+        <v>-1851.483499028983</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1665311638323247</v>
+        <v>0.1664817177130973</v>
       </c>
       <c r="T77">
         <v>2.21032804158406</v>
       </c>
       <c r="U77">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7892,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2511985566271394</v>
+        <v>0.2692115522732728</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7903,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2115524314242354</v>
+        <v>0.2001400698944286</v>
       </c>
       <c r="C78">
-        <v>-7867.391182634989</v>
+        <v>-7616.385207338788</v>
       </c>
       <c r="D78">
-        <v>3409.832817365011</v>
+        <v>3660.838792661211</v>
       </c>
       <c r="E78">
         <v>5920.724</v>
@@ -7683,37 +7936,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M78">
-        <v>2767.767731608629</v>
+        <v>2582.575871608629</v>
       </c>
       <c r="N78">
-        <v>-2081.656620497518</v>
+        <v>-1896.464760497518</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-2081.656620497518</v>
+        <v>-1896.464760497518</v>
       </c>
       <c r="Q78">
-        <v>-2070.656620497518</v>
+        <v>-1885.464760497518</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1715616289920049</v>
+        <v>0.1715101226178097</v>
       </c>
       <c r="T78">
         <v>2.30242504331673</v>
       </c>
       <c r="U78">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V78">
         <v>0</v>
       </c>
       <c r="W78">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7974,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2478933124609928</v>
+        <v>0.2656692950065191</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7985,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2133362424830006</v>
+        <v>0.2017738809531938</v>
       </c>
       <c r="C79">
-        <v>-8066.039177148476</v>
+        <v>-7817.057340385641</v>
       </c>
       <c r="D79">
-        <v>3373.633822851525</v>
+        <v>3622.61565961436</v>
       </c>
       <c r="E79">
         <v>6083.173000000001</v>
@@ -7765,37 +8018,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M79">
-        <v>2804.185728077164</v>
+        <v>2616.557133077164</v>
       </c>
       <c r="N79">
-        <v>-2118.074616966052</v>
+        <v>-1930.446021966053</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-2118.074616966052</v>
+        <v>-1930.446021966053</v>
       </c>
       <c r="Q79">
-        <v>-2107.074616966052</v>
+        <v>-1919.446021966053</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1770295259047008</v>
+        <v>0.1769757801229319</v>
       </c>
       <c r="T79">
         <v>2.402530479982674</v>
       </c>
       <c r="U79">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V79">
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +8056,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2446739187926683</v>
+        <v>0.2622190444220188</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +8067,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2151200535417658</v>
+        <v>0.2034076920119589</v>
       </c>
       <c r="C80">
-        <v>-8263.92666376458</v>
+        <v>-8016.939539157662</v>
       </c>
       <c r="D80">
-        <v>3338.195336235421</v>
+        <v>3585.182460842339</v>
       </c>
       <c r="E80">
         <v>6245.622000000001</v>
@@ -7847,37 +8100,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M80">
-        <v>2840.603724545698</v>
+        <v>2650.538394545698</v>
       </c>
       <c r="N80">
-        <v>-2154.492613434587</v>
+        <v>-1964.427283434587</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-2154.492613434587</v>
+        <v>-1964.427283434587</v>
       </c>
       <c r="Q80">
-        <v>-2143.492613434587</v>
+        <v>-1953.427283434587</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1829945043549145</v>
+        <v>0.1829383155830651</v>
       </c>
       <c r="T80">
         <v>2.511736410890978</v>
       </c>
       <c r="U80">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +8138,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2415370736799418</v>
+        <v>0.2588572618012237</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8149,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.216903864600531</v>
+        <v>0.2050415030707241</v>
       </c>
       <c r="C81">
-        <v>-8461.077359711764</v>
+        <v>-8216.056040845013</v>
       </c>
       <c r="D81">
-        <v>3303.493640288235</v>
+        <v>3548.514959154987</v>
       </c>
       <c r="E81">
         <v>6408.071</v>
@@ -7929,37 +8182,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M81">
-        <v>2877.021721014233</v>
+        <v>2684.519656014233</v>
       </c>
       <c r="N81">
-        <v>-2190.910609903121</v>
+        <v>-1998.408544903122</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-2190.910609903121</v>
+        <v>-1998.408544903122</v>
       </c>
       <c r="Q81">
-        <v>-2179.910609903121</v>
+        <v>-1987.408544903122</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1895275759908628</v>
+        <v>0.1894687115632111</v>
       </c>
       <c r="T81">
         <v>2.631342906647691</v>
       </c>
       <c r="U81">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8220,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2384796423675375</v>
+        <v>0.2555805876012083</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8231,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2186876756592962</v>
+        <v>0.2066753141294893</v>
       </c>
       <c r="C82">
-        <v>-8657.514006169671</v>
+        <v>-8414.430101131478</v>
       </c>
       <c r="D82">
-        <v>3269.505993830329</v>
+        <v>3512.589898868522</v>
       </c>
       <c r="E82">
         <v>6570.52</v>
@@ -8011,37 +8264,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M82">
-        <v>2913.439717482767</v>
+        <v>2718.500917482767</v>
       </c>
       <c r="N82">
-        <v>-2227.328606371656</v>
+        <v>-2032.389806371656</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-2227.328606371656</v>
+        <v>-2032.389806371656</v>
       </c>
       <c r="Q82">
-        <v>-2216.328606371656</v>
+        <v>-2021.389806371656</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1967139547904059</v>
+        <v>0.1966521471413717</v>
       </c>
       <c r="T82">
         <v>2.762910051980076</v>
       </c>
       <c r="U82">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V82">
         <v>0</v>
       </c>
       <c r="W82">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8302,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2354986468379432</v>
+        <v>0.2523858302561932</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8313,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2204714867180614</v>
+        <v>0.2083091251882545</v>
       </c>
       <c r="C83">
-        <v>-8853.258417967663</v>
+        <v>-8612.084043380211</v>
       </c>
       <c r="D83">
-        <v>3236.210582032336</v>
+        <v>3477.38495661979</v>
       </c>
       <c r="E83">
         <v>6732.969000000001</v>
@@ -8093,37 +8346,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M83">
-        <v>2949.857713951302</v>
+        <v>2752.482178951302</v>
       </c>
       <c r="N83">
-        <v>-2263.746602840191</v>
+        <v>-2066.371067840191</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-2263.746602840191</v>
+        <v>-2066.371067840191</v>
       </c>
       <c r="Q83">
-        <v>-2252.746602840191</v>
+        <v>-2055.371067840191</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2046567945162168</v>
+        <v>0.2045917338330228</v>
       </c>
       <c r="T83">
         <v>2.908326370505343</v>
       </c>
       <c r="U83">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V83">
         <v>0</v>
       </c>
       <c r="W83">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8384,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2325912561362401</v>
+        <v>0.2492699558085857</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8395,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2222552977768266</v>
+        <v>0.2099429362470197</v>
       </c>
       <c r="C84">
-        <v>-9048.331530277346</v>
+        <v>-8809.039304891052</v>
       </c>
       <c r="D84">
-        <v>3203.586469722655</v>
+        <v>3442.878695108948</v>
       </c>
       <c r="E84">
         <v>6895.418000000001</v>
@@ -8175,37 +8428,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M84">
-        <v>2986.275710419837</v>
+        <v>2786.463440419837</v>
       </c>
       <c r="N84">
-        <v>-2300.164599308726</v>
+        <v>-2100.352329308726</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-2300.164599308726</v>
+        <v>-2100.352329308726</v>
       </c>
       <c r="Q84">
-        <v>-2289.164599308726</v>
+        <v>-2089.352329308726</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2134821719893399</v>
+        <v>0.2134134968237464</v>
       </c>
       <c r="T84">
         <v>3.06990005775564</v>
       </c>
       <c r="U84">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V84">
         <v>0</v>
       </c>
       <c r="W84">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8466,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2297547774028713</v>
+        <v>0.2462300782987251</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8477,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2240391088355917</v>
+        <v>0.2115767473057849</v>
       </c>
       <c r="C85">
-        <v>-9242.753442509009</v>
+        <v>-9005.316480430833</v>
       </c>
       <c r="D85">
-        <v>3171.613557490993</v>
+        <v>3409.050519569168</v>
       </c>
       <c r="E85">
         <v>7057.867000000002</v>
@@ -8257,37 +8510,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M85">
-        <v>3022.693706888372</v>
+        <v>2820.444701888371</v>
       </c>
       <c r="N85">
-        <v>-2336.58259577726</v>
+        <v>-2134.33359077726</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-2336.58259577726</v>
+        <v>-2134.33359077726</v>
       </c>
       <c r="Q85">
-        <v>-2325.58259577726</v>
+        <v>-2123.33359077726</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2233458291651835</v>
+        <v>0.2232731142839667</v>
       </c>
       <c r="T85">
         <v>3.250482414094208</v>
       </c>
       <c r="U85">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V85">
         <v>0</v>
       </c>
       <c r="W85">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8548,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.226986647554644</v>
+        <v>0.2432634508493429</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8559,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2258229198943569</v>
+        <v>0.2132105583645501</v>
       </c>
       <c r="C86">
-        <v>-9436.543459605453</v>
+        <v>-9200.935363222372</v>
       </c>
       <c r="D86">
-        <v>3140.272540394545</v>
+        <v>3375.880636777626</v>
       </c>
       <c r="E86">
         <v>7220.315999999999</v>
@@ -8339,37 +8592,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M86">
-        <v>3059.111703356905</v>
+        <v>2854.425963356905</v>
       </c>
       <c r="N86">
-        <v>-2373.000592245794</v>
+        <v>-2168.314852245794</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-2373.000592245794</v>
+        <v>-2168.314852245794</v>
       </c>
       <c r="Q86">
-        <v>-2362.000592245794</v>
+        <v>-2157.314852245794</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2344424434880074</v>
+        <v>0.2343651839267146</v>
       </c>
       <c r="T86">
         <v>3.453637564975094</v>
       </c>
       <c r="U86">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8630,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.224284425559946</v>
+        <v>0.2403674573868507</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8641,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2276067309531221</v>
+        <v>0.2148443694233153</v>
       </c>
       <c r="C87">
-        <v>-9629.720130911468</v>
+        <v>-9395.914983563636</v>
       </c>
       <c r="D87">
-        <v>3109.544869088531</v>
+        <v>3343.350016436363</v>
       </c>
       <c r="E87">
         <v>7382.764999999999</v>
@@ -8421,37 +8674,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M87">
-        <v>3095.52969982544</v>
+        <v>2888.40722482544</v>
       </c>
       <c r="N87">
-        <v>-2409.418588714329</v>
+        <v>-2202.296113714329</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-2409.418588714329</v>
+        <v>-2202.296113714329</v>
       </c>
       <c r="Q87">
-        <v>-2398.418588714329</v>
+        <v>-2191.296113714329</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2470186063872079</v>
+        <v>0.2469361961884955</v>
       </c>
       <c r="T87">
         <v>3.683880069306767</v>
       </c>
       <c r="U87">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V87">
         <v>0</v>
       </c>
       <c r="W87">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8712,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2216457852592405</v>
+        <v>0.2375396049470052</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8723,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2293905420118873</v>
+        <v>0.2164781804820804</v>
       </c>
       <c r="C88">
-        <v>-9822.301286783324</v>
+        <v>-9590.273645235329</v>
       </c>
       <c r="D88">
-        <v>3079.412713216675</v>
+        <v>3311.440354764671</v>
       </c>
       <c r="E88">
         <v>7545.214</v>
@@ -8503,37 +8756,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M88">
-        <v>3131.947696293975</v>
+        <v>2922.388486293975</v>
       </c>
       <c r="N88">
-        <v>-2445.836585182864</v>
+        <v>-2236.277375182864</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-2445.836585182864</v>
+        <v>-2236.277375182864</v>
       </c>
       <c r="Q88">
-        <v>-2434.836585182864</v>
+        <v>-2225.277375182864</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2613913639862941</v>
+        <v>0.2613030673448166</v>
       </c>
       <c r="T88">
         <v>3.947014359971536</v>
       </c>
       <c r="U88">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V88">
         <v>0</v>
       </c>
       <c r="W88">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8794,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2190685086864587</v>
+        <v>0.2347775165173891</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8805,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2311743530706525</v>
+        <v>0.2181119915408456</v>
       </c>
       <c r="C89">
-        <v>-10014.30407309024</v>
+        <v>-9784.028959843323</v>
       </c>
       <c r="D89">
-        <v>3049.858926909755</v>
+        <v>3280.134040156676</v>
       </c>
       <c r="E89">
         <v>7707.663</v>
@@ -8585,37 +8838,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M89">
-        <v>3168.36569276251</v>
+        <v>2956.369747762509</v>
       </c>
       <c r="N89">
-        <v>-2482.254581651398</v>
+        <v>-2270.258636651398</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-2482.254581651398</v>
+        <v>-2270.258636651398</v>
       </c>
       <c r="Q89">
-        <v>-2471.254581651398</v>
+        <v>-2259.258636651398</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2779753150621629</v>
+        <v>0.277880226371341</v>
       </c>
       <c r="T89">
         <v>4.250630849200116</v>
       </c>
       <c r="U89">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V89">
         <v>0</v>
       </c>
       <c r="W89">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8876,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2165504798509823</v>
+        <v>0.2320789243735111</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8887,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2329581641294177</v>
+        <v>0.2197458025996108</v>
       </c>
       <c r="C90">
-        <v>-10205.744983748</v>
+        <v>-9977.197879231295</v>
       </c>
       <c r="D90">
-        <v>3020.867016252</v>
+        <v>3249.414120768706</v>
       </c>
       <c r="E90">
         <v>7870.112000000001</v>
@@ -8667,37 +8920,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M90">
-        <v>3204.783689231044</v>
+        <v>2990.351009231044</v>
       </c>
       <c r="N90">
-        <v>-2518.672578119933</v>
+        <v>-2304.239898119933</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-2518.672578119933</v>
+        <v>-2304.239898119933</v>
       </c>
       <c r="Q90">
-        <v>-2507.672578119933</v>
+        <v>-2293.239898119933</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2973232579840099</v>
+        <v>0.2972202452356195</v>
       </c>
       <c r="T90">
         <v>4.604850086633459</v>
       </c>
       <c r="U90">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8958,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2140896789435848</v>
+        <v>0.2294416638692665</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8969,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2347419751881828</v>
+        <v>0.221379613658376</v>
       </c>
       <c r="C91">
-        <v>-10396.63989141442</v>
+        <v>-10169.79672608889</v>
       </c>
       <c r="D91">
-        <v>2992.421108585577</v>
+        <v>3219.264273911106</v>
       </c>
       <c r="E91">
         <v>8032.561</v>
@@ -8749,37 +9002,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M91">
-        <v>3241.201685699579</v>
+        <v>3024.332270699578</v>
       </c>
       <c r="N91">
-        <v>-2555.090574588467</v>
+        <v>-2338.221159588467</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-2555.090574588467</v>
+        <v>-2338.221159588467</v>
       </c>
       <c r="Q91">
-        <v>-2544.090574588467</v>
+        <v>-2327.221159588467</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3201890087098289</v>
+        <v>0.3200766311661303</v>
       </c>
       <c r="T91">
         <v>5.023472821781955</v>
       </c>
       <c r="U91">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V91">
         <v>0</v>
       </c>
       <c r="W91">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +9040,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2116841769329827</v>
+        <v>0.2268636676460163</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +9051,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2365257862469481</v>
+        <v>0.2230134247171412</v>
       </c>
       <c r="C92">
-        <v>-10587.00407646683</v>
+        <v>-10361.8412228716</v>
       </c>
       <c r="D92">
-        <v>2964.505923533168</v>
+        <v>3189.6687771284</v>
       </c>
       <c r="E92">
         <v>8195.01</v>
@@ -8831,37 +9084,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M92">
-        <v>3277.619682168113</v>
+        <v>3058.313532168113</v>
       </c>
       <c r="N92">
-        <v>-2591.508571057002</v>
+        <v>-2372.202421057002</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-2591.508571057002</v>
+        <v>-2372.202421057002</v>
       </c>
       <c r="Q92">
-        <v>-2580.508571057002</v>
+        <v>-2361.202421057002</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3476279095808119</v>
+        <v>0.3475042942827434</v>
       </c>
       <c r="T92">
         <v>5.525820103960152</v>
       </c>
       <c r="U92">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V92">
         <v>0</v>
       </c>
       <c r="W92">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +9122,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2093321305226162</v>
+        <v>0.2243429602277274</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9133,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2383095973057132</v>
+        <v>0.2246472357759064</v>
       </c>
       <c r="C93">
-        <v>-10776.85225437252</v>
+        <v>-10553.34651913989</v>
       </c>
       <c r="D93">
-        <v>2937.106745627482</v>
+        <v>3160.612480860112</v>
       </c>
       <c r="E93">
         <v>8357.459000000001</v>
@@ -8913,37 +9166,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M93">
-        <v>3314.037678636648</v>
+        <v>3092.294793636648</v>
       </c>
       <c r="N93">
-        <v>-2627.926567525536</v>
+        <v>-2406.183682525537</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-2627.926567525536</v>
+        <v>-2406.183682525537</v>
       </c>
       <c r="Q93">
-        <v>-2616.926567525536</v>
+        <v>-2395.183682525537</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3811643439786799</v>
+        <v>0.3810269936474927</v>
       </c>
       <c r="T93">
         <v>6.139800115511281</v>
       </c>
       <c r="U93">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V93">
         <v>0</v>
       </c>
       <c r="W93">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9204,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.20703177743995</v>
+        <v>0.2218776529724774</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9215,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2400934083644784</v>
+        <v>0.2262810468346716</v>
       </c>
       <c r="C94">
-        <v>-10966.19860155534</v>
+        <v>-10744.32721741762</v>
       </c>
       <c r="D94">
-        <v>2910.209398444666</v>
+        <v>3132.080782582384</v>
       </c>
       <c r="E94">
         <v>8519.908000000001</v>
@@ -8995,37 +9248,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M94">
-        <v>3350.455675105183</v>
+        <v>3126.276055105182</v>
       </c>
       <c r="N94">
-        <v>-2664.344563994072</v>
+        <v>-2440.164943994071</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-2664.344563994072</v>
+        <v>-2440.164943994071</v>
       </c>
       <c r="Q94">
-        <v>-2653.344563994072</v>
+        <v>-2429.164943994071</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.423084886976015</v>
+        <v>0.4229303678534294</v>
       </c>
       <c r="T94">
         <v>6.907275129950192</v>
       </c>
       <c r="U94">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V94">
         <v>0</v>
       </c>
       <c r="W94">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9286,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2047814320329939</v>
+        <v>0.2194659393532116</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9297,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2418772194232436</v>
+        <v>0.2279148578934367</v>
       </c>
       <c r="C95">
-        <v>-11155.05677985388</v>
+        <v>-10934.79739766237</v>
       </c>
       <c r="D95">
-        <v>2883.800220146116</v>
+        <v>3104.059602337633</v>
       </c>
       <c r="E95">
         <v>8682.357</v>
@@ -9077,37 +9330,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M95">
-        <v>3386.873671573717</v>
+        <v>3160.257316573717</v>
       </c>
       <c r="N95">
-        <v>-2700.762560462606</v>
+        <v>-2474.146205462605</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-2700.762560462606</v>
+        <v>-2474.146205462605</v>
       </c>
       <c r="Q95">
-        <v>-2689.762560462606</v>
+        <v>-2463.146205462605</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4769827279725886</v>
+        <v>0.4768061346896336</v>
       </c>
       <c r="T95">
         <v>7.894028719943078</v>
       </c>
       <c r="U95">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V95">
         <v>0</v>
       </c>
       <c r="W95">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9368,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2025794811509189</v>
+        <v>0.2171060905429619</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9379,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2436610304820088</v>
+        <v>0.2295486689522019</v>
       </c>
       <c r="C96">
-        <v>-11343.43995966</v>
+        <v>-11124.77064043387</v>
       </c>
       <c r="D96">
-        <v>2857.86604034</v>
+        <v>3076.535359566132</v>
       </c>
       <c r="E96">
         <v>8844.806</v>
@@ -9159,37 +9412,37 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M96">
-        <v>3423.291668042252</v>
+        <v>3194.238578042251</v>
       </c>
       <c r="N96">
-        <v>-2737.180556931141</v>
+        <v>-2508.127466931141</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-2737.180556931141</v>
+        <v>-2508.127466931141</v>
       </c>
       <c r="Q96">
-        <v>-2726.180556931141</v>
+        <v>-2497.127466931141</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.54884651596802</v>
+        <v>0.5486404904712392</v>
       </c>
       <c r="T96">
         <v>9.209700173266926</v>
       </c>
       <c r="U96">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V96">
         <v>0</v>
       </c>
       <c r="W96">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9450,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2004243802876111</v>
+        <v>0.2147964512818664</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9461,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.273944841540774</v>
+        <v>0.2311824800109671</v>
       </c>
       <c r="C97">
-        <v>-11884.42206864531</v>
+        <v>-11314.26004884064</v>
       </c>
       <c r="D97">
-        <v>2479.332931354687</v>
+        <v>3049.49495115936</v>
       </c>
       <c r="E97">
         <v>9007.255000000001</v>
@@ -9241,45 +9494,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M97">
-        <v>3922.689314510786</v>
+        <v>3228.219839510786</v>
       </c>
       <c r="N97">
-        <v>-3236.578203399675</v>
+        <v>-2542.108728399675</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-3236.578203399675</v>
+        <v>-2542.108728399675</v>
       </c>
       <c r="Q97">
-        <v>-3225.578203399675</v>
+        <v>-2531.108728399675</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6494558191616244</v>
+        <v>0.6492085885654874</v>
       </c>
       <c r="T97">
         <v>11.05164020792032</v>
       </c>
       <c r="U97">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V97">
         <v>0</v>
       </c>
       <c r="W97">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.174908348864911</v>
+        <v>0.2125354360052154</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9543,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2760286525995391</v>
+        <v>0.2328162910697323</v>
       </c>
       <c r="C98">
-        <v>-12069.26366361619</v>
+        <v>-11503.27826933935</v>
       </c>
       <c r="D98">
-        <v>2456.94033638381</v>
+        <v>3022.925730660645</v>
       </c>
       <c r="E98">
         <v>9169.704</v>
@@ -9323,45 +9576,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M98">
-        <v>3963.98078097932</v>
+        <v>3262.20110097932</v>
       </c>
       <c r="N98">
-        <v>-3277.869669868209</v>
+        <v>-2576.089989868209</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-3277.869669868209</v>
+        <v>-2576.089989868209</v>
       </c>
       <c r="Q98">
-        <v>-3266.869669868209</v>
+        <v>-2565.089989868209</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8003697739520288</v>
+        <v>0.8000607357068575</v>
       </c>
       <c r="T98">
         <v>13.81455025990036</v>
       </c>
       <c r="U98">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V98">
         <v>0</v>
       </c>
       <c r="W98">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.1730863868975683</v>
+        <v>0.2103215252134943</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9625,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2781124636583043</v>
+        <v>0.2344501021284975</v>
       </c>
       <c r="C99">
-        <v>-12253.70439262135</v>
+        <v>-11691.83751145627</v>
       </c>
       <c r="D99">
-        <v>2434.948607378647</v>
+        <v>2996.815488543727</v>
       </c>
       <c r="E99">
         <v>9332.153</v>
@@ -9405,45 +9658,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M99">
-        <v>4005.272247447855</v>
+        <v>3296.182362447855</v>
       </c>
       <c r="N99">
-        <v>-3319.161136336744</v>
+        <v>-2610.071251336744</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-3319.161136336744</v>
+        <v>-2610.071251336744</v>
       </c>
       <c r="Q99">
-        <v>-3308.161136336744</v>
+        <v>-2599.071251336744</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.051893031936038</v>
+        <v>1.051480980942477</v>
       </c>
       <c r="T99">
         <v>18.41940034653382</v>
       </c>
       <c r="U99">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V99">
         <v>0</v>
       </c>
       <c r="W99">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.1713019911563561</v>
+        <v>0.2081532620669634</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9707,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2801962747170695</v>
+        <v>0.2360839131872627</v>
       </c>
       <c r="C100">
-        <v>-12437.75492445138</v>
+        <v>-11879.94956649537</v>
       </c>
       <c r="D100">
-        <v>2413.347075548621</v>
+        <v>2971.152433504625</v>
       </c>
       <c r="E100">
         <v>9494.601999999999</v>
@@ -9487,45 +9740,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M100">
-        <v>4046.563713916389</v>
+        <v>3330.163623916389</v>
       </c>
       <c r="N100">
-        <v>-3360.452602805278</v>
+        <v>-2644.052512805279</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-3360.452602805278</v>
+        <v>-2644.052512805279</v>
       </c>
       <c r="Q100">
-        <v>-3349.452602805278</v>
+        <v>-2633.052512805279</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.554939547904058</v>
+        <v>1.554321471413715</v>
       </c>
       <c r="T100">
         <v>27.62910051980073</v>
       </c>
       <c r="U100">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V100">
         <v>0</v>
       </c>
       <c r="W100">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.1695540116547607</v>
+        <v>0.2060292491887291</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9789,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2822800857758347</v>
+        <v>0.2377177242460279</v>
       </c>
       <c r="C101">
-        <v>-12621.42555263526</v>
+        <v>-12067.62582529345</v>
       </c>
       <c r="D101">
-        <v>2392.125447364735</v>
+        <v>2945.925174706546</v>
       </c>
       <c r="E101">
         <v>9657.050999999999</v>
@@ -9569,45 +9822,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M101">
-        <v>4087.855180384924</v>
+        <v>3364.144885384924</v>
       </c>
       <c r="N101">
-        <v>-3401.744069273813</v>
+        <v>-2678.033774273813</v>
       </c>
       <c r="O101">
         <v>-0</v>
       </c>
       <c r="P101">
-        <v>-3401.744069273813</v>
+        <v>-2678.033774273813</v>
       </c>
       <c r="Q101">
-        <v>-3390.744069273813</v>
+        <v>-2667.033774273813</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.064079095808115</v>
+        <v>3.06284294282743</v>
       </c>
       <c r="T101">
         <v>55.25820103960146</v>
       </c>
       <c r="U101">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V101">
         <v>0</v>
       </c>
       <c r="W101">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.1678413448703692</v>
+        <v>0.2039481456615703</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/bermuda/bermuda_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_real_estate_operations_services.xlsx
@@ -1386,43 +1386,43 @@
         <v>2.53976102183766</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>71.97457688223901</v>
       </c>
       <c r="G2">
         <v>10.2413133567102</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.258924131335671</v>
       </c>
       <c r="I2">
         <v>0.395533367395306</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>9819.5</v>
       </c>
       <c r="L2">
-        <v>19548.2039153343</v>
+        <v>19308.4822118712</v>
       </c>
       <c r="M2">
         <v>15176</v>
       </c>
       <c r="N2">
-        <v>18479.3039153343</v>
+        <v>18402.0312118712</v>
       </c>
       <c r="O2">
         <v>6425.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>162.449</v>
       </c>
       <c r="Q2">
         <v>0.08264747008097049</v>
       </c>
       <c r="R2">
-        <v>0.0759704294282743</v>
+        <v>0.0760992404870395</v>
       </c>
       <c r="S2">
         <v>0.06268110587651871</v>
@@ -1444,13 +1444,13 @@
         <v>0.0957124811873694</v>
       </c>
       <c r="X2">
-        <v>0.0759704294282743</v>
+        <v>0.0762751812406811</v>
       </c>
       <c r="Y2">
         <v>0.914164621486046</v>
       </c>
       <c r="Z2">
-        <v>0.552582010396015</v>
+        <v>0.558163646864662</v>
       </c>
       <c r="AA2">
         <v>6425.4</v>
@@ -1531,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1668,22 +1668,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07597042942827434</v>
+        <v>0.07609924048703952</v>
       </c>
       <c r="C2">
-        <v>19548.20391533428</v>
+        <v>19308.48221187117</v>
       </c>
       <c r="D2">
-        <v>18479.30391533428</v>
+        <v>18402.03121187117</v>
       </c>
       <c r="E2">
-        <v>-6425.4</v>
+        <v>-6262.951</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>162.449</v>
       </c>
       <c r="G2">
         <v>1068.9</v>
@@ -1704,28 +1704,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>9.532686968534589</v>
       </c>
       <c r="N2">
-        <v>686.1111111111111</v>
+        <v>676.5784241425765</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>686.1111111111111</v>
+        <v>676.5784241425765</v>
       </c>
       <c r="Q2">
-        <v>697.1111111111111</v>
+        <v>687.5784241425765</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07597042942827434</v>
+        <v>0.07627518124068114</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5581636468646617</v>
       </c>
       <c r="U2">
         <v>0.05868110587651872</v>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>71.97457688223905</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1750,22 +1750,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07609924048703952</v>
+        <v>0.0762280515458047</v>
       </c>
       <c r="C3">
-        <v>19308.48221187117</v>
+        <v>19069.40406145376</v>
       </c>
       <c r="D3">
-        <v>18402.03121187117</v>
+        <v>18325.40206145376</v>
       </c>
       <c r="E3">
-        <v>-6262.951</v>
+        <v>-6100.501999999999</v>
       </c>
       <c r="F3">
-        <v>162.449</v>
+        <v>324.898</v>
       </c>
       <c r="G3">
         <v>1068.9</v>
@@ -1786,28 +1786,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M3">
-        <v>9.532686968534589</v>
+        <v>19.06537393706918</v>
       </c>
       <c r="N3">
-        <v>676.5784241425765</v>
+        <v>667.045737174042</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>676.5784241425765</v>
+        <v>667.045737174042</v>
       </c>
       <c r="Q3">
-        <v>687.5784241425765</v>
+        <v>678.045737174042</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07627518124068114</v>
+        <v>0.07658615247783095</v>
       </c>
       <c r="T3">
-        <v>0.5581636468646617</v>
+        <v>0.563859194281648</v>
       </c>
       <c r="U3">
         <v>0.05868110587651872</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>71.97457688223905</v>
+        <v>35.98728844111952</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1832,22 +1832,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0762280515458047</v>
+        <v>0.07635686260456989</v>
       </c>
       <c r="C4">
-        <v>19069.40406145376</v>
+        <v>18830.96145783233</v>
       </c>
       <c r="D4">
-        <v>18325.40206145376</v>
+        <v>18249.40845783233</v>
       </c>
       <c r="E4">
-        <v>-6100.501999999999</v>
+        <v>-5938.053</v>
       </c>
       <c r="F4">
-        <v>324.898</v>
+        <v>487.347</v>
       </c>
       <c r="G4">
         <v>1068.9</v>
@@ -1868,28 +1868,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M4">
-        <v>19.06537393706918</v>
+        <v>28.59806090560377</v>
       </c>
       <c r="N4">
-        <v>667.045737174042</v>
+        <v>657.5130502055073</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>667.045737174042</v>
+        <v>657.5130502055073</v>
       </c>
       <c r="Q4">
-        <v>678.045737174042</v>
+        <v>668.5130502055073</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07658615247783095</v>
+        <v>0.07690353549306632</v>
       </c>
       <c r="T4">
-        <v>0.563859194281648</v>
+        <v>0.5696721756659948</v>
       </c>
       <c r="U4">
         <v>0.05868110587651872</v>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.98728844111952</v>
+        <v>23.99152562741302</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1914,22 +1914,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07635686260456989</v>
+        <v>0.07648567366333507</v>
       </c>
       <c r="C5">
-        <v>18830.96145783233</v>
+        <v>18593.14652701318</v>
       </c>
       <c r="D5">
-        <v>18249.40845783233</v>
+        <v>18174.04252701318</v>
       </c>
       <c r="E5">
-        <v>-5938.053</v>
+        <v>-5775.603999999999</v>
       </c>
       <c r="F5">
-        <v>487.347</v>
+        <v>649.796</v>
       </c>
       <c r="G5">
         <v>1068.9</v>
@@ -1950,28 +1950,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M5">
-        <v>28.59806090560377</v>
+        <v>38.13074787413836</v>
       </c>
       <c r="N5">
-        <v>657.5130502055073</v>
+        <v>647.9803632369727</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>657.5130502055073</v>
+        <v>647.9803632369727</v>
       </c>
       <c r="Q5">
-        <v>668.5130502055073</v>
+        <v>658.9803632369727</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07690353549306632</v>
+        <v>0.07722753065445243</v>
       </c>
       <c r="T5">
-        <v>0.5696721756659948</v>
+        <v>0.5756062608291824</v>
       </c>
       <c r="U5">
         <v>0.05868110587651872</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.99152562741302</v>
+        <v>17.99364422055976</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1996,22 +1996,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07648567366333507</v>
+        <v>0.07661448472210027</v>
       </c>
       <c r="C6">
-        <v>18593.14652701318</v>
+        <v>18355.95152453887</v>
       </c>
       <c r="D6">
-        <v>18174.04252701318</v>
+        <v>18099.29652453887</v>
       </c>
       <c r="E6">
-        <v>-5775.603999999999</v>
+        <v>-5613.155</v>
       </c>
       <c r="F6">
-        <v>649.796</v>
+        <v>812.245</v>
       </c>
       <c r="G6">
         <v>1068.9</v>
@@ -2032,28 +2032,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M6">
-        <v>38.13074787413836</v>
+        <v>47.66343484267294</v>
       </c>
       <c r="N6">
-        <v>647.9803632369727</v>
+        <v>638.4476762684382</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>647.9803632369727</v>
+        <v>638.4476762684382</v>
       </c>
       <c r="Q6">
-        <v>658.9803632369727</v>
+        <v>649.4476762684382</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07722753065445243</v>
+        <v>0.07755834676660456</v>
       </c>
       <c r="T6">
-        <v>0.5756062608291824</v>
+        <v>0.5816652741010685</v>
       </c>
       <c r="U6">
         <v>0.05868110587651872</v>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.99364422055976</v>
+        <v>14.39491537644781</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2078,22 +2078,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07661448472210027</v>
+        <v>0.07674329578086544</v>
       </c>
       <c r="C7">
-        <v>18355.95152453887</v>
+        <v>18119.36883283543</v>
       </c>
       <c r="D7">
-        <v>18099.29652453887</v>
+        <v>18025.16283283543</v>
       </c>
       <c r="E7">
-        <v>-5613.155</v>
+        <v>-5450.705999999999</v>
       </c>
       <c r="F7">
-        <v>812.245</v>
+        <v>974.6940000000001</v>
       </c>
       <c r="G7">
         <v>1068.9</v>
@@ -2114,28 +2114,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M7">
-        <v>47.66343484267294</v>
+        <v>57.19612181120754</v>
       </c>
       <c r="N7">
-        <v>638.4476762684382</v>
+        <v>628.9149892999036</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>638.4476762684382</v>
+        <v>628.9149892999036</v>
       </c>
       <c r="Q7">
-        <v>649.4476762684382</v>
+        <v>639.9149892999036</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07755834676660456</v>
+        <v>0.07789620151944078</v>
       </c>
       <c r="T7">
-        <v>0.5816652741010685</v>
+        <v>0.5878532025489522</v>
       </c>
       <c r="U7">
         <v>0.05868110587651872</v>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>14.39491537644781</v>
+        <v>11.99576281370651</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2160,22 +2160,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07674329578086544</v>
+        <v>0.07687210683963064</v>
       </c>
       <c r="C8">
-        <v>18119.36883283543</v>
+        <v>17883.39095862435</v>
       </c>
       <c r="D8">
-        <v>18025.16283283543</v>
+        <v>17951.63395862435</v>
       </c>
       <c r="E8">
-        <v>-5450.706</v>
+        <v>-5288.257</v>
       </c>
       <c r="F8">
-        <v>974.694</v>
+        <v>1137.143</v>
       </c>
       <c r="G8">
         <v>1068.9</v>
@@ -2196,28 +2196,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M8">
-        <v>57.19612181120753</v>
+        <v>66.72880877974211</v>
       </c>
       <c r="N8">
-        <v>628.9149892999036</v>
+        <v>619.3823023313689</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>628.9149892999036</v>
+        <v>619.3823023313689</v>
       </c>
       <c r="Q8">
-        <v>639.9149892999036</v>
+        <v>630.3823023313689</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07789620151944078</v>
+        <v>0.07824132196588637</v>
       </c>
       <c r="T8">
-        <v>0.5878532025489522</v>
+        <v>0.5941742047268979</v>
       </c>
       <c r="U8">
         <v>0.05868110587651872</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.99576281370651</v>
+        <v>10.28208241174844</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2242,22 +2242,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07687210683963064</v>
+        <v>0.07700091789839583</v>
       </c>
       <c r="C9">
-        <v>17883.39095862435</v>
+        <v>17648.01053039779</v>
       </c>
       <c r="D9">
-        <v>17951.63395862435</v>
+        <v>17878.70253039779</v>
       </c>
       <c r="E9">
-        <v>-5288.257</v>
+        <v>-5125.807999999999</v>
       </c>
       <c r="F9">
-        <v>1137.143</v>
+        <v>1299.592</v>
       </c>
       <c r="G9">
         <v>1068.9</v>
@@ -2278,28 +2278,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M9">
-        <v>66.72880877974212</v>
+        <v>76.26149574827672</v>
       </c>
       <c r="N9">
-        <v>619.3823023313689</v>
+        <v>609.8496153628344</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>619.3823023313689</v>
+        <v>609.8496153628344</v>
       </c>
       <c r="Q9">
-        <v>630.3823023313689</v>
+        <v>620.8496153628344</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07824132196588637</v>
+        <v>0.07859394503073297</v>
       </c>
       <c r="T9">
-        <v>0.5941742047268979</v>
+        <v>0.6006326199956685</v>
       </c>
       <c r="U9">
         <v>0.05868110587651872</v>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.28208241174844</v>
+        <v>8.996822110279881</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2324,22 +2324,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07700091789839583</v>
+        <v>0.07726472895716102</v>
       </c>
       <c r="C10">
-        <v>17648.01053039779</v>
+        <v>17338.02893812492</v>
       </c>
       <c r="D10">
-        <v>17878.70253039779</v>
+        <v>17731.16993812492</v>
       </c>
       <c r="E10">
-        <v>-5125.807999999999</v>
+        <v>-4963.358999999999</v>
       </c>
       <c r="F10">
-        <v>1299.592</v>
+        <v>1462.041</v>
       </c>
       <c r="G10">
         <v>1068.9</v>
@@ -2360,45 +2360,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M10">
-        <v>76.26149574827672</v>
+        <v>87.98724421681131</v>
       </c>
       <c r="N10">
-        <v>609.8496153628344</v>
+        <v>598.1238668942998</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>609.8496153628344</v>
+        <v>598.1238668942998</v>
       </c>
       <c r="Q10">
-        <v>620.8496153628344</v>
+        <v>609.1238668942998</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07859394503073297</v>
+        <v>0.07895431805304873</v>
       </c>
       <c r="T10">
-        <v>0.6006326199956685</v>
+        <v>0.6072329784571595</v>
       </c>
       <c r="U10">
-        <v>0.05868110587651872</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.05868110587651872</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.996822110279881</v>
+        <v>7.797847485942958</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2406,22 +2406,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07726472895716102</v>
+        <v>0.0774085400159262</v>
       </c>
       <c r="C11">
-        <v>17338.02893812492</v>
+        <v>17096.17647670852</v>
       </c>
       <c r="D11">
-        <v>17731.16993812492</v>
+        <v>17651.76647670852</v>
       </c>
       <c r="E11">
-        <v>-4963.358999999999</v>
+        <v>-4800.91</v>
       </c>
       <c r="F11">
-        <v>1462.041</v>
+        <v>1624.49</v>
       </c>
       <c r="G11">
         <v>1068.9</v>
@@ -2442,28 +2442,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M11">
-        <v>87.98724421681131</v>
+        <v>97.76360468534588</v>
       </c>
       <c r="N11">
-        <v>598.1238668942998</v>
+        <v>588.3475064257652</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>598.1238668942998</v>
+        <v>588.3475064257652</v>
       </c>
       <c r="Q11">
-        <v>609.1238668942998</v>
+        <v>599.3475064257652</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07895431805304873</v>
+        <v>0.07932269936474926</v>
       </c>
       <c r="T11">
-        <v>0.6072329784571595</v>
+        <v>0.6139800115511279</v>
       </c>
       <c r="U11">
         <v>0.06018110587651872</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.797847485942958</v>
+        <v>7.018062737348663</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2488,22 +2488,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0774085400159262</v>
+        <v>0.0777393510746914</v>
       </c>
       <c r="C12">
-        <v>17096.17647670852</v>
+        <v>16753.74630993861</v>
       </c>
       <c r="D12">
-        <v>17651.76647670852</v>
+        <v>17471.78530993861</v>
       </c>
       <c r="E12">
-        <v>-4800.91</v>
+        <v>-4638.460999999999</v>
       </c>
       <c r="F12">
-        <v>1624.49</v>
+        <v>1786.939</v>
       </c>
       <c r="G12">
         <v>1068.9</v>
@@ -2524,45 +2524,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M12">
-        <v>97.7636046853459</v>
+        <v>110.5777614538805</v>
       </c>
       <c r="N12">
-        <v>588.3475064257652</v>
+        <v>575.5333496572306</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>588.3475064257652</v>
+        <v>575.5333496572306</v>
       </c>
       <c r="Q12">
-        <v>599.3475064257652</v>
+        <v>586.5333496572306</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07932269936474926</v>
+        <v>0.07969935890817341</v>
       </c>
       <c r="T12">
-        <v>0.6139800115511279</v>
+        <v>0.6208786633663091</v>
       </c>
       <c r="U12">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.018062737348663</v>
+        <v>6.204783874172319</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2570,22 +2570,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0777393510746914</v>
+        <v>0.07790016213345657</v>
       </c>
       <c r="C13">
-        <v>16753.74630993861</v>
+        <v>16505.12558148245</v>
       </c>
       <c r="D13">
-        <v>17471.78530993861</v>
+        <v>17385.61358148245</v>
       </c>
       <c r="E13">
-        <v>-4638.460999999999</v>
+        <v>-4476.012</v>
       </c>
       <c r="F13">
-        <v>1786.939</v>
+        <v>1949.388</v>
       </c>
       <c r="G13">
         <v>1068.9</v>
@@ -2606,28 +2606,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M13">
-        <v>110.5777614538805</v>
+        <v>120.6302852224151</v>
       </c>
       <c r="N13">
-        <v>575.5333496572306</v>
+        <v>565.480825888696</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>575.5333496572306</v>
+        <v>565.480825888696</v>
       </c>
       <c r="Q13">
-        <v>586.5333496572306</v>
+        <v>576.480825888696</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07969935890817341</v>
+        <v>0.08008457889576628</v>
       </c>
       <c r="T13">
-        <v>0.6208786633663091</v>
+        <v>0.6279341027227443</v>
       </c>
       <c r="U13">
         <v>0.06188110587651872</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.204783874172319</v>
+        <v>5.687718551324626</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2652,22 +2652,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07790016213345657</v>
+        <v>0.07816497319222176</v>
       </c>
       <c r="C14">
-        <v>16505.12558148245</v>
+        <v>16202.61314446036</v>
       </c>
       <c r="D14">
-        <v>17385.61358148245</v>
+        <v>17245.55014446036</v>
       </c>
       <c r="E14">
-        <v>-4476.012</v>
+        <v>-4313.563</v>
       </c>
       <c r="F14">
-        <v>1949.388</v>
+        <v>2111.837</v>
       </c>
       <c r="G14">
         <v>1068.9</v>
@@ -2688,45 +2688,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M14">
-        <v>120.6302852224151</v>
+        <v>132.3722785909497</v>
       </c>
       <c r="N14">
-        <v>565.480825888696</v>
+        <v>553.7388325201614</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>565.480825888696</v>
+        <v>553.7388325201614</v>
       </c>
       <c r="Q14">
-        <v>576.480825888696</v>
+        <v>564.7388325201614</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08008457889576628</v>
+        <v>0.08047865451525785</v>
       </c>
       <c r="T14">
-        <v>0.6279341027227443</v>
+        <v>0.6351517360873736</v>
       </c>
       <c r="U14">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651872</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>5.687718551324626</v>
+        <v>5.183193327292477</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2734,22 +2734,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07816497319222176</v>
+        <v>0.07833378425098694</v>
       </c>
       <c r="C15">
-        <v>16202.61314446036</v>
+        <v>15952.04873003331</v>
       </c>
       <c r="D15">
-        <v>17245.55014446036</v>
+        <v>17157.43473003331</v>
       </c>
       <c r="E15">
-        <v>-4313.563</v>
+        <v>-4151.114</v>
       </c>
       <c r="F15">
-        <v>2111.837</v>
+        <v>2274.286</v>
       </c>
       <c r="G15">
         <v>1068.9</v>
@@ -2770,28 +2770,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M15">
-        <v>132.3722785909497</v>
+        <v>142.5547615594843</v>
       </c>
       <c r="N15">
-        <v>553.7388325201614</v>
+        <v>543.5563495516268</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>553.7388325201614</v>
+        <v>543.5563495516268</v>
       </c>
       <c r="Q15">
-        <v>564.7388325201614</v>
+        <v>554.5563495516268</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08047865451525785</v>
+        <v>0.08088189468403992</v>
       </c>
       <c r="T15">
-        <v>0.6351517360873736</v>
+        <v>0.6425372213907152</v>
       </c>
       <c r="U15">
         <v>0.06268110587651872</v>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.183193327292477</v>
+        <v>4.812965232485871</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2816,22 +2816,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07833378425098694</v>
+        <v>0.07850259530975214</v>
       </c>
       <c r="C16">
-        <v>15952.04873003331</v>
+        <v>15702.38018223449</v>
       </c>
       <c r="D16">
-        <v>17157.43473003331</v>
+        <v>17070.21518223449</v>
       </c>
       <c r="E16">
-        <v>-4151.114</v>
+        <v>-3988.665</v>
       </c>
       <c r="F16">
-        <v>2274.286</v>
+        <v>2436.735</v>
       </c>
       <c r="G16">
         <v>1068.9</v>
@@ -2852,28 +2852,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M16">
-        <v>142.5547615594843</v>
+        <v>152.7372445280189</v>
       </c>
       <c r="N16">
-        <v>543.5563495516268</v>
+        <v>533.3738665830922</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>543.5563495516268</v>
+        <v>533.3738665830922</v>
       </c>
       <c r="Q16">
-        <v>554.5563495516268</v>
+        <v>544.3738665830922</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08088189468403992</v>
+        <v>0.08129462285679333</v>
       </c>
       <c r="T16">
-        <v>0.6425372213907152</v>
+        <v>0.6500964828188412</v>
       </c>
       <c r="U16">
         <v>0.06268110587651872</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.812965232485871</v>
+        <v>4.492100883653479</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2898,22 +2898,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07850259530975214</v>
+        <v>0.07883140636851732</v>
       </c>
       <c r="C17">
-        <v>15702.38018223449</v>
+        <v>15372.56530557344</v>
       </c>
       <c r="D17">
-        <v>17070.21518223449</v>
+        <v>16902.84930557344</v>
       </c>
       <c r="E17">
-        <v>-3988.665</v>
+        <v>-3826.215999999999</v>
       </c>
       <c r="F17">
-        <v>2436.735</v>
+        <v>2599.184</v>
       </c>
       <c r="G17">
         <v>1068.9</v>
@@ -2934,45 +2934,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M17">
-        <v>152.7372445280188</v>
+        <v>165.5189114965534</v>
       </c>
       <c r="N17">
-        <v>533.3738665830922</v>
+        <v>520.5921996145577</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>533.3738665830922</v>
+        <v>520.5921996145577</v>
       </c>
       <c r="Q17">
-        <v>544.3738665830922</v>
+        <v>531.5921996145577</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08129462285679333</v>
+        <v>0.08171717789080277</v>
       </c>
       <c r="T17">
-        <v>0.6500964828188412</v>
+        <v>0.6578357266619227</v>
       </c>
       <c r="U17">
-        <v>0.06268110587651872</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.06268110587651872</v>
+        <v>0.06368110587651872</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.49210088365348</v>
+        <v>4.145212803223382</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2980,22 +2980,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07883140636851732</v>
+        <v>0.07901021742728251</v>
       </c>
       <c r="C18">
-        <v>15372.56530557344</v>
+        <v>15120.47124420821</v>
       </c>
       <c r="D18">
-        <v>16902.84930557344</v>
+        <v>16813.20424420821</v>
       </c>
       <c r="E18">
-        <v>-3826.215999999999</v>
+        <v>-3663.766999999999</v>
       </c>
       <c r="F18">
-        <v>2599.184</v>
+        <v>2761.633</v>
       </c>
       <c r="G18">
         <v>1068.9</v>
@@ -3016,28 +3016,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M18">
-        <v>165.5189114965534</v>
+        <v>175.8638434650881</v>
       </c>
       <c r="N18">
-        <v>520.5921996145577</v>
+        <v>510.247267646023</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>520.5921996145577</v>
+        <v>510.247267646023</v>
       </c>
       <c r="Q18">
-        <v>531.5921996145577</v>
+        <v>521.247267646023</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08171717789080277</v>
+        <v>0.0821499149738245</v>
       </c>
       <c r="T18">
-        <v>0.6578357266619227</v>
+        <v>0.6657614583084519</v>
       </c>
       <c r="U18">
         <v>0.06368110587651872</v>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.145212803223382</v>
+        <v>3.901376755974947</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3062,22 +3062,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07901021742728251</v>
+        <v>0.0791890284860477</v>
       </c>
       <c r="C19">
-        <v>15120.47124420821</v>
+        <v>14869.3230400966</v>
       </c>
       <c r="D19">
-        <v>16813.20424420821</v>
+        <v>16724.5050400966</v>
       </c>
       <c r="E19">
-        <v>-3663.766999999999</v>
+        <v>-3501.317999999999</v>
       </c>
       <c r="F19">
-        <v>2761.633</v>
+        <v>2924.082</v>
       </c>
       <c r="G19">
         <v>1068.9</v>
@@ -3098,28 +3098,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M19">
-        <v>175.8638434650881</v>
+        <v>186.2087754336226</v>
       </c>
       <c r="N19">
-        <v>510.247267646023</v>
+        <v>499.9023356774885</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>510.247267646023</v>
+        <v>499.9023356774885</v>
       </c>
       <c r="Q19">
-        <v>521.247267646023</v>
+        <v>510.9023356774885</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0821499149738245</v>
+        <v>0.08259320661984675</v>
       </c>
       <c r="T19">
-        <v>0.6657614583084519</v>
+        <v>0.6738805004829452</v>
       </c>
       <c r="U19">
         <v>0.06368110587651872</v>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.901376755974947</v>
+        <v>3.684633602865228</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3144,22 +3144,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07918902848604771</v>
+        <v>0.0793678395448129</v>
       </c>
       <c r="C20">
-        <v>14869.3230400966</v>
+        <v>14619.10580199531</v>
       </c>
       <c r="D20">
-        <v>16724.5050400966</v>
+        <v>16636.73680199531</v>
       </c>
       <c r="E20">
-        <v>-3501.318</v>
+        <v>-3338.869</v>
       </c>
       <c r="F20">
-        <v>2924.082</v>
+        <v>3086.531</v>
       </c>
       <c r="G20">
         <v>1068.9</v>
@@ -3180,28 +3180,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M20">
-        <v>186.2087754336226</v>
+        <v>196.5537074021572</v>
       </c>
       <c r="N20">
-        <v>499.9023356774885</v>
+        <v>489.5574037089539</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>499.9023356774885</v>
+        <v>489.5574037089539</v>
       </c>
       <c r="Q20">
-        <v>510.9023356774885</v>
+        <v>500.5574037089539</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08259320661984675</v>
+        <v>0.08304744373861028</v>
       </c>
       <c r="T20">
-        <v>0.6738805004829452</v>
+        <v>0.6822000128345864</v>
       </c>
       <c r="U20">
         <v>0.06368110587651872</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.684633602865229</v>
+        <v>3.4907055185039</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3226,22 +3226,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0793678395448129</v>
+        <v>0.07954665060357809</v>
       </c>
       <c r="C21">
-        <v>14619.10580199531</v>
+        <v>14369.80494961914</v>
       </c>
       <c r="D21">
-        <v>16636.73680199531</v>
+        <v>16549.88494961914</v>
       </c>
       <c r="E21">
-        <v>-3338.869</v>
+        <v>-3176.42</v>
       </c>
       <c r="F21">
-        <v>3086.531</v>
+        <v>3248.98</v>
       </c>
       <c r="G21">
         <v>1068.9</v>
@@ -3262,28 +3262,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M21">
-        <v>196.5537074021572</v>
+        <v>206.8986393706918</v>
       </c>
       <c r="N21">
-        <v>489.5574037089539</v>
+        <v>479.2124717404193</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>489.5574037089539</v>
+        <v>479.2124717404193</v>
       </c>
       <c r="Q21">
-        <v>500.5574037089539</v>
+        <v>490.2124717404193</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08304744373861028</v>
+        <v>0.08351303678534291</v>
       </c>
       <c r="T21">
-        <v>0.6822000128345864</v>
+        <v>0.6907275129950188</v>
       </c>
       <c r="U21">
         <v>0.06368110587651872</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.4907055185039</v>
+        <v>3.316170242578705</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3308,22 +3308,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07954665060357809</v>
+        <v>0.07972546166234327</v>
       </c>
       <c r="C22">
-        <v>14369.80494961914</v>
+        <v>14121.40620556637</v>
       </c>
       <c r="D22">
-        <v>16549.88494961914</v>
+        <v>16463.93520556637</v>
       </c>
       <c r="E22">
-        <v>-3176.42</v>
+        <v>-3013.971</v>
       </c>
       <c r="F22">
-        <v>3248.98</v>
+        <v>3411.429</v>
       </c>
       <c r="G22">
         <v>1068.9</v>
@@ -3344,28 +3344,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M22">
-        <v>206.8986393706918</v>
+        <v>217.2435713392264</v>
       </c>
       <c r="N22">
-        <v>479.2124717404193</v>
+        <v>468.8675397718847</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>479.2124717404193</v>
+        <v>468.8675397718847</v>
       </c>
       <c r="Q22">
-        <v>490.2124717404193</v>
+        <v>479.8675397718847</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08351303678534291</v>
+        <v>0.08399041699781562</v>
       </c>
       <c r="T22">
-        <v>0.6907275129950188</v>
+        <v>0.6994708992354621</v>
       </c>
       <c r="U22">
         <v>0.06368110587651872</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.316170242578705</v>
+        <v>3.158257373884481</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3390,22 +3390,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07972546166234326</v>
+        <v>0.07990427272110845</v>
       </c>
       <c r="C23">
-        <v>14121.40620556638</v>
+        <v>13873.89558749452</v>
       </c>
       <c r="D23">
-        <v>16463.93520556638</v>
+        <v>16378.87358749452</v>
       </c>
       <c r="E23">
-        <v>-3013.971</v>
+        <v>-2851.521999999999</v>
       </c>
       <c r="F23">
-        <v>3411.429</v>
+        <v>3573.878</v>
       </c>
       <c r="G23">
         <v>1068.9</v>
@@ -3426,28 +3426,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M23">
-        <v>217.2435713392263</v>
+        <v>227.588503307761</v>
       </c>
       <c r="N23">
-        <v>468.8675397718847</v>
+        <v>458.5226078033501</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>468.8675397718847</v>
+        <v>458.5226078033501</v>
       </c>
       <c r="Q23">
-        <v>479.8675397718847</v>
+        <v>469.5226078033501</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08399041699781562</v>
+        <v>0.08448003772855683</v>
       </c>
       <c r="T23">
-        <v>0.6994708992354621</v>
+        <v>0.7084384748666859</v>
       </c>
       <c r="U23">
         <v>0.06368110587651872</v>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.158257373884481</v>
+        <v>3.014700220526096</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3472,22 +3472,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07990427272110845</v>
+        <v>0.08065808377987364</v>
       </c>
       <c r="C24">
-        <v>13873.89558749452</v>
+        <v>13362.31066445911</v>
       </c>
       <c r="D24">
-        <v>16378.87358749452</v>
+        <v>16029.73766445911</v>
       </c>
       <c r="E24">
-        <v>-2851.521999999999</v>
+        <v>-2689.072999999999</v>
       </c>
       <c r="F24">
-        <v>3573.878</v>
+        <v>3736.327</v>
       </c>
       <c r="G24">
         <v>1068.9</v>
@@ -3508,45 +3508,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M24">
-        <v>227.588503307761</v>
+        <v>247.2742527762956</v>
       </c>
       <c r="N24">
-        <v>458.5226078033501</v>
+        <v>438.8368583348155</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>458.5226078033501</v>
+        <v>438.8368583348155</v>
       </c>
       <c r="Q24">
-        <v>469.5226078033501</v>
+        <v>449.8368583348155</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08448003772855683</v>
+        <v>0.08498237588087576</v>
       </c>
       <c r="T24">
-        <v>0.7084384748666859</v>
+        <v>0.7176389745402793</v>
       </c>
       <c r="U24">
-        <v>0.06368110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.06368110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.014700220526096</v>
+        <v>2.774696934305664</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3554,22 +3554,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08065808377987364</v>
+        <v>0.08086189483863883</v>
       </c>
       <c r="C25">
-        <v>13362.31066445911</v>
+        <v>13108.00591381858</v>
       </c>
       <c r="D25">
-        <v>16029.73766445911</v>
+        <v>15937.88191381858</v>
       </c>
       <c r="E25">
-        <v>-2689.072999999999</v>
+        <v>-2526.623999999999</v>
       </c>
       <c r="F25">
-        <v>3736.327</v>
+        <v>3898.776</v>
       </c>
       <c r="G25">
         <v>1068.9</v>
@@ -3590,28 +3590,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M25">
-        <v>247.2742527762956</v>
+        <v>258.0253072448302</v>
       </c>
       <c r="N25">
-        <v>438.8368583348155</v>
+        <v>428.0858038662809</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>438.8368583348155</v>
+        <v>428.0858038662809</v>
       </c>
       <c r="Q25">
-        <v>449.8368583348155</v>
+        <v>439.0858038662809</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08498237588087576</v>
+        <v>0.08549793345825571</v>
       </c>
       <c r="T25">
-        <v>0.7176389745402793</v>
+        <v>0.7270815926263356</v>
       </c>
       <c r="U25">
         <v>0.06618110587651872</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.774696934305664</v>
+        <v>2.659084562042928</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3636,22 +3636,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08086189483863883</v>
+        <v>0.08106570589740401</v>
       </c>
       <c r="C26">
-        <v>13108.00591381858</v>
+        <v>12854.74789332543</v>
       </c>
       <c r="D26">
-        <v>15937.88191381858</v>
+        <v>15847.07289332543</v>
       </c>
       <c r="E26">
-        <v>-2526.624</v>
+        <v>-2364.175</v>
       </c>
       <c r="F26">
-        <v>3898.776</v>
+        <v>4061.225</v>
       </c>
       <c r="G26">
         <v>1068.9</v>
@@ -3672,28 +3672,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M26">
-        <v>258.0253072448302</v>
+        <v>268.7763617133647</v>
       </c>
       <c r="N26">
-        <v>428.0858038662809</v>
+        <v>417.3347493977464</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>428.0858038662809</v>
+        <v>417.3347493977464</v>
       </c>
       <c r="Q26">
-        <v>439.0858038662809</v>
+        <v>428.3347493977464</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08549793345825571</v>
+        <v>0.08602723923769912</v>
       </c>
       <c r="T26">
-        <v>0.7270815926263356</v>
+        <v>0.7367760138613534</v>
       </c>
       <c r="U26">
         <v>0.06618110587651872</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.659084562042928</v>
+        <v>2.552721179561211</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3718,22 +3718,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08106570589740401</v>
+        <v>0.08217951695616919</v>
       </c>
       <c r="C27">
-        <v>12854.74789332543</v>
+        <v>12213.76281222267</v>
       </c>
       <c r="D27">
-        <v>15847.07289332543</v>
+        <v>15368.53681222266</v>
       </c>
       <c r="E27">
-        <v>-2364.175</v>
+        <v>-2201.726</v>
       </c>
       <c r="F27">
-        <v>4061.225</v>
+        <v>4223.674</v>
       </c>
       <c r="G27">
         <v>1068.9</v>
@@ -3754,45 +3754,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M27">
-        <v>268.7763617133647</v>
+        <v>294.3102751818993</v>
       </c>
       <c r="N27">
-        <v>417.3347493977464</v>
+        <v>391.8008359292118</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>417.3347493977464</v>
+        <v>391.8008359292118</v>
       </c>
       <c r="Q27">
-        <v>428.3347493977464</v>
+        <v>402.8008359292118</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08602723923769912</v>
+        <v>0.0865708505787491</v>
       </c>
       <c r="T27">
-        <v>0.7367760138613534</v>
+        <v>0.7467324464811014</v>
       </c>
       <c r="U27">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.552721179561211</v>
+        <v>2.3312509584895</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3800,22 +3800,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08217951695616919</v>
+        <v>0.08317432801493439</v>
       </c>
       <c r="C28">
-        <v>12213.76281222267</v>
+        <v>11647.69712357523</v>
       </c>
       <c r="D28">
-        <v>15368.53681222266</v>
+        <v>14964.92012357523</v>
       </c>
       <c r="E28">
-        <v>-2201.726</v>
+        <v>-2039.276999999999</v>
       </c>
       <c r="F28">
-        <v>4223.674</v>
+        <v>4386.123000000001</v>
       </c>
       <c r="G28">
         <v>1068.9</v>
@@ -3836,45 +3836,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M28">
-        <v>294.3102751818993</v>
+        <v>317.911045550434</v>
       </c>
       <c r="N28">
-        <v>391.8008359292118</v>
+        <v>368.2000655606771</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>391.8008359292118</v>
+        <v>368.2000655606771</v>
       </c>
       <c r="Q28">
-        <v>402.8008359292118</v>
+        <v>379.2000655606771</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0865708505787491</v>
+        <v>0.08712935538119772</v>
       </c>
       <c r="T28">
-        <v>0.7467324464811014</v>
+        <v>0.7569616580767331</v>
       </c>
       <c r="U28">
-        <v>0.06968110587651871</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.06968110587651871</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.3312509584895</v>
+        <v>2.158185821833187</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3882,22 +3882,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08317432801493439</v>
+        <v>0.08344113907369959</v>
       </c>
       <c r="C29">
-        <v>11647.69712357523</v>
+        <v>11380.57723558891</v>
       </c>
       <c r="D29">
-        <v>14964.92012357523</v>
+        <v>14860.24923558891</v>
       </c>
       <c r="E29">
-        <v>-2039.276999999999</v>
+        <v>-1876.828</v>
       </c>
       <c r="F29">
-        <v>4386.123000000001</v>
+        <v>4548.572</v>
       </c>
       <c r="G29">
         <v>1068.9</v>
@@ -3918,28 +3918,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M29">
-        <v>317.911045550434</v>
+        <v>329.6855287189686</v>
       </c>
       <c r="N29">
-        <v>368.2000655606771</v>
+        <v>356.4255823921425</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>368.2000655606771</v>
+        <v>356.4255823921425</v>
       </c>
       <c r="Q29">
-        <v>379.2000655606771</v>
+        <v>367.4255823921425</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08712935538119772</v>
+        <v>0.08770337420593657</v>
       </c>
       <c r="T29">
-        <v>0.7569616580767331</v>
+        <v>0.7674750144389098</v>
       </c>
       <c r="U29">
         <v>0.07248110587651872</v>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.158185821833187</v>
+        <v>2.081107756767716</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3964,22 +3964,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08344113907369959</v>
+        <v>0.08370795013246475</v>
       </c>
       <c r="C30">
-        <v>11380.57723558891</v>
+        <v>11114.91140097185</v>
       </c>
       <c r="D30">
-        <v>14860.24923558891</v>
+        <v>14757.03240097185</v>
       </c>
       <c r="E30">
-        <v>-1876.828</v>
+        <v>-1714.378999999999</v>
       </c>
       <c r="F30">
-        <v>4548.572</v>
+        <v>4711.021000000001</v>
       </c>
       <c r="G30">
         <v>1068.9</v>
@@ -4000,28 +4000,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M30">
-        <v>329.6855287189686</v>
+        <v>341.4600118875031</v>
       </c>
       <c r="N30">
-        <v>356.4255823921425</v>
+        <v>344.651099223608</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>356.4255823921425</v>
+        <v>344.651099223608</v>
       </c>
       <c r="Q30">
-        <v>367.4255823921425</v>
+        <v>355.651099223608</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08770337420593657</v>
+        <v>0.08829356257503426</v>
       </c>
       <c r="T30">
-        <v>0.7674750144389098</v>
+        <v>0.7782845216845283</v>
       </c>
       <c r="U30">
         <v>0.07248110587651872</v>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.081107756767716</v>
+        <v>2.00934542032745</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4046,22 +4046,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08370795013246475</v>
+        <v>0.08631476119122994</v>
       </c>
       <c r="C31">
-        <v>11114.91140097185</v>
+        <v>10014.65458853131</v>
       </c>
       <c r="D31">
-        <v>14757.03240097185</v>
+        <v>13819.22458853131</v>
       </c>
       <c r="E31">
-        <v>-1714.379</v>
+        <v>-1551.93</v>
       </c>
       <c r="F31">
-        <v>4711.021</v>
+        <v>4873.469999999999</v>
       </c>
       <c r="G31">
         <v>1068.9</v>
@@ -4082,45 +4082,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M31">
-        <v>341.4600118875031</v>
+        <v>391.2475610560376</v>
       </c>
       <c r="N31">
-        <v>344.651099223608</v>
+        <v>294.8635500550735</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>344.651099223608</v>
+        <v>294.8635500550735</v>
       </c>
       <c r="Q31">
-        <v>355.651099223608</v>
+        <v>305.8635500550735</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08829356257503426</v>
+        <v>0.08890061346896333</v>
       </c>
       <c r="T31">
-        <v>0.7782845216845282</v>
+        <v>0.7894028719943073</v>
       </c>
       <c r="U31">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.00934542032745</v>
+        <v>1.753649554413045</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4128,22 +4128,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08631476119122994</v>
+        <v>0.08786857224999514</v>
       </c>
       <c r="C32">
-        <v>10014.65458853131</v>
+        <v>9347.846050826529</v>
       </c>
       <c r="D32">
-        <v>13819.22458853131</v>
+        <v>13314.86505082653</v>
       </c>
       <c r="E32">
-        <v>-1551.93</v>
+        <v>-1389.481</v>
       </c>
       <c r="F32">
-        <v>4873.469999999999</v>
+        <v>5035.919</v>
       </c>
       <c r="G32">
         <v>1068.9</v>
@@ -4164,45 +4164,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M32">
-        <v>391.2475610560376</v>
+        <v>423.9292305245723</v>
       </c>
       <c r="N32">
-        <v>294.8635500550735</v>
+        <v>262.1818805865388</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>294.8635500550735</v>
+        <v>262.1818805865388</v>
       </c>
       <c r="Q32">
-        <v>305.8635500550735</v>
+        <v>273.1818805865388</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08890061346896333</v>
+        <v>0.0895252600409773</v>
       </c>
       <c r="T32">
-        <v>0.7894028719943073</v>
+        <v>0.8008434933275581</v>
       </c>
       <c r="U32">
-        <v>0.08028110587651871</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.08028110587651871</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.753649554413045</v>
+        <v>1.618456718028416</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4210,22 +4210,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08786857224999514</v>
+        <v>0.08825238330876031</v>
       </c>
       <c r="C33">
-        <v>9347.846050826529</v>
+        <v>9066.433232482692</v>
       </c>
       <c r="D33">
-        <v>13314.86505082653</v>
+        <v>13195.90123248269</v>
       </c>
       <c r="E33">
-        <v>-1389.481</v>
+        <v>-1227.031999999999</v>
       </c>
       <c r="F33">
-        <v>5035.919</v>
+        <v>5198.368</v>
       </c>
       <c r="G33">
         <v>1068.9</v>
@@ -4246,28 +4246,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M33">
-        <v>423.9292305245723</v>
+        <v>437.6043669931069</v>
       </c>
       <c r="N33">
-        <v>262.1818805865388</v>
+        <v>248.5067441180042</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>262.1818805865388</v>
+        <v>248.5067441180042</v>
       </c>
       <c r="Q33">
-        <v>273.1818805865388</v>
+        <v>259.5067441180042</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0895252600409773</v>
+        <v>0.09016827857099166</v>
       </c>
       <c r="T33">
-        <v>0.8008434933275581</v>
+        <v>0.8126206035235516</v>
       </c>
       <c r="U33">
         <v>0.08418110587651872</v>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.618456718028416</v>
+        <v>1.567879945590028</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4292,22 +4292,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08825238330876031</v>
+        <v>0.08863619436752551</v>
       </c>
       <c r="C34">
-        <v>9066.433232482692</v>
+        <v>8787.127392009828</v>
       </c>
       <c r="D34">
-        <v>13195.90123248269</v>
+        <v>13079.04439200983</v>
       </c>
       <c r="E34">
-        <v>-1227.031999999999</v>
+        <v>-1064.583</v>
       </c>
       <c r="F34">
-        <v>5198.368</v>
+        <v>5360.817</v>
       </c>
       <c r="G34">
         <v>1068.9</v>
@@ -4328,28 +4328,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M34">
-        <v>437.6043669931069</v>
+        <v>451.2795034616415</v>
       </c>
       <c r="N34">
-        <v>248.5067441180042</v>
+        <v>234.8316076494696</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>248.5067441180042</v>
+        <v>234.8316076494696</v>
       </c>
       <c r="Q34">
-        <v>259.5067441180042</v>
+        <v>245.8316076494696</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09016827857099166</v>
+        <v>0.09083049168399154</v>
       </c>
       <c r="T34">
-        <v>0.8126206035235516</v>
+        <v>0.8247492692477837</v>
       </c>
       <c r="U34">
         <v>0.08418110587651872</v>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.567879945590028</v>
+        <v>1.5203684320873</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4374,22 +4374,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08863619436752551</v>
+        <v>0.0938480054262907</v>
       </c>
       <c r="C35">
-        <v>8787.127392009828</v>
+        <v>7220.742757074578</v>
       </c>
       <c r="D35">
-        <v>13079.04439200983</v>
+        <v>11675.10875707458</v>
       </c>
       <c r="E35">
-        <v>-1064.583</v>
+        <v>-902.1339999999991</v>
       </c>
       <c r="F35">
-        <v>5360.817</v>
+        <v>5523.266000000001</v>
       </c>
       <c r="G35">
         <v>1068.9</v>
@@ -4410,45 +4410,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M35">
-        <v>451.2795034616415</v>
+        <v>543.385017130176</v>
       </c>
       <c r="N35">
-        <v>234.8316076494696</v>
+        <v>142.726093980935</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>234.8316076494696</v>
+        <v>142.726093980935</v>
       </c>
       <c r="Q35">
-        <v>245.8316076494696</v>
+        <v>153.726093980935</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09083049168399154</v>
+        <v>0.09151277186102172</v>
       </c>
       <c r="T35">
-        <v>0.8247492692477837</v>
+        <v>0.8372454702969925</v>
       </c>
       <c r="U35">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651872</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651872</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.5203684320873</v>
+        <v>1.262661077286831</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4456,22 +4456,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0938480054262907</v>
+        <v>0.1043838164850559</v>
       </c>
       <c r="C36">
-        <v>7220.742757074578</v>
+        <v>4976.572876468657</v>
       </c>
       <c r="D36">
-        <v>11675.10875707458</v>
+        <v>9593.387876468658</v>
       </c>
       <c r="E36">
-        <v>-902.1339999999991</v>
+        <v>-739.6849999999995</v>
       </c>
       <c r="F36">
-        <v>5523.266000000001</v>
+        <v>5685.715</v>
       </c>
       <c r="G36">
         <v>1068.9</v>
@@ -4492,45 +4492,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M36">
-        <v>543.385017130176</v>
+        <v>721.9783783987107</v>
       </c>
       <c r="N36">
-        <v>142.726093980935</v>
+        <v>-35.86726728759959</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P36">
-        <v>142.726093980935</v>
+        <v>-35.86726728759959</v>
       </c>
       <c r="Q36">
-        <v>153.726093980935</v>
+        <v>-24.86726728759959</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09151277186102172</v>
+        <v>0.0922160452742682</v>
       </c>
       <c r="T36">
-        <v>0.8372454702969925</v>
+        <v>0.8501261698400232</v>
       </c>
       <c r="U36">
-        <v>0.09838110587651872</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.09838110587651872</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.262661077286831</v>
+        <v>0.9503208567448374</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4538,22 +4538,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1043838164850559</v>
+        <v>0.1051956275438211</v>
       </c>
       <c r="C37">
-        <v>4976.572876468657</v>
+        <v>4684.108567810246</v>
       </c>
       <c r="D37">
-        <v>9593.387876468658</v>
+        <v>9463.372567810247</v>
       </c>
       <c r="E37">
-        <v>-739.6849999999995</v>
+        <v>-577.235999999999</v>
       </c>
       <c r="F37">
-        <v>5685.715</v>
+        <v>5848.164000000001</v>
       </c>
       <c r="G37">
         <v>1068.9</v>
@@ -4574,28 +4574,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M37">
-        <v>721.9783783987107</v>
+        <v>742.6063320672454</v>
       </c>
       <c r="N37">
-        <v>-35.86726728759959</v>
+        <v>-56.49522095613429</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-35.86726728759959</v>
+        <v>-56.49522095613429</v>
       </c>
       <c r="Q37">
-        <v>-24.86726728759959</v>
+        <v>-45.49522095613429</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0922160452742682</v>
+        <v>0.09294129598167863</v>
       </c>
       <c r="T37">
-        <v>0.8501261698400232</v>
+        <v>0.8634093912437736</v>
       </c>
       <c r="U37">
         <v>0.1269811058765187</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9503208567448374</v>
+        <v>0.9239230551685917</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4620,22 +4620,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1051956275438211</v>
+        <v>0.1060074386025863</v>
       </c>
       <c r="C38">
-        <v>4684.108567810247</v>
+        <v>4395.12122707422</v>
       </c>
       <c r="D38">
-        <v>9463.372567810247</v>
+        <v>9336.83422707422</v>
       </c>
       <c r="E38">
-        <v>-577.2359999999999</v>
+        <v>-414.7870000000003</v>
       </c>
       <c r="F38">
-        <v>5848.164</v>
+        <v>6010.612999999999</v>
       </c>
       <c r="G38">
         <v>1068.9</v>
@@ -4656,28 +4656,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M38">
-        <v>742.6063320672453</v>
+        <v>763.2342857357797</v>
       </c>
       <c r="N38">
-        <v>-56.49522095613418</v>
+        <v>-77.12317462466865</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-56.49522095613418</v>
+        <v>-77.12317462466865</v>
       </c>
       <c r="Q38">
-        <v>-45.49522095613418</v>
+        <v>-66.12317462466865</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09294129598167863</v>
+        <v>0.09368957052107038</v>
       </c>
       <c r="T38">
-        <v>0.8634093912437736</v>
+        <v>0.877114302215897</v>
       </c>
       <c r="U38">
         <v>0.1269811058765187</v>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9239230551685919</v>
+        <v>0.8989521617856571</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4702,22 +4702,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1060074386025863</v>
+        <v>0.1068192496613515</v>
       </c>
       <c r="C39">
-        <v>4395.12122707422</v>
+        <v>4109.473219065872</v>
       </c>
       <c r="D39">
-        <v>9336.83422707422</v>
+        <v>9213.635219065873</v>
       </c>
       <c r="E39">
-        <v>-414.7870000000003</v>
+        <v>-252.3379999999997</v>
       </c>
       <c r="F39">
-        <v>6010.612999999999</v>
+        <v>6173.062</v>
       </c>
       <c r="G39">
         <v>1068.9</v>
@@ -4738,28 +4738,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M39">
-        <v>763.2342857357797</v>
+        <v>783.8622394043144</v>
       </c>
       <c r="N39">
-        <v>-77.12317462466865</v>
+        <v>-97.75112829320335</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-77.12317462466865</v>
+        <v>-97.75112829320335</v>
       </c>
       <c r="Q39">
-        <v>-66.12317462466865</v>
+        <v>-86.75112829320335</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09368957052107038</v>
+        <v>0.09446198294882957</v>
       </c>
       <c r="T39">
-        <v>0.877114302215897</v>
+        <v>0.8912613070903468</v>
       </c>
       <c r="U39">
         <v>0.1269811058765187</v>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8989521617856571</v>
+        <v>0.8752955259491922</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4784,22 +4784,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1068192496613515</v>
+        <v>0.1076310607201166</v>
       </c>
       <c r="C40">
-        <v>4109.473219065872</v>
+        <v>3827.034078340985</v>
       </c>
       <c r="D40">
-        <v>9213.635219065873</v>
+        <v>9093.645078340985</v>
       </c>
       <c r="E40">
-        <v>-252.3379999999997</v>
+        <v>-89.88899999999921</v>
       </c>
       <c r="F40">
-        <v>6173.062</v>
+        <v>6335.511</v>
       </c>
       <c r="G40">
         <v>1068.9</v>
@@ -4820,28 +4820,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M40">
-        <v>783.8622394043144</v>
+        <v>804.4901930728491</v>
       </c>
       <c r="N40">
-        <v>-97.75112829320335</v>
+        <v>-118.3790819617381</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-97.75112829320335</v>
+        <v>-118.3790819617381</v>
       </c>
       <c r="Q40">
-        <v>-86.75112829320335</v>
+        <v>-107.3790819617381</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09446198294882957</v>
+        <v>0.09525972037422022</v>
       </c>
       <c r="T40">
-        <v>0.8912613070903468</v>
+        <v>0.9058721481901887</v>
       </c>
       <c r="U40">
         <v>0.1269811058765187</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8752955259491922</v>
+        <v>0.8528520509248539</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4866,22 +4866,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1076310607201166</v>
+        <v>0.1084428717788818</v>
       </c>
       <c r="C41">
-        <v>3827.034078340985</v>
+        <v>3547.680048345567</v>
       </c>
       <c r="D41">
-        <v>9093.645078340985</v>
+        <v>8976.740048345568</v>
       </c>
       <c r="E41">
-        <v>-89.88899999999921</v>
+        <v>72.5600000000004</v>
       </c>
       <c r="F41">
-        <v>6335.511</v>
+        <v>6497.96</v>
       </c>
       <c r="G41">
         <v>1068.9</v>
@@ -4902,28 +4902,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M41">
-        <v>804.4901930728491</v>
+        <v>825.1181467413836</v>
       </c>
       <c r="N41">
-        <v>-118.3790819617381</v>
+        <v>-139.0070356302725</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-118.3790819617381</v>
+        <v>-139.0070356302725</v>
       </c>
       <c r="Q41">
-        <v>-107.3790819617381</v>
+        <v>-128.0070356302725</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09525972037422022</v>
+        <v>0.09608404904712389</v>
       </c>
       <c r="T41">
-        <v>0.9058721481901887</v>
+        <v>0.9209700173266918</v>
       </c>
       <c r="U41">
         <v>0.1269811058765187</v>
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8528520509248539</v>
+        <v>0.8315307496517327</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4948,22 +4948,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1084428717788818</v>
+        <v>0.109254682837647</v>
       </c>
       <c r="C42">
-        <v>3547.680048345567</v>
+        <v>3271.293655652483</v>
       </c>
       <c r="D42">
-        <v>8976.740048345568</v>
+        <v>8862.802655652484</v>
       </c>
       <c r="E42">
-        <v>72.5600000000004</v>
+        <v>235.0090000000009</v>
       </c>
       <c r="F42">
-        <v>6497.96</v>
+        <v>6660.409000000001</v>
       </c>
       <c r="G42">
         <v>1068.9</v>
@@ -4984,28 +4984,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M42">
-        <v>825.1181467413836</v>
+        <v>845.7461004099183</v>
       </c>
       <c r="N42">
-        <v>-139.0070356302725</v>
+        <v>-159.6349892988072</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-139.0070356302725</v>
+        <v>-159.6349892988072</v>
       </c>
       <c r="Q42">
-        <v>-128.0070356302725</v>
+        <v>-148.6349892988072</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09608404904712389</v>
+        <v>0.09693632106487174</v>
       </c>
       <c r="T42">
-        <v>0.9209700173266918</v>
+        <v>0.9365796786373136</v>
       </c>
       <c r="U42">
         <v>0.1269811058765187</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8315307496517327</v>
+        <v>0.8112495118553489</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5030,22 +5030,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.109254682837647</v>
+        <v>0.1445904938964122</v>
       </c>
       <c r="C43">
-        <v>3271.293655652483</v>
+        <v>-45.11357270572807</v>
       </c>
       <c r="D43">
-        <v>8862.802655652484</v>
+        <v>5708.844427294272</v>
       </c>
       <c r="E43">
-        <v>235.0090000000009</v>
+        <v>397.4580000000005</v>
       </c>
       <c r="F43">
-        <v>6660.409000000001</v>
+        <v>6822.858</v>
       </c>
       <c r="G43">
         <v>1068.9</v>
@@ -5066,45 +5066,45 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M43">
-        <v>845.7461004099183</v>
+        <v>1427.212981678453</v>
       </c>
       <c r="N43">
-        <v>-159.6349892988072</v>
+        <v>-741.1018705673418</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-159.6349892988072</v>
+        <v>-741.1018705673418</v>
       </c>
       <c r="Q43">
-        <v>-148.6349892988072</v>
+        <v>-730.1018705673418</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09693632106487174</v>
+        <v>0.09781798177288678</v>
       </c>
       <c r="T43">
-        <v>0.9365796786373136</v>
+        <v>0.9527276041310605</v>
       </c>
       <c r="U43">
-        <v>0.1269811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.1269811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.8112495118553489</v>
+        <v>0.4807349147737012</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5112,22 +5112,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1445904938964122</v>
+        <v>0.1462243049551774</v>
       </c>
       <c r="C44">
-        <v>-45.11357270572717</v>
+        <v>-299.9753669449228</v>
       </c>
       <c r="D44">
-        <v>5708.844427294272</v>
+        <v>5616.431633055077</v>
       </c>
       <c r="E44">
-        <v>397.4579999999996</v>
+        <v>559.9070000000002</v>
       </c>
       <c r="F44">
-        <v>6822.857999999999</v>
+        <v>6985.307</v>
       </c>
       <c r="G44">
         <v>1068.9</v>
@@ -5148,28 +5148,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M44">
-        <v>1427.212981678453</v>
+        <v>1461.194243146987</v>
       </c>
       <c r="N44">
-        <v>-741.1018705673416</v>
+        <v>-775.0831320358764</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-741.1018705673416</v>
+        <v>-775.0831320358764</v>
       </c>
       <c r="Q44">
-        <v>-730.1018705673416</v>
+        <v>-764.0831320358764</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09781798177288678</v>
+        <v>0.09873057794434092</v>
       </c>
       <c r="T44">
-        <v>0.9527276041310604</v>
+        <v>0.9694421235017807</v>
       </c>
       <c r="U44">
         <v>0.2091811058765187</v>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4807349147737013</v>
+        <v>0.469555033034778</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5194,22 +5194,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1462243049551774</v>
+        <v>0.1478581160139426</v>
       </c>
       <c r="C45">
-        <v>-299.9753669449228</v>
+        <v>-551.8929288520658</v>
       </c>
       <c r="D45">
-        <v>5616.431633055077</v>
+        <v>5526.963071147934</v>
       </c>
       <c r="E45">
-        <v>559.9070000000002</v>
+        <v>722.3560000000007</v>
       </c>
       <c r="F45">
-        <v>6985.307</v>
+        <v>7147.756</v>
       </c>
       <c r="G45">
         <v>1068.9</v>
@@ -5230,28 +5230,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M45">
-        <v>1461.194243146987</v>
+        <v>1495.175504615522</v>
       </c>
       <c r="N45">
-        <v>-775.0831320358764</v>
+        <v>-809.0643935044109</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-775.0831320358764</v>
+        <v>-809.0643935044109</v>
       </c>
       <c r="Q45">
-        <v>-764.0831320358764</v>
+        <v>-798.0643935044109</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09873057794434092</v>
+        <v>0.09967576683620416</v>
       </c>
       <c r="T45">
-        <v>0.9694421235017807</v>
+        <v>0.986753589992884</v>
       </c>
       <c r="U45">
         <v>0.2091811058765187</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.469555033034778</v>
+        <v>0.458883327738533</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5276,22 +5276,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1478581160139426</v>
+        <v>0.1494919270727078</v>
       </c>
       <c r="C46">
-        <v>-551.8929288520658</v>
+        <v>-801.0047551885782</v>
       </c>
       <c r="D46">
-        <v>5526.963071147934</v>
+        <v>5440.300244811421</v>
       </c>
       <c r="E46">
-        <v>722.3560000000007</v>
+        <v>884.8050000000003</v>
       </c>
       <c r="F46">
-        <v>7147.756</v>
+        <v>7310.205</v>
       </c>
       <c r="G46">
         <v>1068.9</v>
@@ -5312,28 +5312,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M46">
-        <v>1495.175504615522</v>
+        <v>1529.156766084056</v>
       </c>
       <c r="N46">
-        <v>-809.0643935044109</v>
+        <v>-843.0456549729454</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-809.0643935044109</v>
+        <v>-843.0456549729454</v>
       </c>
       <c r="Q46">
-        <v>-798.0643935044109</v>
+        <v>-832.0456549729454</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09967576683620416</v>
+        <v>0.1006553262332261</v>
       </c>
       <c r="T46">
-        <v>0.986753589992884</v>
+        <v>1.004694564356391</v>
       </c>
       <c r="U46">
         <v>0.2091811058765187</v>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.458883327738533</v>
+        <v>0.4486859204554545</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5358,22 +5358,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1494919270727078</v>
+        <v>0.151125738131473</v>
       </c>
       <c r="C47">
-        <v>-801.0047551885782</v>
+        <v>-1047.440790296469</v>
       </c>
       <c r="D47">
-        <v>5440.300244811421</v>
+        <v>5356.313209703532</v>
       </c>
       <c r="E47">
-        <v>884.8050000000003</v>
+        <v>1047.254000000001</v>
       </c>
       <c r="F47">
-        <v>7310.205</v>
+        <v>7472.654</v>
       </c>
       <c r="G47">
         <v>1068.9</v>
@@ -5394,28 +5394,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M47">
-        <v>1529.156766084056</v>
+        <v>1563.138027552591</v>
       </c>
       <c r="N47">
-        <v>-843.0456549729454</v>
+        <v>-877.0269164414801</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-843.0456549729454</v>
+        <v>-877.0269164414801</v>
       </c>
       <c r="Q47">
-        <v>-832.0456549729454</v>
+        <v>-866.0269164414801</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1006553262332261</v>
+        <v>0.1016711656079154</v>
       </c>
       <c r="T47">
-        <v>1.004694564356391</v>
+        <v>1.02330001925188</v>
       </c>
       <c r="U47">
         <v>0.2091811058765187</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4486859204554545</v>
+        <v>0.4389318787064229</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5440,22 +5440,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.151125738131473</v>
+        <v>0.1527595491902382</v>
       </c>
       <c r="C48">
-        <v>-1047.440790296469</v>
+        <v>-1291.323076220512</v>
       </c>
       <c r="D48">
-        <v>5356.313209703532</v>
+        <v>5274.879923779487</v>
       </c>
       <c r="E48">
-        <v>1047.254000000001</v>
+        <v>1209.703</v>
       </c>
       <c r="F48">
-        <v>7472.654</v>
+        <v>7635.103</v>
       </c>
       <c r="G48">
         <v>1068.9</v>
@@ -5476,28 +5476,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M48">
-        <v>1563.138027552591</v>
+        <v>1597.119289021126</v>
       </c>
       <c r="N48">
-        <v>-877.0269164414801</v>
+        <v>-911.0081779100146</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-877.0269164414801</v>
+        <v>-911.0081779100146</v>
       </c>
       <c r="Q48">
-        <v>-866.0269164414801</v>
+        <v>-900.0081779100146</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1016711656079154</v>
+        <v>0.1027253385439138</v>
       </c>
       <c r="T48">
-        <v>1.02330001925188</v>
+        <v>1.042607566784934</v>
       </c>
       <c r="U48">
         <v>0.2091811058765187</v>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4389318787064229</v>
+        <v>0.4295929025637331</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5522,22 +5522,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1527595491902382</v>
+        <v>0.1543933602490033</v>
       </c>
       <c r="C49">
-        <v>-1291.323076220512</v>
+        <v>-1532.766344414796</v>
       </c>
       <c r="D49">
-        <v>5274.879923779487</v>
+        <v>5195.885655585204</v>
       </c>
       <c r="E49">
-        <v>1209.703</v>
+        <v>1372.152000000001</v>
       </c>
       <c r="F49">
-        <v>7635.103</v>
+        <v>7797.552000000001</v>
       </c>
       <c r="G49">
         <v>1068.9</v>
@@ -5558,28 +5558,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M49">
-        <v>1597.119289021126</v>
+        <v>1631.10055048966</v>
       </c>
       <c r="N49">
-        <v>-911.0081779100146</v>
+        <v>-944.9894393785494</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-911.0081779100146</v>
+        <v>-944.9894393785494</v>
       </c>
       <c r="Q49">
-        <v>-900.0081779100146</v>
+        <v>-933.9894393785494</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1027253385439138</v>
+        <v>0.1038200565928352</v>
       </c>
       <c r="T49">
-        <v>1.042607566784934</v>
+        <v>1.062657712300029</v>
       </c>
       <c r="U49">
         <v>0.2091811058765187</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4295929025637331</v>
+        <v>0.4206430504269886</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5604,22 +5604,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1543933602490033</v>
+        <v>0.1560271713077685</v>
       </c>
       <c r="C50">
-        <v>-1532.766344414795</v>
+        <v>-1771.878555066894</v>
       </c>
       <c r="D50">
-        <v>5195.885655585204</v>
+        <v>5119.222444933105</v>
       </c>
       <c r="E50">
-        <v>1372.152</v>
+        <v>1534.601</v>
       </c>
       <c r="F50">
-        <v>7797.552</v>
+        <v>7960.000999999999</v>
       </c>
       <c r="G50">
         <v>1068.9</v>
@@ -5640,28 +5640,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M50">
-        <v>1631.10055048966</v>
+        <v>1665.081811958195</v>
       </c>
       <c r="N50">
-        <v>-944.9894393785492</v>
+        <v>-978.9707008470837</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-944.9894393785492</v>
+        <v>-978.9707008470837</v>
       </c>
       <c r="Q50">
-        <v>-933.9894393785492</v>
+        <v>-967.9707008470837</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1038200565928352</v>
+        <v>0.1049577047613222</v>
       </c>
       <c r="T50">
-        <v>1.062657712300029</v>
+        <v>1.083494138031402</v>
       </c>
       <c r="U50">
         <v>0.2091811058765187</v>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4206430504269887</v>
+        <v>0.4120584983774582</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5686,22 +5686,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1560271713077685</v>
+        <v>0.1576609823665337</v>
       </c>
       <c r="C51">
-        <v>-1771.878555066894</v>
+        <v>-2008.761389371201</v>
       </c>
       <c r="D51">
-        <v>5119.222444933105</v>
+        <v>5044.788610628798</v>
       </c>
       <c r="E51">
-        <v>1534.601</v>
+        <v>1697.05</v>
       </c>
       <c r="F51">
-        <v>7960.000999999999</v>
+        <v>8122.45</v>
       </c>
       <c r="G51">
         <v>1068.9</v>
@@ -5722,28 +5722,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M51">
-        <v>1665.081811958195</v>
+        <v>1699.063073426729</v>
       </c>
       <c r="N51">
-        <v>-978.9707008470837</v>
+        <v>-1012.951962315618</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-978.9707008470837</v>
+        <v>-1012.951962315618</v>
       </c>
       <c r="Q51">
-        <v>-967.9707008470837</v>
+        <v>-1001.951962315618</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1049577047613222</v>
+        <v>0.1061408588565487</v>
       </c>
       <c r="T51">
-        <v>1.083494138031402</v>
+        <v>1.10516402079203</v>
       </c>
       <c r="U51">
         <v>0.2091811058765187</v>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4120584983774582</v>
+        <v>0.403817328409909</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5768,22 +5768,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1576609823665337</v>
+        <v>0.1592947934252989</v>
       </c>
       <c r="C52">
-        <v>-2008.761389371201</v>
+        <v>-2243.510699471608</v>
       </c>
       <c r="D52">
-        <v>5044.788610628798</v>
+        <v>4972.488300528391</v>
       </c>
       <c r="E52">
-        <v>1697.05</v>
+        <v>1859.499</v>
       </c>
       <c r="F52">
-        <v>8122.45</v>
+        <v>8284.898999999999</v>
       </c>
       <c r="G52">
         <v>1068.9</v>
@@ -5804,28 +5804,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M52">
-        <v>1699.063073426729</v>
+        <v>1733.044334895264</v>
       </c>
       <c r="N52">
-        <v>-1012.951962315618</v>
+        <v>-1046.933223784153</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-1012.951962315618</v>
+        <v>-1046.933223784153</v>
       </c>
       <c r="Q52">
-        <v>-1001.951962315618</v>
+        <v>-1035.933223784153</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1061408588565487</v>
+        <v>0.1073723049556619</v>
       </c>
       <c r="T52">
-        <v>1.10516402079203</v>
+        <v>1.127718388563296</v>
       </c>
       <c r="U52">
         <v>0.2091811058765187</v>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.403817328409909</v>
+        <v>0.3958993415783423</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5850,22 +5850,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1592947934252989</v>
+        <v>0.1609286044840641</v>
       </c>
       <c r="C53">
-        <v>-2243.510699471608</v>
+        <v>-2476.216920260265</v>
       </c>
       <c r="D53">
-        <v>4972.488300528391</v>
+        <v>4902.231079739735</v>
       </c>
       <c r="E53">
-        <v>1859.499</v>
+        <v>2021.948</v>
       </c>
       <c r="F53">
-        <v>8284.898999999999</v>
+        <v>8447.348</v>
       </c>
       <c r="G53">
         <v>1068.9</v>
@@ -5886,28 +5886,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M53">
-        <v>1733.044334895264</v>
+        <v>1767.025596363799</v>
       </c>
       <c r="N53">
-        <v>-1046.933223784153</v>
+        <v>-1080.914485252688</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-1046.933223784153</v>
+        <v>-1080.914485252688</v>
       </c>
       <c r="Q53">
-        <v>-1035.933223784153</v>
+        <v>-1069.914485252688</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1073723049556619</v>
+        <v>0.1086550613089049</v>
       </c>
       <c r="T53">
-        <v>1.127718388563296</v>
+        <v>1.151212521658365</v>
       </c>
       <c r="U53">
         <v>0.2091811058765187</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3958993415783423</v>
+        <v>0.3882858927018357</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5932,22 +5932,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1609286044840641</v>
+        <v>0.1625624155428293</v>
       </c>
       <c r="C54">
-        <v>-2476.216920260265</v>
+        <v>-2706.9654467524</v>
       </c>
       <c r="D54">
-        <v>4902.231079739735</v>
+        <v>4833.9315532476</v>
       </c>
       <c r="E54">
-        <v>2021.948</v>
+        <v>2184.397000000001</v>
       </c>
       <c r="F54">
-        <v>8447.348</v>
+        <v>8609.797</v>
       </c>
       <c r="G54">
         <v>1068.9</v>
@@ -5968,28 +5968,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M54">
-        <v>1767.025596363799</v>
+        <v>1801.006857832333</v>
       </c>
       <c r="N54">
-        <v>-1080.914485252688</v>
+        <v>-1114.895746721222</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-1080.914485252688</v>
+        <v>-1114.895746721222</v>
       </c>
       <c r="Q54">
-        <v>-1069.914485252688</v>
+        <v>-1103.895746721222</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1086550613089049</v>
+        <v>0.1099924030388816</v>
       </c>
       <c r="T54">
-        <v>1.151212521658365</v>
+        <v>1.175706405097904</v>
       </c>
       <c r="U54">
         <v>0.2091811058765187</v>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3882858927018357</v>
+        <v>0.3809597437829331</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6014,22 +6014,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1625624155428293</v>
+        <v>0.1641962266015944</v>
       </c>
       <c r="C55">
-        <v>-2706.9654467524</v>
+        <v>-2935.836980348362</v>
       </c>
       <c r="D55">
-        <v>4833.9315532476</v>
+        <v>4767.509019651639</v>
       </c>
       <c r="E55">
-        <v>2184.397000000001</v>
+        <v>2346.846000000001</v>
       </c>
       <c r="F55">
-        <v>8609.797</v>
+        <v>8772.246000000001</v>
       </c>
       <c r="G55">
         <v>1068.9</v>
@@ -6050,28 +6050,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M55">
-        <v>1801.006857832333</v>
+        <v>1834.988119300868</v>
       </c>
       <c r="N55">
-        <v>-1114.895746721222</v>
+        <v>-1148.877008189757</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-1114.895746721222</v>
+        <v>-1148.877008189757</v>
       </c>
       <c r="Q55">
-        <v>-1103.895746721222</v>
+        <v>-1137.877008189757</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1099924030388816</v>
+        <v>0.1113878900614659</v>
       </c>
       <c r="T55">
-        <v>1.175706405097904</v>
+        <v>1.201265239991337</v>
       </c>
       <c r="U55">
         <v>0.2091811058765187</v>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3809597437829331</v>
+        <v>0.3739049337128787</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6096,22 +6096,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1641962266015944</v>
+        <v>0.1658300376603596</v>
       </c>
       <c r="C56">
-        <v>-2935.836980348362</v>
+        <v>-3162.907846934912</v>
       </c>
       <c r="D56">
-        <v>4767.509019651639</v>
+        <v>4702.887153065088</v>
       </c>
       <c r="E56">
-        <v>2346.846000000001</v>
+        <v>2509.295</v>
       </c>
       <c r="F56">
-        <v>8772.246000000001</v>
+        <v>8934.695</v>
       </c>
       <c r="G56">
         <v>1068.9</v>
@@ -6132,28 +6132,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M56">
-        <v>1834.988119300868</v>
+        <v>1868.969380769403</v>
       </c>
       <c r="N56">
-        <v>-1148.877008189757</v>
+        <v>-1182.858269658291</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-1148.877008189757</v>
+        <v>-1182.858269658291</v>
       </c>
       <c r="Q56">
-        <v>-1137.877008189757</v>
+        <v>-1171.858269658291</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1113878900614659</v>
+        <v>0.1128453987294985</v>
       </c>
       <c r="T56">
-        <v>1.201265239991337</v>
+        <v>1.227960023102256</v>
       </c>
       <c r="U56">
         <v>0.2091811058765187</v>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3739049337128787</v>
+        <v>0.3671066621908264</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6178,22 +6178,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1658300376603596</v>
+        <v>0.1674638487191248</v>
       </c>
       <c r="C57">
-        <v>-3162.907846934912</v>
+        <v>-3388.250289461997</v>
       </c>
       <c r="D57">
-        <v>4702.887153065088</v>
+        <v>4639.993710538002</v>
       </c>
       <c r="E57">
-        <v>2509.295</v>
+        <v>2671.744000000001</v>
       </c>
       <c r="F57">
-        <v>8934.695</v>
+        <v>9097.144</v>
       </c>
       <c r="G57">
         <v>1068.9</v>
@@ -6214,28 +6214,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M57">
-        <v>1868.969380769403</v>
+        <v>1902.950642237937</v>
       </c>
       <c r="N57">
-        <v>-1182.858269658291</v>
+        <v>-1216.839531126826</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-1182.858269658291</v>
+        <v>-1216.839531126826</v>
       </c>
       <c r="Q57">
-        <v>-1171.858269658291</v>
+        <v>-1205.839531126826</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1128453987294985</v>
+        <v>0.1143691577915326</v>
       </c>
       <c r="T57">
-        <v>1.227960023102256</v>
+        <v>1.255868205445489</v>
       </c>
       <c r="U57">
         <v>0.2091811058765187</v>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3671066621908264</v>
+        <v>0.3605511860802759</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6260,22 +6260,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1674638487191248</v>
+        <v>0.16909765977789</v>
       </c>
       <c r="C58">
-        <v>-3388.250289461997</v>
+        <v>-3611.932737352921</v>
       </c>
       <c r="D58">
-        <v>4639.993710538002</v>
+        <v>4578.76026264708</v>
       </c>
       <c r="E58">
-        <v>2671.744000000001</v>
+        <v>2834.193000000001</v>
       </c>
       <c r="F58">
-        <v>9097.144</v>
+        <v>9259.593000000001</v>
       </c>
       <c r="G58">
         <v>1068.9</v>
@@ -6296,28 +6296,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M58">
-        <v>1902.950642237937</v>
+        <v>1936.931903706472</v>
       </c>
       <c r="N58">
-        <v>-1216.839531126826</v>
+        <v>-1250.820792595361</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-1216.839531126826</v>
+        <v>-1250.820792595361</v>
       </c>
       <c r="Q58">
-        <v>-1205.839531126826</v>
+        <v>-1239.820792595361</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1143691577915326</v>
+        <v>0.1159637893680799</v>
       </c>
       <c r="T58">
-        <v>1.255868205445489</v>
+        <v>1.285074442781431</v>
       </c>
       <c r="U58">
         <v>0.2091811058765187</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3605511860802759</v>
+        <v>0.3542257266753588</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6342,22 +6342,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.16909765977789</v>
+        <v>0.1707314708366552</v>
       </c>
       <c r="C59">
-        <v>-3611.932737352921</v>
+        <v>-3834.020054860113</v>
       </c>
       <c r="D59">
-        <v>4578.76026264708</v>
+        <v>4519.121945139887</v>
       </c>
       <c r="E59">
-        <v>2834.193000000001</v>
+        <v>2996.642000000002</v>
       </c>
       <c r="F59">
-        <v>9259.593000000001</v>
+        <v>9422.042000000001</v>
       </c>
       <c r="G59">
         <v>1068.9</v>
@@ -6378,28 +6378,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M59">
-        <v>1936.931903706472</v>
+        <v>1970.913165175006</v>
       </c>
       <c r="N59">
-        <v>-1250.820792595361</v>
+        <v>-1284.802054063895</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-1250.820792595361</v>
+        <v>-1284.802054063895</v>
       </c>
       <c r="Q59">
-        <v>-1239.820792595361</v>
+        <v>-1273.802054063895</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1159637893680799</v>
+        <v>0.1176343557816056</v>
       </c>
       <c r="T59">
-        <v>1.285074442781431</v>
+        <v>1.315671453323846</v>
       </c>
       <c r="U59">
         <v>0.2091811058765187</v>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3542257266753588</v>
+        <v>0.3481183865602664</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6424,22 +6424,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1707314708366552</v>
+        <v>0.1723652818954204</v>
       </c>
       <c r="C60">
-        <v>-3834.020054860111</v>
+        <v>-4054.573770261482</v>
       </c>
       <c r="D60">
-        <v>4519.121945139887</v>
+        <v>4461.017229738518</v>
       </c>
       <c r="E60">
-        <v>2996.642</v>
+        <v>3159.091</v>
       </c>
       <c r="F60">
-        <v>9422.041999999999</v>
+        <v>9584.491</v>
       </c>
       <c r="G60">
         <v>1068.9</v>
@@ -6460,28 +6460,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M60">
-        <v>1970.913165175006</v>
+        <v>2004.894426643541</v>
       </c>
       <c r="N60">
-        <v>-1284.802054063895</v>
+        <v>-1318.78331553243</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-1284.802054063895</v>
+        <v>-1318.78331553243</v>
       </c>
       <c r="Q60">
-        <v>-1273.802054063895</v>
+        <v>-1307.78331553243</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1176343557816055</v>
+        <v>0.1193864132396935</v>
       </c>
       <c r="T60">
-        <v>1.315671453323845</v>
+        <v>1.34776100096589</v>
       </c>
       <c r="U60">
         <v>0.2091811058765187</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3481183865602665</v>
+        <v>0.3422180749236517</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6506,22 +6506,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1723652818954204</v>
+        <v>0.1739990929541856</v>
       </c>
       <c r="C61">
-        <v>-4054.573770261482</v>
+        <v>-4273.652287599803</v>
       </c>
       <c r="D61">
-        <v>4461.017229738518</v>
+        <v>4404.387712400196</v>
       </c>
       <c r="E61">
-        <v>3159.091</v>
+        <v>3321.539999999999</v>
       </c>
       <c r="F61">
-        <v>9584.491</v>
+        <v>9746.939999999999</v>
       </c>
       <c r="G61">
         <v>1068.9</v>
@@ -6542,28 +6542,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M61">
-        <v>2004.894426643541</v>
+        <v>2038.875688112075</v>
       </c>
       <c r="N61">
-        <v>-1318.78331553243</v>
+        <v>-1352.764577000964</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-1318.78331553243</v>
+        <v>-1352.764577000964</v>
       </c>
       <c r="Q61">
-        <v>-1307.78331553243</v>
+        <v>-1341.764577000964</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1193864132396935</v>
+        <v>0.1212260735706858</v>
       </c>
       <c r="T61">
-        <v>1.34776100096589</v>
+        <v>1.381455025990038</v>
       </c>
       <c r="U61">
         <v>0.2091811058765187</v>
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3422180749236517</v>
+        <v>0.3365144403415909</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6588,22 +6588,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1739990929541856</v>
+        <v>0.1756329040129507</v>
       </c>
       <c r="C62">
-        <v>-4273.652287599803</v>
+        <v>-4491.311082496994</v>
       </c>
       <c r="D62">
-        <v>4404.387712400196</v>
+        <v>4349.177917503005</v>
       </c>
       <c r="E62">
-        <v>3321.539999999999</v>
+        <v>3483.989</v>
       </c>
       <c r="F62">
-        <v>9746.939999999999</v>
+        <v>9909.388999999999</v>
       </c>
       <c r="G62">
         <v>1068.9</v>
@@ -6624,28 +6624,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M62">
-        <v>2038.875688112075</v>
+        <v>2072.85694958061</v>
       </c>
       <c r="N62">
-        <v>-1352.764577000964</v>
+        <v>-1386.745838469499</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-1352.764577000964</v>
+        <v>-1386.745838469499</v>
       </c>
       <c r="Q62">
-        <v>-1341.764577000964</v>
+        <v>-1375.745838469499</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1212260735706858</v>
+        <v>0.1231600754571137</v>
       </c>
       <c r="T62">
-        <v>1.381455025990038</v>
+        <v>1.416876949733372</v>
       </c>
       <c r="U62">
         <v>0.2091811058765187</v>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3365144403415909</v>
+        <v>0.3309978101720567</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6670,22 +6670,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1756329040129507</v>
+        <v>0.1772667150717159</v>
       </c>
       <c r="C63">
-        <v>-4491.311082496994</v>
+        <v>-4707.602883423269</v>
       </c>
       <c r="D63">
-        <v>4349.177917503005</v>
+        <v>4295.33511657673</v>
       </c>
       <c r="E63">
-        <v>3483.989</v>
+        <v>3646.438</v>
       </c>
       <c r="F63">
-        <v>9909.388999999999</v>
+        <v>10071.838</v>
       </c>
       <c r="G63">
         <v>1068.9</v>
@@ -6706,28 +6706,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M63">
-        <v>2072.85694958061</v>
+        <v>2106.838211049144</v>
       </c>
       <c r="N63">
-        <v>-1386.745838469499</v>
+        <v>-1420.727099938033</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-1386.745838469499</v>
+        <v>-1420.727099938033</v>
       </c>
       <c r="Q63">
-        <v>-1375.745838469499</v>
+        <v>-1409.727099938033</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1231600754571137</v>
+        <v>0.1251958669165114</v>
       </c>
       <c r="T63">
-        <v>1.416876949733372</v>
+        <v>1.454163185252671</v>
       </c>
       <c r="U63">
         <v>0.2091811058765187</v>
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3309978101720567</v>
+        <v>0.3256591358144428</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6752,22 +6752,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1772667150717159</v>
+        <v>0.1789005261304811</v>
       </c>
       <c r="C64">
-        <v>-4707.602883423269</v>
+        <v>-4922.577839666325</v>
       </c>
       <c r="D64">
-        <v>4295.33511657673</v>
+        <v>4242.809160333675</v>
       </c>
       <c r="E64">
-        <v>3646.438</v>
+        <v>3808.887000000001</v>
       </c>
       <c r="F64">
-        <v>10071.838</v>
+        <v>10234.287</v>
       </c>
       <c r="G64">
         <v>1068.9</v>
@@ -6788,28 +6788,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M64">
-        <v>2106.838211049144</v>
+        <v>2140.819472517679</v>
       </c>
       <c r="N64">
-        <v>-1420.727099938033</v>
+        <v>-1454.708361406568</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-1420.727099938033</v>
+        <v>-1454.708361406568</v>
       </c>
       <c r="Q64">
-        <v>-1409.727099938033</v>
+        <v>-1443.708361406568</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1251958669165114</v>
+        <v>0.1273417011574982</v>
       </c>
       <c r="T64">
-        <v>1.454163185252671</v>
+        <v>1.493464892962203</v>
       </c>
       <c r="U64">
         <v>0.2091811058765187</v>
@@ -6826,7 +6826,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3256591358144428</v>
+        <v>0.3204899431824675</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6834,22 +6834,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1789005261304811</v>
+        <v>0.1805343371892463</v>
       </c>
       <c r="C65">
-        <v>-4922.577839666325</v>
+        <v>-5136.283677125206</v>
       </c>
       <c r="D65">
-        <v>4242.809160333675</v>
+        <v>4191.552322874794</v>
       </c>
       <c r="E65">
-        <v>3808.887000000001</v>
+        <v>3971.336000000001</v>
       </c>
       <c r="F65">
-        <v>10234.287</v>
+        <v>10396.736</v>
       </c>
       <c r="G65">
         <v>1068.9</v>
@@ -6870,28 +6870,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M65">
-        <v>2140.819472517679</v>
+        <v>2174.800733986214</v>
       </c>
       <c r="N65">
-        <v>-1454.708361406568</v>
+        <v>-1488.689622875103</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-1454.708361406568</v>
+        <v>-1488.689622875103</v>
       </c>
       <c r="Q65">
-        <v>-1443.708361406568</v>
+        <v>-1477.689622875103</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1273417011574982</v>
+        <v>0.1296067484118731</v>
       </c>
       <c r="T65">
-        <v>1.493464892962203</v>
+        <v>1.53495002887782</v>
       </c>
       <c r="U65">
         <v>0.2091811058765187</v>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3204899431824675</v>
+        <v>0.3154822878202415</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6916,22 +6916,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1805343371892463</v>
+        <v>0.1821681482480115</v>
       </c>
       <c r="C66">
-        <v>-5136.283677125206</v>
+        <v>-5348.765842946234</v>
       </c>
       <c r="D66">
-        <v>4191.552322874794</v>
+        <v>4141.519157053766</v>
       </c>
       <c r="E66">
-        <v>3971.336000000001</v>
+        <v>4133.785</v>
       </c>
       <c r="F66">
-        <v>10396.736</v>
+        <v>10559.185</v>
       </c>
       <c r="G66">
         <v>1068.9</v>
@@ -6952,28 +6952,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M66">
-        <v>2174.800733986214</v>
+        <v>2208.781995454748</v>
       </c>
       <c r="N66">
-        <v>-1488.689622875103</v>
+        <v>-1522.670884343637</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-1488.689622875103</v>
+        <v>-1522.670884343637</v>
       </c>
       <c r="Q66">
-        <v>-1477.689622875103</v>
+        <v>-1511.670884343637</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1296067484118731</v>
+        <v>0.1320012269379267</v>
       </c>
       <c r="T66">
-        <v>1.53495002887782</v>
+        <v>1.578805743988615</v>
       </c>
       <c r="U66">
         <v>0.2091811058765187</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3154822878202415</v>
+        <v>0.3106287141614685</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6998,22 +6998,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1821681482480115</v>
+        <v>0.1838019593067767</v>
       </c>
       <c r="C67">
-        <v>-5348.765842946234</v>
+        <v>-5560.067639922285</v>
       </c>
       <c r="D67">
-        <v>4141.519157053766</v>
+        <v>4092.666360077715</v>
       </c>
       <c r="E67">
-        <v>4133.785</v>
+        <v>4296.234</v>
       </c>
       <c r="F67">
-        <v>10559.185</v>
+        <v>10721.634</v>
       </c>
       <c r="G67">
         <v>1068.9</v>
@@ -7034,28 +7034,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M67">
-        <v>2208.781995454748</v>
+        <v>2242.763256923283</v>
       </c>
       <c r="N67">
-        <v>-1522.670884343637</v>
+        <v>-1556.652145812172</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-1522.670884343637</v>
+        <v>-1556.652145812172</v>
       </c>
       <c r="Q67">
-        <v>-1511.670884343637</v>
+        <v>-1545.652145812172</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1320012269379267</v>
+        <v>0.1345365571419833</v>
       </c>
       <c r="T67">
-        <v>1.578805743988615</v>
+        <v>1.625241207047103</v>
       </c>
       <c r="U67">
         <v>0.2091811058765187</v>
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3106287141614685</v>
+        <v>0.3059222184923553</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7080,22 +7080,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1838019593067767</v>
+        <v>0.1854357703655419</v>
       </c>
       <c r="C68">
-        <v>-5560.067639922285</v>
+        <v>-5770.230351490854</v>
       </c>
       <c r="D68">
-        <v>4092.666360077715</v>
+        <v>4044.952648509146</v>
       </c>
       <c r="E68">
-        <v>4296.234</v>
+        <v>4458.683000000001</v>
       </c>
       <c r="F68">
-        <v>10721.634</v>
+        <v>10884.083</v>
       </c>
       <c r="G68">
         <v>1068.9</v>
@@ -7116,28 +7116,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M68">
-        <v>2242.763256923283</v>
+        <v>2276.744518391818</v>
       </c>
       <c r="N68">
-        <v>-1556.652145812172</v>
+        <v>-1590.633407280706</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-1556.652145812172</v>
+        <v>-1590.633407280706</v>
       </c>
       <c r="Q68">
-        <v>-1545.652145812172</v>
+        <v>-1579.633407280706</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1345365571419833</v>
+        <v>0.1372255437220434</v>
       </c>
       <c r="T68">
-        <v>1.625241207047103</v>
+        <v>1.674490940593985</v>
       </c>
       <c r="U68">
         <v>0.2091811058765187</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3059222184923553</v>
+        <v>0.3013562152312754</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7162,22 +7162,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1854357703655419</v>
+        <v>0.1870695814243071</v>
       </c>
       <c r="C69">
-        <v>-5770.230351490854</v>
+        <v>-5979.293358089228</v>
       </c>
       <c r="D69">
-        <v>4044.952648509146</v>
+        <v>3998.338641910774</v>
       </c>
       <c r="E69">
-        <v>4458.683000000001</v>
+        <v>4621.132000000001</v>
       </c>
       <c r="F69">
-        <v>10884.083</v>
+        <v>11046.532</v>
       </c>
       <c r="G69">
         <v>1068.9</v>
@@ -7198,28 +7198,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M69">
-        <v>2276.744518391818</v>
+        <v>2310.725779860352</v>
       </c>
       <c r="N69">
-        <v>-1590.633407280706</v>
+        <v>-1624.614668749241</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-1590.633407280706</v>
+        <v>-1624.614668749241</v>
       </c>
       <c r="Q69">
-        <v>-1579.633407280706</v>
+        <v>-1613.614668749241</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1372255437220434</v>
+        <v>0.1400825919633573</v>
       </c>
       <c r="T69">
-        <v>1.674490940593985</v>
+        <v>1.726818782487547</v>
       </c>
       <c r="U69">
         <v>0.2091811058765187</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3013562152312754</v>
+        <v>0.2969245061837567</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7244,22 +7244,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1870695814243071</v>
+        <v>0.1887033924830723</v>
       </c>
       <c r="C70">
-        <v>-5979.293358089228</v>
+        <v>-6187.294245556071</v>
       </c>
       <c r="D70">
-        <v>3998.338641910774</v>
+        <v>3952.78675444393</v>
       </c>
       <c r="E70">
-        <v>4621.132000000001</v>
+        <v>4783.581000000002</v>
       </c>
       <c r="F70">
-        <v>11046.532</v>
+        <v>11208.981</v>
       </c>
       <c r="G70">
         <v>1068.9</v>
@@ -7280,28 +7280,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M70">
-        <v>2310.725779860352</v>
+        <v>2344.707041328887</v>
       </c>
       <c r="N70">
-        <v>-1624.614668749241</v>
+        <v>-1658.595930217776</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-1624.614668749241</v>
+        <v>-1658.595930217776</v>
       </c>
       <c r="Q70">
-        <v>-1613.614668749241</v>
+        <v>-1647.595930217776</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1400825919633573</v>
+        <v>0.1431239658976592</v>
       </c>
       <c r="T70">
-        <v>1.726818782487547</v>
+        <v>1.782522614180694</v>
       </c>
       <c r="U70">
         <v>0.2091811058765187</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2969245061837567</v>
+        <v>0.2926212524709486</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7326,22 +7326,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1887033924830723</v>
+        <v>0.1903372035418374</v>
       </c>
       <c r="C71">
-        <v>-6187.294245556071</v>
+        <v>-6394.268906206577</v>
       </c>
       <c r="D71">
-        <v>3952.78675444393</v>
+        <v>3908.261093793423</v>
       </c>
       <c r="E71">
-        <v>4783.581000000002</v>
+        <v>4946.030000000001</v>
       </c>
       <c r="F71">
-        <v>11208.981</v>
+        <v>11371.43</v>
       </c>
       <c r="G71">
         <v>1068.9</v>
@@ -7362,28 +7362,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M71">
-        <v>2344.707041328887</v>
+        <v>2378.688302797421</v>
       </c>
       <c r="N71">
-        <v>-1658.595930217776</v>
+        <v>-1692.57719168631</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-1658.595930217776</v>
+        <v>-1692.57719168631</v>
       </c>
       <c r="Q71">
-        <v>-1647.595930217776</v>
+        <v>-1681.57719168631</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1431239658976592</v>
+        <v>0.1463680980942478</v>
       </c>
       <c r="T71">
-        <v>1.782522614180694</v>
+        <v>1.841940034653384</v>
       </c>
       <c r="U71">
         <v>0.2091811058765187</v>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2926212524709486</v>
+        <v>0.2884409488642208</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7408,22 +7408,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1903372035418374</v>
+        <v>0.1919710146006026</v>
       </c>
       <c r="C72">
-        <v>-6394.268906206577</v>
+        <v>-6600.251633152388</v>
       </c>
       <c r="D72">
-        <v>3908.261093793423</v>
+        <v>3864.727366847613</v>
       </c>
       <c r="E72">
-        <v>4946.030000000001</v>
+        <v>5108.479000000001</v>
       </c>
       <c r="F72">
-        <v>11371.43</v>
+        <v>11533.879</v>
       </c>
       <c r="G72">
         <v>1068.9</v>
@@ -7444,28 +7444,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M72">
-        <v>2378.688302797421</v>
+        <v>2412.669564265956</v>
       </c>
       <c r="N72">
-        <v>-1692.57719168631</v>
+        <v>-1726.558453154845</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-1692.57719168631</v>
+        <v>-1726.558453154845</v>
       </c>
       <c r="Q72">
-        <v>-1681.57719168631</v>
+        <v>-1715.558453154845</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1463680980942478</v>
+        <v>0.1498359635457736</v>
       </c>
       <c r="T72">
-        <v>1.841940034653384</v>
+        <v>1.905455208262121</v>
       </c>
       <c r="U72">
         <v>0.2091811058765187</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2884409488642208</v>
+        <v>0.2843784002886683</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7490,22 +7490,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1919710146006026</v>
+        <v>0.1936048256593678</v>
       </c>
       <c r="C73">
-        <v>-6600.251633152386</v>
+        <v>-6805.27520838726</v>
       </c>
       <c r="D73">
-        <v>3864.727366847613</v>
+        <v>3822.152791612739</v>
       </c>
       <c r="E73">
-        <v>5108.478999999999</v>
+        <v>5270.928</v>
       </c>
       <c r="F73">
-        <v>11533.879</v>
+        <v>11696.328</v>
       </c>
       <c r="G73">
         <v>1068.9</v>
@@ -7526,28 +7526,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M73">
-        <v>2412.669564265956</v>
+        <v>2446.65082573449</v>
       </c>
       <c r="N73">
-        <v>-1726.558453154845</v>
+        <v>-1760.539714623379</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-1726.558453154845</v>
+        <v>-1760.539714623379</v>
       </c>
       <c r="Q73">
-        <v>-1715.558453154845</v>
+        <v>-1749.539714623379</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1498359635457736</v>
+        <v>0.1535515336724083</v>
       </c>
       <c r="T73">
-        <v>1.905455208262121</v>
+        <v>1.973507179985768</v>
       </c>
       <c r="U73">
         <v>0.2091811058765187</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2843784002886683</v>
+        <v>0.280428700284659</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7572,22 +7572,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1936048256593678</v>
+        <v>0.195238636718133</v>
       </c>
       <c r="C74">
-        <v>-6805.27520838726</v>
+        <v>-7009.370985113959</v>
       </c>
       <c r="D74">
-        <v>3822.152791612739</v>
+        <v>3780.506014886041</v>
       </c>
       <c r="E74">
-        <v>5270.928</v>
+        <v>5433.377</v>
       </c>
       <c r="F74">
-        <v>11696.328</v>
+        <v>11858.777</v>
       </c>
       <c r="G74">
         <v>1068.9</v>
@@ -7608,28 +7608,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M74">
-        <v>2446.65082573449</v>
+        <v>2480.632087203025</v>
       </c>
       <c r="N74">
-        <v>-1760.539714623379</v>
+        <v>-1794.520976091914</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-1760.539714623379</v>
+        <v>-1794.520976091914</v>
       </c>
       <c r="Q74">
-        <v>-1749.539714623379</v>
+        <v>-1783.520976091914</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1535515336724083</v>
+        <v>0.1575423312158309</v>
       </c>
       <c r="T74">
-        <v>1.973507179985768</v>
+        <v>2.046600038503759</v>
       </c>
       <c r="U74">
         <v>0.2091811058765187</v>
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.280428700284659</v>
+        <v>0.2765872112396638</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7654,22 +7654,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.195238636718133</v>
+        <v>0.1968724477768982</v>
       </c>
       <c r="C75">
-        <v>-7009.370985113959</v>
+        <v>-7212.568964746863</v>
       </c>
       <c r="D75">
-        <v>3780.506014886041</v>
+        <v>3739.757035253136</v>
       </c>
       <c r="E75">
-        <v>5433.377</v>
+        <v>5595.825999999999</v>
       </c>
       <c r="F75">
-        <v>11858.777</v>
+        <v>12021.226</v>
       </c>
       <c r="G75">
         <v>1068.9</v>
@@ -7690,28 +7690,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M75">
-        <v>2480.632087203025</v>
+        <v>2514.613348671559</v>
       </c>
       <c r="N75">
-        <v>-1794.520976091914</v>
+        <v>-1828.502237560448</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-1794.520976091914</v>
+        <v>-1828.502237560448</v>
       </c>
       <c r="Q75">
-        <v>-1783.520976091914</v>
+        <v>-1817.502237560448</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1575423312158309</v>
+        <v>0.1618401131856705</v>
       </c>
       <c r="T75">
-        <v>2.046600038503759</v>
+        <v>2.125315424600058</v>
       </c>
       <c r="U75">
         <v>0.2091811058765187</v>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2765872112396638</v>
+        <v>0.2728495462229116</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7736,22 +7736,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1968724477768982</v>
+        <v>0.1985062588356634</v>
       </c>
       <c r="C76">
-        <v>-7212.568964746863</v>
+        <v>-7414.897868987782</v>
       </c>
       <c r="D76">
-        <v>3739.757035253136</v>
+        <v>3699.877131012217</v>
       </c>
       <c r="E76">
-        <v>5595.825999999999</v>
+        <v>5758.275</v>
       </c>
       <c r="F76">
-        <v>12021.226</v>
+        <v>12183.675</v>
       </c>
       <c r="G76">
         <v>1068.9</v>
@@ -7772,28 +7772,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M76">
-        <v>2514.613348671559</v>
+        <v>2548.594610140094</v>
       </c>
       <c r="N76">
-        <v>-1828.502237560448</v>
+        <v>-1862.483499028983</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-1828.502237560448</v>
+        <v>-1862.483499028983</v>
       </c>
       <c r="Q76">
-        <v>-1817.502237560448</v>
+        <v>-1851.483499028983</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1618401131856705</v>
+        <v>0.1664817177130973</v>
       </c>
       <c r="T76">
-        <v>2.125315424600058</v>
+        <v>2.21032804158406</v>
       </c>
       <c r="U76">
         <v>0.2091811058765187</v>
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2728495462229116</v>
+        <v>0.2692115522732728</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7818,22 +7818,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1985062588356634</v>
+        <v>0.2001400698944286</v>
       </c>
       <c r="C77">
-        <v>-7414.897868987782</v>
+        <v>-7616.385207338788</v>
       </c>
       <c r="D77">
-        <v>3699.877131012217</v>
+        <v>3660.838792661211</v>
       </c>
       <c r="E77">
-        <v>5758.275</v>
+        <v>5920.724</v>
       </c>
       <c r="F77">
-        <v>12183.675</v>
+        <v>12346.124</v>
       </c>
       <c r="G77">
         <v>1068.9</v>
@@ -7854,28 +7854,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M77">
-        <v>2548.594610140094</v>
+        <v>2582.575871608629</v>
       </c>
       <c r="N77">
-        <v>-1862.483499028983</v>
+        <v>-1896.464760497518</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-1862.483499028983</v>
+        <v>-1896.464760497518</v>
       </c>
       <c r="Q77">
-        <v>-1851.483499028983</v>
+        <v>-1885.464760497518</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1664817177130973</v>
+        <v>0.1715101226178097</v>
       </c>
       <c r="T77">
-        <v>2.21032804158406</v>
+        <v>2.30242504331673</v>
       </c>
       <c r="U77">
         <v>0.2091811058765187</v>
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2692115522732728</v>
+        <v>0.2656692950065191</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2001400698944286</v>
+        <v>0.2017738809531938</v>
       </c>
       <c r="C78">
-        <v>-7616.385207338788</v>
+        <v>-7817.057340385641</v>
       </c>
       <c r="D78">
-        <v>3660.838792661211</v>
+        <v>3622.61565961436</v>
       </c>
       <c r="E78">
-        <v>5920.724</v>
+        <v>6083.173000000001</v>
       </c>
       <c r="F78">
-        <v>12346.124</v>
+        <v>12508.573</v>
       </c>
       <c r="G78">
         <v>1068.9</v>
@@ -7936,28 +7936,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M78">
-        <v>2582.575871608629</v>
+        <v>2616.557133077164</v>
       </c>
       <c r="N78">
-        <v>-1896.464760497518</v>
+        <v>-1930.446021966053</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-1896.464760497518</v>
+        <v>-1930.446021966053</v>
       </c>
       <c r="Q78">
-        <v>-1885.464760497518</v>
+        <v>-1919.446021966053</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1715101226178097</v>
+        <v>0.1769757801229319</v>
       </c>
       <c r="T78">
-        <v>2.30242504331673</v>
+        <v>2.402530479982674</v>
       </c>
       <c r="U78">
         <v>0.2091811058765187</v>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2656692950065191</v>
+        <v>0.2622190444220188</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7982,22 +7982,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2017738809531938</v>
+        <v>0.2034076920119589</v>
       </c>
       <c r="C79">
-        <v>-7817.057340385641</v>
+        <v>-8016.939539157662</v>
       </c>
       <c r="D79">
-        <v>3622.61565961436</v>
+        <v>3585.182460842339</v>
       </c>
       <c r="E79">
-        <v>6083.173000000001</v>
+        <v>6245.622000000001</v>
       </c>
       <c r="F79">
-        <v>12508.573</v>
+        <v>12671.022</v>
       </c>
       <c r="G79">
         <v>1068.9</v>
@@ -8018,28 +8018,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M79">
-        <v>2616.557133077164</v>
+        <v>2650.538394545698</v>
       </c>
       <c r="N79">
-        <v>-1930.446021966053</v>
+        <v>-1964.427283434587</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-1930.446021966053</v>
+        <v>-1964.427283434587</v>
       </c>
       <c r="Q79">
-        <v>-1919.446021966053</v>
+        <v>-1953.427283434587</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1769757801229319</v>
+        <v>0.1829383155830651</v>
       </c>
       <c r="T79">
-        <v>2.402530479982674</v>
+        <v>2.511736410890978</v>
       </c>
       <c r="U79">
         <v>0.2091811058765187</v>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2622190444220188</v>
+        <v>0.2588572618012237</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8064,22 +8064,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2034076920119589</v>
+        <v>0.2050415030707241</v>
       </c>
       <c r="C80">
-        <v>-8016.939539157662</v>
+        <v>-8216.056040845013</v>
       </c>
       <c r="D80">
-        <v>3585.182460842339</v>
+        <v>3548.514959154987</v>
       </c>
       <c r="E80">
-        <v>6245.622000000001</v>
+        <v>6408.071</v>
       </c>
       <c r="F80">
-        <v>12671.022</v>
+        <v>12833.471</v>
       </c>
       <c r="G80">
         <v>1068.9</v>
@@ -8100,28 +8100,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M80">
-        <v>2650.538394545698</v>
+        <v>2684.519656014233</v>
       </c>
       <c r="N80">
-        <v>-1964.427283434587</v>
+        <v>-1998.408544903122</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-1964.427283434587</v>
+        <v>-1998.408544903122</v>
       </c>
       <c r="Q80">
-        <v>-1953.427283434587</v>
+        <v>-1987.408544903122</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1829383155830651</v>
+        <v>0.1894687115632111</v>
       </c>
       <c r="T80">
-        <v>2.511736410890978</v>
+        <v>2.631342906647691</v>
       </c>
       <c r="U80">
         <v>0.2091811058765187</v>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2588572618012237</v>
+        <v>0.2555805876012083</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8146,22 +8146,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2050415030707241</v>
+        <v>0.2066753141294893</v>
       </c>
       <c r="C81">
-        <v>-8216.056040845013</v>
+        <v>-8414.430101131478</v>
       </c>
       <c r="D81">
-        <v>3548.514959154987</v>
+        <v>3512.589898868522</v>
       </c>
       <c r="E81">
-        <v>6408.071</v>
+        <v>6570.52</v>
       </c>
       <c r="F81">
-        <v>12833.471</v>
+        <v>12995.92</v>
       </c>
       <c r="G81">
         <v>1068.9</v>
@@ -8182,28 +8182,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M81">
-        <v>2684.519656014233</v>
+        <v>2718.500917482767</v>
       </c>
       <c r="N81">
-        <v>-1998.408544903122</v>
+        <v>-2032.389806371656</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-1998.408544903122</v>
+        <v>-2032.389806371656</v>
       </c>
       <c r="Q81">
-        <v>-1987.408544903122</v>
+        <v>-2021.389806371656</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1894687115632111</v>
+        <v>0.1966521471413717</v>
       </c>
       <c r="T81">
-        <v>2.631342906647691</v>
+        <v>2.762910051980076</v>
       </c>
       <c r="U81">
         <v>0.2091811058765187</v>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2555805876012083</v>
+        <v>0.2523858302561932</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8228,22 +8228,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2066753141294893</v>
+        <v>0.2083091251882545</v>
       </c>
       <c r="C82">
-        <v>-8414.430101131478</v>
+        <v>-8612.084043380211</v>
       </c>
       <c r="D82">
-        <v>3512.589898868522</v>
+        <v>3477.38495661979</v>
       </c>
       <c r="E82">
-        <v>6570.52</v>
+        <v>6732.969000000001</v>
       </c>
       <c r="F82">
-        <v>12995.92</v>
+        <v>13158.369</v>
       </c>
       <c r="G82">
         <v>1068.9</v>
@@ -8264,28 +8264,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M82">
-        <v>2718.500917482767</v>
+        <v>2752.482178951302</v>
       </c>
       <c r="N82">
-        <v>-2032.389806371656</v>
+        <v>-2066.371067840191</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-2032.389806371656</v>
+        <v>-2066.371067840191</v>
       </c>
       <c r="Q82">
-        <v>-2021.389806371656</v>
+        <v>-2055.371067840191</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1966521471413717</v>
+        <v>0.2045917338330228</v>
       </c>
       <c r="T82">
-        <v>2.762910051980076</v>
+        <v>2.908326370505343</v>
       </c>
       <c r="U82">
         <v>0.2091811058765187</v>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2523858302561932</v>
+        <v>0.2492699558085857</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8310,22 +8310,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2083091251882545</v>
+        <v>0.2099429362470197</v>
       </c>
       <c r="C83">
-        <v>-8612.084043380211</v>
+        <v>-8809.039304891052</v>
       </c>
       <c r="D83">
-        <v>3477.38495661979</v>
+        <v>3442.878695108948</v>
       </c>
       <c r="E83">
-        <v>6732.969000000001</v>
+        <v>6895.418000000001</v>
       </c>
       <c r="F83">
-        <v>13158.369</v>
+        <v>13320.818</v>
       </c>
       <c r="G83">
         <v>1068.9</v>
@@ -8346,28 +8346,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M83">
-        <v>2752.482178951302</v>
+        <v>2786.463440419837</v>
       </c>
       <c r="N83">
-        <v>-2066.371067840191</v>
+        <v>-2100.352329308726</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-2066.371067840191</v>
+        <v>-2100.352329308726</v>
       </c>
       <c r="Q83">
-        <v>-2055.371067840191</v>
+        <v>-2089.352329308726</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2045917338330228</v>
+        <v>0.2134134968237464</v>
       </c>
       <c r="T83">
-        <v>2.908326370505343</v>
+        <v>3.06990005775564</v>
       </c>
       <c r="U83">
         <v>0.2091811058765187</v>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2492699558085857</v>
+        <v>0.2462300782987251</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8392,22 +8392,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2099429362470197</v>
+        <v>0.2115767473057849</v>
       </c>
       <c r="C84">
-        <v>-8809.039304891052</v>
+        <v>-9005.316480430833</v>
       </c>
       <c r="D84">
-        <v>3442.878695108948</v>
+        <v>3409.050519569168</v>
       </c>
       <c r="E84">
-        <v>6895.418000000001</v>
+        <v>7057.867000000002</v>
       </c>
       <c r="F84">
-        <v>13320.818</v>
+        <v>13483.267</v>
       </c>
       <c r="G84">
         <v>1068.9</v>
@@ -8428,28 +8428,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M84">
-        <v>2786.463440419837</v>
+        <v>2820.444701888371</v>
       </c>
       <c r="N84">
-        <v>-2100.352329308726</v>
+        <v>-2134.33359077726</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-2100.352329308726</v>
+        <v>-2134.33359077726</v>
       </c>
       <c r="Q84">
-        <v>-2089.352329308726</v>
+        <v>-2123.33359077726</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2134134968237464</v>
+        <v>0.2232731142839667</v>
       </c>
       <c r="T84">
-        <v>3.06990005775564</v>
+        <v>3.250482414094208</v>
       </c>
       <c r="U84">
         <v>0.2091811058765187</v>
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2462300782987251</v>
+        <v>0.2432634508493429</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8474,22 +8474,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2115767473057849</v>
+        <v>0.2132105583645501</v>
       </c>
       <c r="C85">
-        <v>-9005.316480430833</v>
+        <v>-9200.935363222376</v>
       </c>
       <c r="D85">
-        <v>3409.050519569168</v>
+        <v>3375.880636777625</v>
       </c>
       <c r="E85">
-        <v>7057.867000000002</v>
+        <v>7220.316000000001</v>
       </c>
       <c r="F85">
-        <v>13483.267</v>
+        <v>13645.716</v>
       </c>
       <c r="G85">
         <v>1068.9</v>
@@ -8510,28 +8510,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M85">
-        <v>2820.444701888371</v>
+        <v>2854.425963356906</v>
       </c>
       <c r="N85">
-        <v>-2134.33359077726</v>
+        <v>-2168.314852245795</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-2134.33359077726</v>
+        <v>-2168.314852245795</v>
       </c>
       <c r="Q85">
-        <v>-2123.33359077726</v>
+        <v>-2157.314852245795</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2232731142839667</v>
+        <v>0.2343651839267147</v>
       </c>
       <c r="T85">
-        <v>3.250482414094208</v>
+        <v>3.453637564975096</v>
       </c>
       <c r="U85">
         <v>0.2091811058765187</v>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2432634508493429</v>
+        <v>0.2403674573868505</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8556,22 +8556,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2132105583645501</v>
+        <v>0.2148443694233153</v>
       </c>
       <c r="C86">
-        <v>-9200.935363222372</v>
+        <v>-9395.914983563636</v>
       </c>
       <c r="D86">
-        <v>3375.880636777626</v>
+        <v>3343.350016436363</v>
       </c>
       <c r="E86">
-        <v>7220.315999999999</v>
+        <v>7382.764999999999</v>
       </c>
       <c r="F86">
-        <v>13645.716</v>
+        <v>13808.165</v>
       </c>
       <c r="G86">
         <v>1068.9</v>
@@ -8592,28 +8592,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M86">
-        <v>2854.425963356905</v>
+        <v>2888.40722482544</v>
       </c>
       <c r="N86">
-        <v>-2168.314852245794</v>
+        <v>-2202.296113714329</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-2168.314852245794</v>
+        <v>-2202.296113714329</v>
       </c>
       <c r="Q86">
-        <v>-2157.314852245794</v>
+        <v>-2191.296113714329</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2343651839267146</v>
+        <v>0.2469361961884955</v>
       </c>
       <c r="T86">
-        <v>3.453637564975094</v>
+        <v>3.683880069306767</v>
       </c>
       <c r="U86">
         <v>0.2091811058765187</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2403674573868507</v>
+        <v>0.2375396049470052</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8638,22 +8638,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2148443694233153</v>
+        <v>0.2164781804820804</v>
       </c>
       <c r="C87">
-        <v>-9395.914983563636</v>
+        <v>-9590.273645235329</v>
       </c>
       <c r="D87">
-        <v>3343.350016436363</v>
+        <v>3311.440354764671</v>
       </c>
       <c r="E87">
-        <v>7382.764999999999</v>
+        <v>7545.214</v>
       </c>
       <c r="F87">
-        <v>13808.165</v>
+        <v>13970.614</v>
       </c>
       <c r="G87">
         <v>1068.9</v>
@@ -8674,28 +8674,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M87">
-        <v>2888.40722482544</v>
+        <v>2922.388486293975</v>
       </c>
       <c r="N87">
-        <v>-2202.296113714329</v>
+        <v>-2236.277375182864</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-2202.296113714329</v>
+        <v>-2236.277375182864</v>
       </c>
       <c r="Q87">
-        <v>-2191.296113714329</v>
+        <v>-2225.277375182864</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2469361961884955</v>
+        <v>0.2613030673448166</v>
       </c>
       <c r="T87">
-        <v>3.683880069306767</v>
+        <v>3.947014359971536</v>
       </c>
       <c r="U87">
         <v>0.2091811058765187</v>
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2375396049470052</v>
+        <v>0.2347775165173891</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8720,22 +8720,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2164781804820804</v>
+        <v>0.2181119915408456</v>
       </c>
       <c r="C88">
-        <v>-9590.273645235329</v>
+        <v>-9784.028959843323</v>
       </c>
       <c r="D88">
-        <v>3311.440354764671</v>
+        <v>3280.134040156676</v>
       </c>
       <c r="E88">
-        <v>7545.214</v>
+        <v>7707.663</v>
       </c>
       <c r="F88">
-        <v>13970.614</v>
+        <v>14133.063</v>
       </c>
       <c r="G88">
         <v>1068.9</v>
@@ -8756,28 +8756,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M88">
-        <v>2922.388486293975</v>
+        <v>2956.369747762509</v>
       </c>
       <c r="N88">
-        <v>-2236.277375182864</v>
+        <v>-2270.258636651398</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-2236.277375182864</v>
+        <v>-2270.258636651398</v>
       </c>
       <c r="Q88">
-        <v>-2225.277375182864</v>
+        <v>-2259.258636651398</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2613030673448166</v>
+        <v>0.277880226371341</v>
       </c>
       <c r="T88">
-        <v>3.947014359971536</v>
+        <v>4.250630849200116</v>
       </c>
       <c r="U88">
         <v>0.2091811058765187</v>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2347775165173891</v>
+        <v>0.2320789243735111</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8802,22 +8802,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2181119915408456</v>
+        <v>0.2197458025996108</v>
       </c>
       <c r="C89">
-        <v>-9784.028959843323</v>
+        <v>-9977.197879231295</v>
       </c>
       <c r="D89">
-        <v>3280.134040156676</v>
+        <v>3249.414120768706</v>
       </c>
       <c r="E89">
-        <v>7707.663</v>
+        <v>7870.112000000001</v>
       </c>
       <c r="F89">
-        <v>14133.063</v>
+        <v>14295.512</v>
       </c>
       <c r="G89">
         <v>1068.9</v>
@@ -8838,28 +8838,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M89">
-        <v>2956.369747762509</v>
+        <v>2990.351009231044</v>
       </c>
       <c r="N89">
-        <v>-2270.258636651398</v>
+        <v>-2304.239898119933</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-2270.258636651398</v>
+        <v>-2304.239898119933</v>
       </c>
       <c r="Q89">
-        <v>-2259.258636651398</v>
+        <v>-2293.239898119933</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.277880226371341</v>
+        <v>0.2972202452356195</v>
       </c>
       <c r="T89">
-        <v>4.250630849200116</v>
+        <v>4.604850086633459</v>
       </c>
       <c r="U89">
         <v>0.2091811058765187</v>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2320789243735111</v>
+        <v>0.2294416638692665</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8884,22 +8884,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2197458025996108</v>
+        <v>0.221379613658376</v>
       </c>
       <c r="C90">
-        <v>-9977.197879231295</v>
+        <v>-10169.79672608889</v>
       </c>
       <c r="D90">
-        <v>3249.414120768706</v>
+        <v>3219.264273911106</v>
       </c>
       <c r="E90">
-        <v>7870.112000000001</v>
+        <v>8032.561</v>
       </c>
       <c r="F90">
-        <v>14295.512</v>
+        <v>14457.961</v>
       </c>
       <c r="G90">
         <v>1068.9</v>
@@ -8920,28 +8920,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M90">
-        <v>2990.351009231044</v>
+        <v>3024.332270699578</v>
       </c>
       <c r="N90">
-        <v>-2304.239898119933</v>
+        <v>-2338.221159588467</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-2304.239898119933</v>
+        <v>-2338.221159588467</v>
       </c>
       <c r="Q90">
-        <v>-2293.239898119933</v>
+        <v>-2327.221159588467</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2972202452356195</v>
+        <v>0.3200766311661303</v>
       </c>
       <c r="T90">
-        <v>4.604850086633459</v>
+        <v>5.023472821781955</v>
       </c>
       <c r="U90">
         <v>0.2091811058765187</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2294416638692665</v>
+        <v>0.2268636676460163</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8966,22 +8966,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.221379613658376</v>
+        <v>0.2230134247171412</v>
       </c>
       <c r="C91">
-        <v>-10169.79672608889</v>
+        <v>-10361.8412228716</v>
       </c>
       <c r="D91">
-        <v>3219.264273911106</v>
+        <v>3189.6687771284</v>
       </c>
       <c r="E91">
-        <v>8032.561</v>
+        <v>8195.01</v>
       </c>
       <c r="F91">
-        <v>14457.961</v>
+        <v>14620.41</v>
       </c>
       <c r="G91">
         <v>1068.9</v>
@@ -9002,28 +9002,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M91">
-        <v>3024.332270699578</v>
+        <v>3058.313532168113</v>
       </c>
       <c r="N91">
-        <v>-2338.221159588467</v>
+        <v>-2372.202421057002</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-2338.221159588467</v>
+        <v>-2372.202421057002</v>
       </c>
       <c r="Q91">
-        <v>-2327.221159588467</v>
+        <v>-2361.202421057002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3200766311661303</v>
+        <v>0.3475042942827434</v>
       </c>
       <c r="T91">
-        <v>5.023472821781955</v>
+        <v>5.525820103960152</v>
       </c>
       <c r="U91">
         <v>0.2091811058765187</v>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2268636676460163</v>
+        <v>0.2243429602277274</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9048,22 +9048,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2230134247171412</v>
+        <v>0.2246472357759064</v>
       </c>
       <c r="C92">
-        <v>-10361.8412228716</v>
+        <v>-10553.34651913989</v>
       </c>
       <c r="D92">
-        <v>3189.6687771284</v>
+        <v>3160.612480860112</v>
       </c>
       <c r="E92">
-        <v>8195.01</v>
+        <v>8357.459000000001</v>
       </c>
       <c r="F92">
-        <v>14620.41</v>
+        <v>14782.859</v>
       </c>
       <c r="G92">
         <v>1068.9</v>
@@ -9084,28 +9084,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M92">
-        <v>3058.313532168113</v>
+        <v>3092.294793636648</v>
       </c>
       <c r="N92">
-        <v>-2372.202421057002</v>
+        <v>-2406.183682525537</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-2372.202421057002</v>
+        <v>-2406.183682525537</v>
       </c>
       <c r="Q92">
-        <v>-2361.202421057002</v>
+        <v>-2395.183682525537</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3475042942827434</v>
+        <v>0.3810269936474927</v>
       </c>
       <c r="T92">
-        <v>5.525820103960152</v>
+        <v>6.139800115511281</v>
       </c>
       <c r="U92">
         <v>0.2091811058765187</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2243429602277274</v>
+        <v>0.2218776529724774</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9130,22 +9130,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2246472357759064</v>
+        <v>0.2262810468346716</v>
       </c>
       <c r="C93">
-        <v>-10553.34651913989</v>
+        <v>-10744.32721741762</v>
       </c>
       <c r="D93">
-        <v>3160.612480860112</v>
+        <v>3132.080782582384</v>
       </c>
       <c r="E93">
-        <v>8357.459000000001</v>
+        <v>8519.908000000001</v>
       </c>
       <c r="F93">
-        <v>14782.859</v>
+        <v>14945.308</v>
       </c>
       <c r="G93">
         <v>1068.9</v>
@@ -9166,28 +9166,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M93">
-        <v>3092.294793636648</v>
+        <v>3126.276055105182</v>
       </c>
       <c r="N93">
-        <v>-2406.183682525537</v>
+        <v>-2440.164943994071</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-2406.183682525537</v>
+        <v>-2440.164943994071</v>
       </c>
       <c r="Q93">
-        <v>-2395.183682525537</v>
+        <v>-2429.164943994071</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3810269936474927</v>
+        <v>0.4229303678534294</v>
       </c>
       <c r="T93">
-        <v>6.139800115511281</v>
+        <v>6.907275129950192</v>
       </c>
       <c r="U93">
         <v>0.2091811058765187</v>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2218776529724774</v>
+        <v>0.2194659393532116</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9212,22 +9212,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2262810468346716</v>
+        <v>0.2279148578934367</v>
       </c>
       <c r="C94">
-        <v>-10744.32721741762</v>
+        <v>-10934.79739766237</v>
       </c>
       <c r="D94">
-        <v>3132.080782582384</v>
+        <v>3104.059602337633</v>
       </c>
       <c r="E94">
-        <v>8519.908000000001</v>
+        <v>8682.357</v>
       </c>
       <c r="F94">
-        <v>14945.308</v>
+        <v>15107.757</v>
       </c>
       <c r="G94">
         <v>1068.9</v>
@@ -9248,28 +9248,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M94">
-        <v>3126.276055105182</v>
+        <v>3160.257316573717</v>
       </c>
       <c r="N94">
-        <v>-2440.164943994071</v>
+        <v>-2474.146205462605</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-2440.164943994071</v>
+        <v>-2474.146205462605</v>
       </c>
       <c r="Q94">
-        <v>-2429.164943994071</v>
+        <v>-2463.146205462605</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4229303678534294</v>
+        <v>0.4768061346896336</v>
       </c>
       <c r="T94">
-        <v>6.907275129950192</v>
+        <v>7.894028719943078</v>
       </c>
       <c r="U94">
         <v>0.2091811058765187</v>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2194659393532116</v>
+        <v>0.2171060905429619</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9294,22 +9294,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2279148578934367</v>
+        <v>0.2295486689522019</v>
       </c>
       <c r="C95">
-        <v>-10934.79739766237</v>
+        <v>-11124.77064043387</v>
       </c>
       <c r="D95">
-        <v>3104.059602337633</v>
+        <v>3076.535359566132</v>
       </c>
       <c r="E95">
-        <v>8682.357</v>
+        <v>8844.806</v>
       </c>
       <c r="F95">
-        <v>15107.757</v>
+        <v>15270.206</v>
       </c>
       <c r="G95">
         <v>1068.9</v>
@@ -9330,28 +9330,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M95">
-        <v>3160.257316573717</v>
+        <v>3194.238578042251</v>
       </c>
       <c r="N95">
-        <v>-2474.146205462605</v>
+        <v>-2508.127466931141</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-2474.146205462605</v>
+        <v>-2508.127466931141</v>
       </c>
       <c r="Q95">
-        <v>-2463.146205462605</v>
+        <v>-2497.127466931141</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4768061346896336</v>
+        <v>0.5486404904712392</v>
       </c>
       <c r="T95">
-        <v>7.894028719943078</v>
+        <v>9.209700173266926</v>
       </c>
       <c r="U95">
         <v>0.2091811058765187</v>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2171060905429619</v>
+        <v>0.2147964512818664</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9376,22 +9376,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2295486689522019</v>
+        <v>0.2311824800109671</v>
       </c>
       <c r="C96">
-        <v>-11124.77064043387</v>
+        <v>-11314.26004884064</v>
       </c>
       <c r="D96">
-        <v>3076.535359566132</v>
+        <v>3049.49495115936</v>
       </c>
       <c r="E96">
-        <v>8844.806</v>
+        <v>9007.255000000001</v>
       </c>
       <c r="F96">
-        <v>15270.206</v>
+        <v>15432.655</v>
       </c>
       <c r="G96">
         <v>1068.9</v>
@@ -9412,28 +9412,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M96">
-        <v>3194.238578042251</v>
+        <v>3228.219839510786</v>
       </c>
       <c r="N96">
-        <v>-2508.127466931141</v>
+        <v>-2542.108728399675</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-2508.127466931141</v>
+        <v>-2542.108728399675</v>
       </c>
       <c r="Q96">
-        <v>-2497.127466931141</v>
+        <v>-2531.108728399675</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5486404904712392</v>
+        <v>0.6492085885654874</v>
       </c>
       <c r="T96">
-        <v>9.209700173266926</v>
+        <v>11.05164020792032</v>
       </c>
       <c r="U96">
         <v>0.2091811058765187</v>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2147964512818664</v>
+        <v>0.2125354360052154</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9458,22 +9458,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2311824800109671</v>
+        <v>0.2328162910697323</v>
       </c>
       <c r="C97">
-        <v>-11314.26004884064</v>
+        <v>-11503.27826933936</v>
       </c>
       <c r="D97">
-        <v>3049.49495115936</v>
+        <v>3022.925730660645</v>
       </c>
       <c r="E97">
-        <v>9007.255000000001</v>
+        <v>9169.704000000002</v>
       </c>
       <c r="F97">
-        <v>15432.655</v>
+        <v>15595.104</v>
       </c>
       <c r="G97">
         <v>1068.9</v>
@@ -9494,28 +9494,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M97">
-        <v>3228.219839510786</v>
+        <v>3262.201100979321</v>
       </c>
       <c r="N97">
-        <v>-2542.108728399675</v>
+        <v>-2576.08998986821</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-2542.108728399675</v>
+        <v>-2576.08998986821</v>
       </c>
       <c r="Q97">
-        <v>-2531.108728399675</v>
+        <v>-2565.08998986821</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6492085885654874</v>
+        <v>0.8000607357068596</v>
       </c>
       <c r="T97">
-        <v>11.05164020792032</v>
+        <v>13.8145502599004</v>
       </c>
       <c r="U97">
         <v>0.2091811058765187</v>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2125354360052154</v>
+        <v>0.2103215252134942</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9540,22 +9540,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2328162910697323</v>
+        <v>0.2344501021284975</v>
       </c>
       <c r="C98">
-        <v>-11503.27826933935</v>
+        <v>-11691.83751145627</v>
       </c>
       <c r="D98">
-        <v>3022.925730660645</v>
+        <v>2996.815488543727</v>
       </c>
       <c r="E98">
-        <v>9169.704</v>
+        <v>9332.153</v>
       </c>
       <c r="F98">
-        <v>15595.104</v>
+        <v>15757.553</v>
       </c>
       <c r="G98">
         <v>1068.9</v>
@@ -9576,28 +9576,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M98">
-        <v>3262.20110097932</v>
+        <v>3296.182362447855</v>
       </c>
       <c r="N98">
-        <v>-2576.089989868209</v>
+        <v>-2610.071251336744</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-2576.089989868209</v>
+        <v>-2610.071251336744</v>
       </c>
       <c r="Q98">
-        <v>-2565.089989868209</v>
+        <v>-2599.071251336744</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8000607357068575</v>
+        <v>1.051480980942477</v>
       </c>
       <c r="T98">
-        <v>13.81455025990036</v>
+        <v>18.41940034653382</v>
       </c>
       <c r="U98">
         <v>0.2091811058765187</v>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2103215252134943</v>
+        <v>0.2081532620669634</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9622,22 +9622,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2344501021284975</v>
+        <v>0.2360839131872627</v>
       </c>
       <c r="C99">
-        <v>-11691.83751145627</v>
+        <v>-11879.94956649537</v>
       </c>
       <c r="D99">
-        <v>2996.815488543727</v>
+        <v>2971.152433504625</v>
       </c>
       <c r="E99">
-        <v>9332.153</v>
+        <v>9494.601999999999</v>
       </c>
       <c r="F99">
-        <v>15757.553</v>
+        <v>15920.002</v>
       </c>
       <c r="G99">
         <v>1068.9</v>
@@ -9658,28 +9658,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M99">
-        <v>3296.182362447855</v>
+        <v>3330.163623916389</v>
       </c>
       <c r="N99">
-        <v>-2610.071251336744</v>
+        <v>-2644.052512805279</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-2610.071251336744</v>
+        <v>-2644.052512805279</v>
       </c>
       <c r="Q99">
-        <v>-2599.071251336744</v>
+        <v>-2633.052512805279</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.051480980942477</v>
+        <v>1.554321471413715</v>
       </c>
       <c r="T99">
-        <v>18.41940034653382</v>
+        <v>27.62910051980073</v>
       </c>
       <c r="U99">
         <v>0.2091811058765187</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2081532620669634</v>
+        <v>0.2060292491887291</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9704,22 +9704,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2360839131872627</v>
+        <v>0.2377177242460279</v>
       </c>
       <c r="C100">
-        <v>-11879.94956649537</v>
+        <v>-12067.62582529345</v>
       </c>
       <c r="D100">
-        <v>2971.152433504625</v>
+        <v>2945.925174706546</v>
       </c>
       <c r="E100">
-        <v>9494.601999999999</v>
+        <v>9657.050999999999</v>
       </c>
       <c r="F100">
-        <v>15920.002</v>
+        <v>16082.451</v>
       </c>
       <c r="G100">
         <v>1068.9</v>
@@ -9740,28 +9740,28 @@
         <v>686.1111111111111</v>
       </c>
       <c r="M100">
-        <v>3330.163623916389</v>
+        <v>3364.144885384924</v>
       </c>
       <c r="N100">
-        <v>-2644.052512805279</v>
+        <v>-2678.033774273813</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-2644.052512805279</v>
+        <v>-2678.033774273813</v>
       </c>
       <c r="Q100">
-        <v>-2633.052512805279</v>
+        <v>-2667.033774273813</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.554321471413715</v>
+        <v>3.06284294282743</v>
       </c>
       <c r="T100">
-        <v>27.62910051980073</v>
+        <v>55.25820103960146</v>
       </c>
       <c r="U100">
         <v>0.2091811058765187</v>
@@ -9778,91 +9778,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2060292491887291</v>
+        <v>0.2039481456615703</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2377177242460279</v>
-      </c>
-      <c r="C101">
-        <v>-12067.62582529345</v>
-      </c>
-      <c r="D101">
-        <v>2945.925174706546</v>
-      </c>
-      <c r="E101">
-        <v>9657.050999999999</v>
-      </c>
-      <c r="F101">
-        <v>16082.451</v>
-      </c>
-      <c r="G101">
-        <v>1068.9</v>
-      </c>
-      <c r="H101">
-        <v>9819.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>697.1111111111111</v>
-      </c>
-      <c r="K101">
-        <v>11</v>
-      </c>
-      <c r="L101">
-        <v>686.1111111111111</v>
-      </c>
-      <c r="M101">
-        <v>3364.144885384924</v>
-      </c>
-      <c r="N101">
-        <v>-2678.033774273813</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-2678.033774273813</v>
-      </c>
-      <c r="Q101">
-        <v>-2667.033774273813</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.06284294282743</v>
-      </c>
-      <c r="T101">
-        <v>55.25820103960146</v>
-      </c>
-      <c r="U101">
-        <v>0.2091811058765187</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2091811058765187</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2039481456615703</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
